--- a/artfynd/A 11444-2025 artfynd.xlsx
+++ b/artfynd/A 11444-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123259440</v>
+        <v>123259882</v>
       </c>
       <c r="B2" t="n">
-        <v>98365</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576980</v>
+        <v>576832</v>
       </c>
       <c r="R2" t="n">
-        <v>6379697</v>
+        <v>6379712</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,13 +761,17 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Bearbetat torrträd</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123259882</v>
+        <v>123259362</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>98365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,35 +802,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576832</v>
+        <v>576989</v>
       </c>
       <c r="R3" t="n">
-        <v>6379712</v>
+        <v>6379691</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,17 +876,13 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bearbetat torrträd</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123259157</v>
+        <v>123259131</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>92233</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,25 +913,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -939,13 +939,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -953,13 +952,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576997</v>
+        <v>577009</v>
       </c>
       <c r="R4" t="n">
-        <v>6379617</v>
+        <v>6379596</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,6 +996,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123259131</v>
+        <v>123259930</v>
       </c>
       <c r="B5" t="n">
-        <v>92233</v>
+        <v>98365</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,38 +1027,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1066,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577009</v>
+        <v>576949</v>
       </c>
       <c r="R5" t="n">
-        <v>6379596</v>
+        <v>6379790</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123259111</v>
+        <v>123259392</v>
       </c>
       <c r="B6" t="n">
-        <v>92233</v>
+        <v>98365</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,38 +1138,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1180,10 +1174,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577001</v>
+        <v>576988</v>
       </c>
       <c r="R6" t="n">
-        <v>6379581</v>
+        <v>6379698</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123259910</v>
+        <v>123259498</v>
       </c>
       <c r="B7" t="n">
-        <v>91362</v>
+        <v>95136</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1259,34 +1253,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5420</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1294,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576891</v>
+        <v>576965</v>
       </c>
       <c r="R7" t="n">
-        <v>6379777</v>
+        <v>6379700</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1357,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123259498</v>
+        <v>123259271</v>
       </c>
       <c r="B8" t="n">
-        <v>95136</v>
+        <v>98365</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,42 +1356,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444. Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576965</v>
+        <v>576994</v>
       </c>
       <c r="R8" t="n">
-        <v>6379700</v>
+        <v>6379690</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1464,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123259471</v>
+        <v>123259157</v>
       </c>
       <c r="B9" t="n">
-        <v>98365</v>
+        <v>57631</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,49 +1467,53 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 11444, Grönlif, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576971</v>
+        <v>576997</v>
       </c>
       <c r="R9" t="n">
-        <v>6379688</v>
+        <v>6379617</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1556,7 +1551,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1575,10 +1569,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123260939</v>
+        <v>123259554</v>
       </c>
       <c r="B10" t="n">
-        <v>98365</v>
+        <v>105471</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,25 +1581,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1623,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576951</v>
+        <v>576891</v>
       </c>
       <c r="R10" t="n">
-        <v>6379805</v>
+        <v>6379769</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,10 +1680,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123259554</v>
+        <v>123259332</v>
       </c>
       <c r="B11" t="n">
-        <v>105471</v>
+        <v>98365</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1698,25 +1692,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1734,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576891</v>
+        <v>576987</v>
       </c>
       <c r="R11" t="n">
-        <v>6379769</v>
+        <v>6379692</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1797,10 +1791,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123259522</v>
+        <v>123259993</v>
       </c>
       <c r="B12" t="n">
-        <v>98365</v>
+        <v>90972</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1809,35 +1803,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1845,10 +1842,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576971</v>
+        <v>576929</v>
       </c>
       <c r="R12" t="n">
-        <v>6379715</v>
+        <v>6379832</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1908,7 +1905,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123259332</v>
+        <v>123260939</v>
       </c>
       <c r="B13" t="n">
         <v>98365</v>
@@ -1956,10 +1953,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576987</v>
+        <v>576951</v>
       </c>
       <c r="R13" t="n">
-        <v>6379692</v>
+        <v>6379805</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,7 +2016,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123259948</v>
+        <v>123259471</v>
       </c>
       <c r="B14" t="n">
         <v>98365</v>
@@ -2063,14 +2060,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444, Grönlif, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576939</v>
+        <v>576971</v>
       </c>
       <c r="R14" t="n">
-        <v>6379798</v>
+        <v>6379688</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2130,10 +2127,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123259828</v>
+        <v>123259522</v>
       </c>
       <c r="B15" t="n">
-        <v>90952</v>
+        <v>98365</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2142,38 +2139,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2181,10 +2175,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576838</v>
+        <v>576971</v>
       </c>
       <c r="R15" t="n">
-        <v>6379654</v>
+        <v>6379715</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2244,10 +2238,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123259419</v>
+        <v>123259628</v>
       </c>
       <c r="B16" t="n">
-        <v>57631</v>
+        <v>57848</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2256,25 +2250,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2286,20 +2280,20 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A 11444, Grönlif, Sm</t>
+          <t>A11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576985</v>
+        <v>576883</v>
       </c>
       <c r="R16" t="n">
-        <v>6379714</v>
+        <v>6379747</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2358,10 +2352,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123259392</v>
+        <v>123259419</v>
       </c>
       <c r="B17" t="n">
-        <v>98365</v>
+        <v>57631</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2370,49 +2364,53 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444, Grönlif, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576988</v>
+        <v>576985</v>
       </c>
       <c r="R17" t="n">
-        <v>6379698</v>
+        <v>6379714</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2450,7 +2448,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2469,10 +2466,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123259851</v>
+        <v>123259948</v>
       </c>
       <c r="B18" t="n">
-        <v>90952</v>
+        <v>98365</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2481,38 +2478,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2520,10 +2514,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576835</v>
+        <v>576939</v>
       </c>
       <c r="R18" t="n">
-        <v>6379715</v>
+        <v>6379798</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2583,10 +2577,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123259312</v>
+        <v>123259828</v>
       </c>
       <c r="B19" t="n">
-        <v>98365</v>
+        <v>90952</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2595,35 +2589,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2631,10 +2628,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576990</v>
+        <v>576838</v>
       </c>
       <c r="R19" t="n">
-        <v>6379697</v>
+        <v>6379654</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2694,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123259183</v>
+        <v>123259209</v>
       </c>
       <c r="B20" t="n">
-        <v>92233</v>
+        <v>90952</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2706,25 +2703,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2734,7 +2731,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -2745,10 +2742,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577000</v>
+        <v>576992</v>
       </c>
       <c r="R20" t="n">
-        <v>6379640</v>
+        <v>6379660</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2808,10 +2805,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123259084</v>
+        <v>123259111</v>
       </c>
       <c r="B21" t="n">
-        <v>92261</v>
+        <v>92233</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2820,30 +2817,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2855,14 +2852,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>A 11444, Grönled, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577012</v>
+        <v>577001</v>
       </c>
       <c r="R21" t="n">
-        <v>6379533</v>
+        <v>6379581</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2922,7 +2919,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123259930</v>
+        <v>123259974</v>
       </c>
       <c r="B22" t="n">
         <v>98365</v>
@@ -2970,10 +2967,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576949</v>
+        <v>576950</v>
       </c>
       <c r="R22" t="n">
-        <v>6379790</v>
+        <v>6379824</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3033,10 +3030,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123259209</v>
+        <v>123259183</v>
       </c>
       <c r="B23" t="n">
-        <v>90952</v>
+        <v>92233</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3045,25 +3042,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3073,7 +3070,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -3084,10 +3081,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576992</v>
+        <v>577000</v>
       </c>
       <c r="R23" t="n">
-        <v>6379660</v>
+        <v>6379640</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3147,10 +3144,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123259993</v>
+        <v>123259460</v>
       </c>
       <c r="B24" t="n">
-        <v>90972</v>
+        <v>92233</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3159,32 +3156,28 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -3198,10 +3191,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>576929</v>
+        <v>576977</v>
       </c>
       <c r="R24" t="n">
-        <v>6379832</v>
+        <v>6379694</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3261,7 +3254,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123260011</v>
+        <v>123259851</v>
       </c>
       <c r="B25" t="n">
         <v>90952</v>
@@ -3312,10 +3305,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>576847</v>
+        <v>576835</v>
       </c>
       <c r="R25" t="n">
-        <v>6379709</v>
+        <v>6379715</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3375,7 +3368,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123259362</v>
+        <v>123259312</v>
       </c>
       <c r="B26" t="n">
         <v>98365</v>
@@ -3423,10 +3416,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>576989</v>
+        <v>576990</v>
       </c>
       <c r="R26" t="n">
-        <v>6379691</v>
+        <v>6379697</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3486,10 +3479,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123259460</v>
+        <v>123259440</v>
       </c>
       <c r="B27" t="n">
-        <v>92233</v>
+        <v>98365</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3498,34 +3491,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3533,10 +3527,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>576977</v>
+        <v>576980</v>
       </c>
       <c r="R27" t="n">
-        <v>6379694</v>
+        <v>6379697</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3596,10 +3590,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123259628</v>
+        <v>123260011</v>
       </c>
       <c r="B28" t="n">
-        <v>57848</v>
+        <v>90952</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3608,25 +3602,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3634,27 +3628,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>A11444, Grönlid, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>576883</v>
+        <v>576847</v>
       </c>
       <c r="R28" t="n">
-        <v>6379747</v>
+        <v>6379709</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3692,6 +3685,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3710,10 +3704,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123259271</v>
+        <v>123259910</v>
       </c>
       <c r="B29" t="n">
-        <v>98365</v>
+        <v>91362</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3722,46 +3716,49 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>A 11444. Grönlid, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>576994</v>
+        <v>576891</v>
       </c>
       <c r="R29" t="n">
-        <v>6379690</v>
+        <v>6379777</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3821,10 +3818,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123259974</v>
+        <v>123259084</v>
       </c>
       <c r="B30" t="n">
-        <v>98365</v>
+        <v>92261</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3833,46 +3830,49 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444, Grönled, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>576950</v>
+        <v>577012</v>
       </c>
       <c r="R30" t="n">
-        <v>6379824</v>
+        <v>6379533</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 11444-2025 artfynd.xlsx
+++ b/artfynd/A 11444-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123259882</v>
+        <v>123259460</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>92233</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576832</v>
+        <v>576977</v>
       </c>
       <c r="R2" t="n">
-        <v>6379712</v>
+        <v>6379694</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,17 +760,13 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Bearbetat torrträd</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123259362</v>
+        <v>123259131</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>92233</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,35 +797,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576989</v>
+        <v>577009</v>
       </c>
       <c r="R3" t="n">
-        <v>6379691</v>
+        <v>6379596</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123259131</v>
+        <v>123259554</v>
       </c>
       <c r="B4" t="n">
-        <v>92233</v>
+        <v>105471</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,34 +915,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -952,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577009</v>
+        <v>576891</v>
       </c>
       <c r="R4" t="n">
-        <v>6379596</v>
+        <v>6379769</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123259930</v>
+        <v>123259882</v>
       </c>
       <c r="B5" t="n">
-        <v>98365</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,35 +1022,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1063,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576949</v>
+        <v>576832</v>
       </c>
       <c r="R5" t="n">
-        <v>6379790</v>
+        <v>6379712</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,13 +1096,17 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bearbetat torrträd</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1126,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123259392</v>
+        <v>123259828</v>
       </c>
       <c r="B6" t="n">
-        <v>98365</v>
+        <v>90952</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,35 +1137,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1174,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576988</v>
+        <v>576838</v>
       </c>
       <c r="R6" t="n">
-        <v>6379698</v>
+        <v>6379654</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123259498</v>
+        <v>123259157</v>
       </c>
       <c r="B7" t="n">
-        <v>95136</v>
+        <v>57631</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1249,31 +1251,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1281,13 +1291,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576965</v>
+        <v>576997</v>
       </c>
       <c r="R7" t="n">
-        <v>6379700</v>
+        <v>6379617</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1325,7 +1335,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1344,10 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123259271</v>
+        <v>123259209</v>
       </c>
       <c r="B8" t="n">
-        <v>98365</v>
+        <v>90952</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,46 +1365,49 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 11444. Grönlid, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576994</v>
+        <v>576992</v>
       </c>
       <c r="R8" t="n">
-        <v>6379690</v>
+        <v>6379660</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,10 +1467,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123259157</v>
+        <v>123259948</v>
       </c>
       <c r="B9" t="n">
-        <v>57631</v>
+        <v>98365</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1467,39 +1479,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1507,13 +1515,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576997</v>
+        <v>576939</v>
       </c>
       <c r="R9" t="n">
-        <v>6379617</v>
+        <v>6379798</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1551,6 +1559,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1569,10 +1578,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123259554</v>
+        <v>123259111</v>
       </c>
       <c r="B10" t="n">
-        <v>105471</v>
+        <v>92233</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1585,31 +1594,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1617,10 +1629,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576891</v>
+        <v>577001</v>
       </c>
       <c r="R10" t="n">
-        <v>6379769</v>
+        <v>6379581</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,7 +1692,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123259332</v>
+        <v>123260939</v>
       </c>
       <c r="B11" t="n">
         <v>98365</v>
@@ -1728,10 +1740,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576987</v>
+        <v>576951</v>
       </c>
       <c r="R11" t="n">
-        <v>6379692</v>
+        <v>6379805</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,10 +1803,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123259993</v>
+        <v>123259974</v>
       </c>
       <c r="B12" t="n">
-        <v>90972</v>
+        <v>98365</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1803,38 +1815,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1842,10 +1851,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576929</v>
+        <v>576950</v>
       </c>
       <c r="R12" t="n">
-        <v>6379832</v>
+        <v>6379824</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1905,7 +1914,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123260939</v>
+        <v>123259930</v>
       </c>
       <c r="B13" t="n">
         <v>98365</v>
@@ -1953,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576951</v>
+        <v>576949</v>
       </c>
       <c r="R13" t="n">
-        <v>6379805</v>
+        <v>6379790</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2016,10 +2025,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123259471</v>
+        <v>123260011</v>
       </c>
       <c r="B14" t="n">
-        <v>98365</v>
+        <v>90952</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2028,46 +2037,49 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 11444, Grönlif, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576971</v>
+        <v>576847</v>
       </c>
       <c r="R14" t="n">
-        <v>6379688</v>
+        <v>6379709</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2127,7 +2139,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123259522</v>
+        <v>123259332</v>
       </c>
       <c r="B15" t="n">
         <v>98365</v>
@@ -2175,10 +2187,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576971</v>
+        <v>576987</v>
       </c>
       <c r="R15" t="n">
-        <v>6379715</v>
+        <v>6379692</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2238,10 +2250,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123259628</v>
+        <v>123259910</v>
       </c>
       <c r="B16" t="n">
-        <v>57848</v>
+        <v>91362</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2254,21 +2266,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>5420</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2276,27 +2288,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A11444, Grönlid, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576883</v>
+        <v>576891</v>
       </c>
       <c r="R16" t="n">
-        <v>6379747</v>
+        <v>6379777</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2334,6 +2345,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2352,10 +2364,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123259419</v>
+        <v>123259993</v>
       </c>
       <c r="B17" t="n">
-        <v>57631</v>
+        <v>90972</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2368,21 +2380,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2390,27 +2402,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A 11444, Grönlif, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576985</v>
+        <v>576929</v>
       </c>
       <c r="R17" t="n">
-        <v>6379714</v>
+        <v>6379832</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2448,6 +2459,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2466,7 +2478,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123259948</v>
+        <v>123259392</v>
       </c>
       <c r="B18" t="n">
         <v>98365</v>
@@ -2514,10 +2526,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576939</v>
+        <v>576988</v>
       </c>
       <c r="R18" t="n">
-        <v>6379798</v>
+        <v>6379698</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2577,10 +2589,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123259828</v>
+        <v>123259628</v>
       </c>
       <c r="B19" t="n">
-        <v>90952</v>
+        <v>57848</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2589,25 +2601,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2615,26 +2627,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576838</v>
+        <v>576883</v>
       </c>
       <c r="R19" t="n">
-        <v>6379654</v>
+        <v>6379747</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2672,7 +2685,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2691,10 +2703,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123259209</v>
+        <v>123259522</v>
       </c>
       <c r="B20" t="n">
-        <v>90952</v>
+        <v>98365</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2703,38 +2715,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2742,10 +2751,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576992</v>
+        <v>576971</v>
       </c>
       <c r="R20" t="n">
-        <v>6379660</v>
+        <v>6379715</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2805,10 +2814,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123259111</v>
+        <v>123259498</v>
       </c>
       <c r="B21" t="n">
-        <v>92233</v>
+        <v>95136</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2821,34 +2830,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2856,10 +2858,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577001</v>
+        <v>576965</v>
       </c>
       <c r="R21" t="n">
-        <v>6379581</v>
+        <v>6379700</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2919,7 +2921,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123259974</v>
+        <v>123259440</v>
       </c>
       <c r="B22" t="n">
         <v>98365</v>
@@ -2967,10 +2969,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576950</v>
+        <v>576980</v>
       </c>
       <c r="R22" t="n">
-        <v>6379824</v>
+        <v>6379697</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3030,10 +3032,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123259183</v>
+        <v>123259419</v>
       </c>
       <c r="B23" t="n">
-        <v>92233</v>
+        <v>57631</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3042,25 +3044,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3068,26 +3070,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444, Grönlif, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577000</v>
+        <v>576985</v>
       </c>
       <c r="R23" t="n">
-        <v>6379640</v>
+        <v>6379714</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3125,7 +3128,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3144,10 +3146,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123259460</v>
+        <v>123259271</v>
       </c>
       <c r="B24" t="n">
-        <v>92233</v>
+        <v>98365</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3156,45 +3158,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444. Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>576977</v>
+        <v>576994</v>
       </c>
       <c r="R24" t="n">
-        <v>6379694</v>
+        <v>6379690</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3254,10 +3257,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123259851</v>
+        <v>123259183</v>
       </c>
       <c r="B25" t="n">
-        <v>90952</v>
+        <v>92233</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3266,25 +3269,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3294,7 +3297,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -3305,10 +3308,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>576835</v>
+        <v>577000</v>
       </c>
       <c r="R25" t="n">
-        <v>6379715</v>
+        <v>6379640</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3368,10 +3371,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123259312</v>
+        <v>123259851</v>
       </c>
       <c r="B26" t="n">
-        <v>98365</v>
+        <v>90952</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3380,35 +3383,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3416,10 +3422,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>576990</v>
+        <v>576835</v>
       </c>
       <c r="R26" t="n">
-        <v>6379697</v>
+        <v>6379715</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3479,10 +3485,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123259440</v>
+        <v>123259084</v>
       </c>
       <c r="B27" t="n">
-        <v>98365</v>
+        <v>92261</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3491,46 +3497,49 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444, Grönled, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>576980</v>
+        <v>577012</v>
       </c>
       <c r="R27" t="n">
-        <v>6379697</v>
+        <v>6379533</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3590,10 +3599,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123260011</v>
+        <v>123259362</v>
       </c>
       <c r="B28" t="n">
-        <v>90952</v>
+        <v>98365</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3602,38 +3611,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3641,10 +3647,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>576847</v>
+        <v>576989</v>
       </c>
       <c r="R28" t="n">
-        <v>6379709</v>
+        <v>6379691</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3704,10 +3710,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123259910</v>
+        <v>123259312</v>
       </c>
       <c r="B29" t="n">
-        <v>91362</v>
+        <v>98365</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3716,38 +3722,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3755,10 +3758,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>576891</v>
+        <v>576990</v>
       </c>
       <c r="R29" t="n">
-        <v>6379777</v>
+        <v>6379697</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3818,10 +3821,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123259084</v>
+        <v>123259471</v>
       </c>
       <c r="B30" t="n">
-        <v>92261</v>
+        <v>98365</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3830,49 +3833,46 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>A 11444, Grönled, Sm</t>
+          <t>A 11444, Grönlif, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577012</v>
+        <v>576971</v>
       </c>
       <c r="R30" t="n">
-        <v>6379533</v>
+        <v>6379688</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3929,6 +3929,2296 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>123312540</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57848</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>A 11444, Grönlid, Sm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>576808</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6379847</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>123313067</v>
+      </c>
+      <c r="B32" t="n">
+        <v>90972</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>A 11444, Grönlid, Sm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>576682</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6379963</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>123312896</v>
+      </c>
+      <c r="B33" t="n">
+        <v>105471</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>A 11444, Grönlid, Sm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>576804</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6379845</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>123312904</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>A 11444, Grönlid, Sm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>576804</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6379845</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>123312921</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>A 11444, Grönlid, Sm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>576799</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6379827</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>123312773</v>
+      </c>
+      <c r="B36" t="n">
+        <v>105471</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>A 11444, Grönlid, Sm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>576839</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6379721</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>123312993</v>
+      </c>
+      <c r="B37" t="n">
+        <v>90972</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>A 11444, Grönlid, Sm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>576745</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6379872</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>123312486</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57848</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>A 11444, Grönlid, Sm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>576693</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6379898</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>123313080</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>A 11444, Grönlid, Sm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>576640</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6379941</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>123312753</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>A 11444, Grönlid, Sm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>576835</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6379711</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>123313044</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91362</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>A 11444, Grönlid, Sm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>576690</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6379955</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>123312502</v>
+      </c>
+      <c r="B42" t="n">
+        <v>95136</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>A 11444, Grönlid, Sm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>576740</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6379855</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>123313124</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>A 11444, Grönlid, Sm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>576507</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6379922</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>123312935</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>A 11444, Grönlid, Sm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>576793</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6379822</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>123313052</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91362</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>A 11444, Grönlid, Sm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>576677</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6379959</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>123313086</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57848</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>A 11444, Grönlid, Sm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>576640</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6379941</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>123312569</v>
+      </c>
+      <c r="B47" t="n">
+        <v>105471</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>A 11444, Grönlid, Sm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>576803</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6379887</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>123312958</v>
+      </c>
+      <c r="B48" t="n">
+        <v>105471</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>A 11444, Grönlid, Sm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>576745</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6379872</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>123312808</v>
+      </c>
+      <c r="B49" t="n">
+        <v>97319</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>A 11444, Grönlid, Sm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>576804</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6379891</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>123312524</v>
+      </c>
+      <c r="B50" t="n">
+        <v>92233</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>A 11444, Grönlid, Sm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>576731</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6379842</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11444-2025 artfynd.xlsx
+++ b/artfynd/A 11444-2025 artfynd.xlsx
@@ -1803,10 +1803,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123259974</v>
+        <v>123260011</v>
       </c>
       <c r="B12" t="n">
-        <v>98365</v>
+        <v>90952</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1815,35 +1815,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1851,10 +1854,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576950</v>
+        <v>576847</v>
       </c>
       <c r="R12" t="n">
-        <v>6379824</v>
+        <v>6379709</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1914,7 +1917,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123259930</v>
+        <v>123259974</v>
       </c>
       <c r="B13" t="n">
         <v>98365</v>
@@ -1962,10 +1965,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576949</v>
+        <v>576950</v>
       </c>
       <c r="R13" t="n">
-        <v>6379790</v>
+        <v>6379824</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2025,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123260011</v>
+        <v>123259930</v>
       </c>
       <c r="B14" t="n">
-        <v>90952</v>
+        <v>98365</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2037,38 +2040,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576847</v>
+        <v>576949</v>
       </c>
       <c r="R14" t="n">
-        <v>6379709</v>
+        <v>6379790</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2139,10 +2139,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123259332</v>
+        <v>123259910</v>
       </c>
       <c r="B15" t="n">
-        <v>98365</v>
+        <v>91362</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2151,35 +2151,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2187,10 +2190,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576987</v>
+        <v>576891</v>
       </c>
       <c r="R15" t="n">
-        <v>6379692</v>
+        <v>6379777</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2250,10 +2253,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123259910</v>
+        <v>123259993</v>
       </c>
       <c r="B16" t="n">
-        <v>91362</v>
+        <v>90972</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2262,25 +2265,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5420</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2301,10 +2304,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576891</v>
+        <v>576929</v>
       </c>
       <c r="R16" t="n">
-        <v>6379777</v>
+        <v>6379832</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2364,10 +2367,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123259993</v>
+        <v>123259332</v>
       </c>
       <c r="B17" t="n">
-        <v>90972</v>
+        <v>98365</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2376,38 +2379,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2415,10 +2415,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576929</v>
+        <v>576987</v>
       </c>
       <c r="R17" t="n">
-        <v>6379832</v>
+        <v>6379692</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 11444-2025 artfynd.xlsx
+++ b/artfynd/A 11444-2025 artfynd.xlsx
@@ -2139,10 +2139,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123259910</v>
+        <v>123259332</v>
       </c>
       <c r="B15" t="n">
-        <v>91362</v>
+        <v>98365</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2151,38 +2151,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2190,10 +2187,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576891</v>
+        <v>576987</v>
       </c>
       <c r="R15" t="n">
-        <v>6379777</v>
+        <v>6379692</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2253,10 +2250,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123259993</v>
+        <v>123259910</v>
       </c>
       <c r="B16" t="n">
-        <v>90972</v>
+        <v>91362</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2265,25 +2262,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2304,10 +2301,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576929</v>
+        <v>576891</v>
       </c>
       <c r="R16" t="n">
-        <v>6379832</v>
+        <v>6379777</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2367,10 +2364,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123259332</v>
+        <v>123259993</v>
       </c>
       <c r="B17" t="n">
-        <v>98365</v>
+        <v>90972</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2379,35 +2376,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2415,10 +2415,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576987</v>
+        <v>576929</v>
       </c>
       <c r="R17" t="n">
-        <v>6379692</v>
+        <v>6379832</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -5070,10 +5070,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123313044</v>
+        <v>123312502</v>
       </c>
       <c r="B41" t="n">
-        <v>91362</v>
+        <v>95136</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5086,34 +5086,27 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5420</v>
+        <v>2180</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5121,10 +5114,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>576690</v>
+        <v>576740</v>
       </c>
       <c r="R41" t="n">
-        <v>6379955</v>
+        <v>6379855</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5154,9 +5147,19 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5184,10 +5187,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123312502</v>
+        <v>123313044</v>
       </c>
       <c r="B42" t="n">
-        <v>95136</v>
+        <v>91362</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5200,27 +5203,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2180</v>
+        <v>5420</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5228,10 +5238,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>576740</v>
+        <v>576690</v>
       </c>
       <c r="R42" t="n">
-        <v>6379855</v>
+        <v>6379955</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5261,19 +5271,9 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>15:50</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 11444-2025 artfynd.xlsx
+++ b/artfynd/A 11444-2025 artfynd.xlsx
@@ -5070,10 +5070,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123312502</v>
+        <v>123313044</v>
       </c>
       <c r="B41" t="n">
-        <v>95136</v>
+        <v>91362</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5086,27 +5086,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2180</v>
+        <v>5420</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5114,10 +5121,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>576740</v>
+        <v>576690</v>
       </c>
       <c r="R41" t="n">
-        <v>6379855</v>
+        <v>6379955</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5147,19 +5154,9 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>15:50</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5187,10 +5184,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123313044</v>
+        <v>123312502</v>
       </c>
       <c r="B42" t="n">
-        <v>91362</v>
+        <v>95136</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5203,34 +5200,27 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5420</v>
+        <v>2180</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5238,10 +5228,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>576690</v>
+        <v>576740</v>
       </c>
       <c r="R42" t="n">
-        <v>6379955</v>
+        <v>6379855</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5271,9 +5261,19 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 11444-2025 artfynd.xlsx
+++ b/artfynd/A 11444-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123259460</v>
+        <v>123259948</v>
       </c>
       <c r="B2" t="n">
-        <v>92233</v>
+        <v>98368</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576977</v>
+        <v>576939</v>
       </c>
       <c r="R2" t="n">
-        <v>6379694</v>
+        <v>6379798</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123259131</v>
+        <v>123259471</v>
       </c>
       <c r="B3" t="n">
-        <v>92233</v>
+        <v>98368</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,49 +798,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444, Grönlif, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577009</v>
+        <v>576971</v>
       </c>
       <c r="R3" t="n">
-        <v>6379596</v>
+        <v>6379688</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123259554</v>
+        <v>123259183</v>
       </c>
       <c r="B4" t="n">
-        <v>105471</v>
+        <v>92236</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,31 +913,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -947,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576891</v>
+        <v>577000</v>
       </c>
       <c r="R4" t="n">
-        <v>6379769</v>
+        <v>6379640</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123259882</v>
+        <v>123259111</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>92236</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,35 +1023,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1058,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576832</v>
+        <v>577001</v>
       </c>
       <c r="R5" t="n">
-        <v>6379712</v>
+        <v>6379581</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,17 +1100,13 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Bearbetat torrträd</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1125,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123259828</v>
+        <v>123259554</v>
       </c>
       <c r="B6" t="n">
-        <v>90952</v>
+        <v>105474</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,38 +1137,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1176,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576838</v>
+        <v>576891</v>
       </c>
       <c r="R6" t="n">
-        <v>6379654</v>
+        <v>6379769</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1239,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123259157</v>
+        <v>123259930</v>
       </c>
       <c r="B7" t="n">
-        <v>57631</v>
+        <v>98368</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,39 +1248,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1291,13 +1284,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576997</v>
+        <v>576949</v>
       </c>
       <c r="R7" t="n">
-        <v>6379617</v>
+        <v>6379790</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1335,6 +1328,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1353,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123259209</v>
+        <v>123259362</v>
       </c>
       <c r="B8" t="n">
-        <v>90952</v>
+        <v>98368</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1365,38 +1359,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1404,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576992</v>
+        <v>576989</v>
       </c>
       <c r="R8" t="n">
-        <v>6379660</v>
+        <v>6379691</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1467,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123259948</v>
+        <v>123259522</v>
       </c>
       <c r="B9" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1515,10 +1506,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576939</v>
+        <v>576971</v>
       </c>
       <c r="R9" t="n">
-        <v>6379798</v>
+        <v>6379715</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1578,10 +1569,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123259111</v>
+        <v>123259312</v>
       </c>
       <c r="B10" t="n">
-        <v>92233</v>
+        <v>98368</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1590,38 +1581,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1629,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577001</v>
+        <v>576990</v>
       </c>
       <c r="R10" t="n">
-        <v>6379581</v>
+        <v>6379697</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1692,10 +1680,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123260939</v>
+        <v>123259392</v>
       </c>
       <c r="B11" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1740,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576951</v>
+        <v>576988</v>
       </c>
       <c r="R11" t="n">
-        <v>6379805</v>
+        <v>6379698</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1803,10 +1791,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123260011</v>
+        <v>123259209</v>
       </c>
       <c r="B12" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,10 +1842,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576847</v>
+        <v>576992</v>
       </c>
       <c r="R12" t="n">
-        <v>6379709</v>
+        <v>6379660</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1917,10 +1905,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123259974</v>
+        <v>123259419</v>
       </c>
       <c r="B13" t="n">
-        <v>98365</v>
+        <v>57634</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1929,49 +1917,53 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444, Grönlif, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576950</v>
+        <v>576985</v>
       </c>
       <c r="R13" t="n">
-        <v>6379824</v>
+        <v>6379714</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2009,7 +2001,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2028,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123259930</v>
+        <v>123259440</v>
       </c>
       <c r="B14" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2076,10 +2067,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576949</v>
+        <v>576980</v>
       </c>
       <c r="R14" t="n">
-        <v>6379790</v>
+        <v>6379697</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2139,10 +2130,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123259332</v>
+        <v>123259498</v>
       </c>
       <c r="B15" t="n">
-        <v>98365</v>
+        <v>95139</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2151,33 +2142,29 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -2187,10 +2174,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576987</v>
+        <v>576965</v>
       </c>
       <c r="R15" t="n">
-        <v>6379692</v>
+        <v>6379700</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2250,10 +2237,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123259910</v>
+        <v>123260011</v>
       </c>
       <c r="B16" t="n">
-        <v>91362</v>
+        <v>90955</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2262,25 +2249,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5420</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2290,7 +2277,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -2301,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576891</v>
+        <v>576847</v>
       </c>
       <c r="R16" t="n">
-        <v>6379777</v>
+        <v>6379709</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2364,10 +2351,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123259993</v>
+        <v>123259084</v>
       </c>
       <c r="B17" t="n">
-        <v>90972</v>
+        <v>92264</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2380,26 +2367,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>5449</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2411,14 +2398,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444, Grönled, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576929</v>
+        <v>577012</v>
       </c>
       <c r="R17" t="n">
-        <v>6379832</v>
+        <v>6379533</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2478,10 +2465,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123259392</v>
+        <v>123259157</v>
       </c>
       <c r="B18" t="n">
-        <v>98365</v>
+        <v>57634</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2490,35 +2477,39 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2526,13 +2517,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576988</v>
+        <v>576997</v>
       </c>
       <c r="R18" t="n">
-        <v>6379698</v>
+        <v>6379617</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2570,7 +2561,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2589,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123259628</v>
+        <v>123260939</v>
       </c>
       <c r="B19" t="n">
-        <v>57848</v>
+        <v>98368</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2601,53 +2591,49 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>A11444, Grönlid, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576883</v>
+        <v>576951</v>
       </c>
       <c r="R19" t="n">
-        <v>6379747</v>
+        <v>6379805</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2685,6 +2671,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2703,10 +2690,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123259522</v>
+        <v>123259271</v>
       </c>
       <c r="B20" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2747,14 +2734,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444. Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576971</v>
+        <v>576994</v>
       </c>
       <c r="R20" t="n">
-        <v>6379715</v>
+        <v>6379690</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2814,10 +2801,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123259498</v>
+        <v>123259851</v>
       </c>
       <c r="B21" t="n">
-        <v>95136</v>
+        <v>90955</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2826,31 +2813,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2858,10 +2852,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>576965</v>
+        <v>576835</v>
       </c>
       <c r="R21" t="n">
-        <v>6379700</v>
+        <v>6379715</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2921,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123259440</v>
+        <v>123259974</v>
       </c>
       <c r="B22" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2969,10 +2963,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576980</v>
+        <v>576950</v>
       </c>
       <c r="R22" t="n">
-        <v>6379697</v>
+        <v>6379824</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3032,10 +3026,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123259419</v>
+        <v>123259628</v>
       </c>
       <c r="B23" t="n">
-        <v>57631</v>
+        <v>57851</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3044,25 +3038,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3074,20 +3068,20 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>A 11444, Grönlif, Sm</t>
+          <t>A11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576985</v>
+        <v>576883</v>
       </c>
       <c r="R23" t="n">
-        <v>6379714</v>
+        <v>6379747</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3146,10 +3140,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123259271</v>
+        <v>123259828</v>
       </c>
       <c r="B24" t="n">
-        <v>98365</v>
+        <v>90955</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3158,46 +3152,49 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>A 11444. Grönlid, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>576994</v>
+        <v>576838</v>
       </c>
       <c r="R24" t="n">
-        <v>6379690</v>
+        <v>6379654</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3257,10 +3254,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123259183</v>
+        <v>123259882</v>
       </c>
       <c r="B25" t="n">
-        <v>92233</v>
+        <v>57497</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3269,38 +3266,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3308,10 +3302,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577000</v>
+        <v>576832</v>
       </c>
       <c r="R25" t="n">
-        <v>6379640</v>
+        <v>6379712</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3346,13 +3340,17 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Bearbetat torrträd</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3371,10 +3369,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123259851</v>
+        <v>123259460</v>
       </c>
       <c r="B26" t="n">
-        <v>90952</v>
+        <v>92236</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3383,35 +3381,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -3422,10 +3416,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>576835</v>
+        <v>576977</v>
       </c>
       <c r="R26" t="n">
-        <v>6379715</v>
+        <v>6379694</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3485,10 +3479,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123259084</v>
+        <v>123259332</v>
       </c>
       <c r="B27" t="n">
-        <v>92261</v>
+        <v>98368</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3497,49 +3491,46 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>A 11444, Grönled, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577012</v>
+        <v>576987</v>
       </c>
       <c r="R27" t="n">
-        <v>6379533</v>
+        <v>6379692</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3599,10 +3590,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123259362</v>
+        <v>123259910</v>
       </c>
       <c r="B28" t="n">
-        <v>98365</v>
+        <v>91365</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3611,35 +3602,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3647,10 +3641,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>576989</v>
+        <v>576891</v>
       </c>
       <c r="R28" t="n">
-        <v>6379691</v>
+        <v>6379777</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3710,10 +3704,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123259312</v>
+        <v>123259131</v>
       </c>
       <c r="B29" t="n">
-        <v>98365</v>
+        <v>92236</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3722,35 +3716,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3758,10 +3755,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>576990</v>
+        <v>577009</v>
       </c>
       <c r="R29" t="n">
-        <v>6379697</v>
+        <v>6379596</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3821,10 +3818,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123259471</v>
+        <v>123259993</v>
       </c>
       <c r="B30" t="n">
-        <v>98365</v>
+        <v>90975</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3833,46 +3830,49 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>A 11444, Grönlif, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>576971</v>
+        <v>576929</v>
       </c>
       <c r="R30" t="n">
-        <v>6379688</v>
+        <v>6379832</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3932,10 +3932,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123312540</v>
+        <v>123312502</v>
       </c>
       <c r="B31" t="n">
-        <v>57848</v>
+        <v>95139</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3948,35 +3948,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3984,13 +3976,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>576808</v>
+        <v>576740</v>
       </c>
       <c r="R31" t="n">
-        <v>6379847</v>
+        <v>6379855</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4038,6 +4030,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4056,10 +4049,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123313067</v>
+        <v>123312753</v>
       </c>
       <c r="B32" t="n">
-        <v>90972</v>
+        <v>98368</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4068,38 +4061,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4107,10 +4097,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>576682</v>
+        <v>576835</v>
       </c>
       <c r="R32" t="n">
-        <v>6379963</v>
+        <v>6379711</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4170,10 +4160,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123312896</v>
+        <v>123312524</v>
       </c>
       <c r="B33" t="n">
-        <v>105471</v>
+        <v>92236</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4186,31 +4176,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4218,10 +4211,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>576804</v>
+        <v>576731</v>
       </c>
       <c r="R33" t="n">
-        <v>6379845</v>
+        <v>6379842</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4251,9 +4244,19 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4281,10 +4284,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123312904</v>
+        <v>123313086</v>
       </c>
       <c r="B34" t="n">
-        <v>98365</v>
+        <v>57851</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4293,35 +4296,39 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4329,10 +4336,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>576804</v>
+        <v>576640</v>
       </c>
       <c r="R34" t="n">
-        <v>6379845</v>
+        <v>6379941</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4373,7 +4380,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4392,10 +4398,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123312921</v>
+        <v>123312486</v>
       </c>
       <c r="B35" t="n">
-        <v>98365</v>
+        <v>57851</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4404,35 +4410,39 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4440,13 +4450,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>576799</v>
+        <v>576693</v>
       </c>
       <c r="R35" t="n">
-        <v>6379827</v>
+        <v>6379898</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4473,18 +4483,27 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4503,10 +4522,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123312773</v>
+        <v>123312904</v>
       </c>
       <c r="B36" t="n">
-        <v>105471</v>
+        <v>98368</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4515,25 +4534,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4551,10 +4570,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>576839</v>
+        <v>576804</v>
       </c>
       <c r="R36" t="n">
-        <v>6379721</v>
+        <v>6379845</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4614,10 +4633,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123312993</v>
+        <v>123312808</v>
       </c>
       <c r="B37" t="n">
-        <v>90972</v>
+        <v>97322</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4626,38 +4645,39 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5442</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4665,10 +4685,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>576745</v>
+        <v>576804</v>
       </c>
       <c r="R37" t="n">
-        <v>6379872</v>
+        <v>6379891</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4728,10 +4748,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123312486</v>
+        <v>123312896</v>
       </c>
       <c r="B38" t="n">
-        <v>57848</v>
+        <v>105474</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4744,35 +4764,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4780,13 +4796,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>576693</v>
+        <v>576804</v>
       </c>
       <c r="R38" t="n">
-        <v>6379898</v>
+        <v>6379845</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4813,27 +4829,18 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4852,10 +4859,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123313080</v>
+        <v>123312540</v>
       </c>
       <c r="B39" t="n">
-        <v>98365</v>
+        <v>57851</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4864,31 +4871,39 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4896,13 +4911,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>576640</v>
+        <v>576808</v>
       </c>
       <c r="R39" t="n">
-        <v>6379941</v>
+        <v>6379847</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4929,18 +4944,27 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4959,10 +4983,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123312753</v>
+        <v>123313124</v>
       </c>
       <c r="B40" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5007,10 +5031,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>576835</v>
+        <v>576507</v>
       </c>
       <c r="R40" t="n">
-        <v>6379711</v>
+        <v>6379922</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5070,10 +5094,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123313044</v>
+        <v>123312569</v>
       </c>
       <c r="B41" t="n">
-        <v>91362</v>
+        <v>105474</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5086,34 +5110,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5420</v>
+        <v>221144</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5121,10 +5142,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>576690</v>
+        <v>576803</v>
       </c>
       <c r="R41" t="n">
-        <v>6379955</v>
+        <v>6379887</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5154,9 +5175,19 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5184,10 +5215,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123312502</v>
+        <v>123313080</v>
       </c>
       <c r="B42" t="n">
-        <v>95136</v>
+        <v>98368</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5196,25 +5227,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5228,10 +5259,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>576740</v>
+        <v>576640</v>
       </c>
       <c r="R42" t="n">
-        <v>6379855</v>
+        <v>6379941</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5261,19 +5292,9 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>15:50</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5301,10 +5322,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123313124</v>
+        <v>123313052</v>
       </c>
       <c r="B43" t="n">
-        <v>98365</v>
+        <v>91365</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5313,35 +5334,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5349,10 +5373,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>576507</v>
+        <v>576677</v>
       </c>
       <c r="R43" t="n">
-        <v>6379922</v>
+        <v>6379959</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5412,10 +5436,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123312935</v>
+        <v>123312921</v>
       </c>
       <c r="B44" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5460,10 +5484,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>576793</v>
+        <v>576799</v>
       </c>
       <c r="R44" t="n">
-        <v>6379822</v>
+        <v>6379827</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5523,10 +5547,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123313052</v>
+        <v>123312935</v>
       </c>
       <c r="B45" t="n">
-        <v>91362</v>
+        <v>98368</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5535,38 +5559,35 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5574,10 +5595,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>576677</v>
+        <v>576793</v>
       </c>
       <c r="R45" t="n">
-        <v>6379959</v>
+        <v>6379822</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5637,10 +5658,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123313086</v>
+        <v>123312773</v>
       </c>
       <c r="B46" t="n">
-        <v>57848</v>
+        <v>105474</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5653,35 +5674,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5689,10 +5706,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>576640</v>
+        <v>576839</v>
       </c>
       <c r="R46" t="n">
-        <v>6379941</v>
+        <v>6379721</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5733,6 +5750,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5751,10 +5769,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123312569</v>
+        <v>123312958</v>
       </c>
       <c r="B47" t="n">
-        <v>105471</v>
+        <v>105474</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5799,10 +5817,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>576803</v>
+        <v>576745</v>
       </c>
       <c r="R47" t="n">
-        <v>6379887</v>
+        <v>6379872</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5832,19 +5850,9 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>15:50</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5865,17 +5873,17 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+          <t>Per Muhr, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123312958</v>
+        <v>123313044</v>
       </c>
       <c r="B48" t="n">
-        <v>105471</v>
+        <v>91365</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5888,31 +5896,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221144</v>
+        <v>5420</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5920,10 +5931,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>576745</v>
+        <v>576690</v>
       </c>
       <c r="R48" t="n">
-        <v>6379872</v>
+        <v>6379955</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5983,10 +5994,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123312808</v>
+        <v>123312993</v>
       </c>
       <c r="B49" t="n">
-        <v>97319</v>
+        <v>90975</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5995,39 +6006,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221945</v>
+        <v>5442</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6035,10 +6045,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>576804</v>
+        <v>576745</v>
       </c>
       <c r="R49" t="n">
-        <v>6379891</v>
+        <v>6379872</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6098,10 +6108,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123312524</v>
+        <v>123313067</v>
       </c>
       <c r="B50" t="n">
-        <v>92233</v>
+        <v>90975</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6110,25 +6120,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -6149,10 +6159,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>576731</v>
+        <v>576682</v>
       </c>
       <c r="R50" t="n">
-        <v>6379842</v>
+        <v>6379963</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6182,19 +6192,9 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>15:50</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 11444-2025 artfynd.xlsx
+++ b/artfynd/A 11444-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123259948</v>
+        <v>123259332</v>
       </c>
       <c r="B2" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576939</v>
+        <v>576987</v>
       </c>
       <c r="R2" t="n">
-        <v>6379798</v>
+        <v>6379692</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123259471</v>
+        <v>123259882</v>
       </c>
       <c r="B3" t="n">
-        <v>98368</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,46 +798,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 11444, Grönlif, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576971</v>
+        <v>576832</v>
       </c>
       <c r="R3" t="n">
-        <v>6379688</v>
+        <v>6379712</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,13 +872,17 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bearbetat torrträd</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -897,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123259183</v>
+        <v>123259362</v>
       </c>
       <c r="B4" t="n">
-        <v>92236</v>
+        <v>98370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,38 +913,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -948,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577000</v>
+        <v>576989</v>
       </c>
       <c r="R4" t="n">
-        <v>6379640</v>
+        <v>6379691</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123259111</v>
+        <v>123259392</v>
       </c>
       <c r="B5" t="n">
-        <v>92236</v>
+        <v>98370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,38 +1024,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1062,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577001</v>
+        <v>576988</v>
       </c>
       <c r="R5" t="n">
-        <v>6379581</v>
+        <v>6379698</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123259554</v>
+        <v>123259910</v>
       </c>
       <c r="B6" t="n">
-        <v>105474</v>
+        <v>91367</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,31 +1139,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>5420</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1176,7 +1177,7 @@
         <v>576891</v>
       </c>
       <c r="R6" t="n">
-        <v>6379769</v>
+        <v>6379777</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123259930</v>
+        <v>123259460</v>
       </c>
       <c r="B7" t="n">
-        <v>98368</v>
+        <v>92238</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,35 +1249,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576949</v>
+        <v>576977</v>
       </c>
       <c r="R7" t="n">
-        <v>6379790</v>
+        <v>6379694</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123259362</v>
+        <v>123259312</v>
       </c>
       <c r="B8" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1395,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576989</v>
+        <v>576990</v>
       </c>
       <c r="R8" t="n">
-        <v>6379691</v>
+        <v>6379697</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1458,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123259522</v>
+        <v>123259131</v>
       </c>
       <c r="B9" t="n">
-        <v>98368</v>
+        <v>92238</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,35 +1470,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1506,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576971</v>
+        <v>577009</v>
       </c>
       <c r="R9" t="n">
-        <v>6379715</v>
+        <v>6379596</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123259312</v>
+        <v>123259554</v>
       </c>
       <c r="B10" t="n">
-        <v>98368</v>
+        <v>105476</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1581,25 +1584,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1617,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576990</v>
+        <v>576891</v>
       </c>
       <c r="R10" t="n">
-        <v>6379697</v>
+        <v>6379769</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123259392</v>
+        <v>123259628</v>
       </c>
       <c r="B11" t="n">
-        <v>98368</v>
+        <v>57851</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1692,49 +1695,53 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576988</v>
+        <v>576883</v>
       </c>
       <c r="R11" t="n">
-        <v>6379698</v>
+        <v>6379747</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1772,7 +1779,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1791,10 +1797,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123259209</v>
+        <v>123259157</v>
       </c>
       <c r="B12" t="n">
-        <v>90955</v>
+        <v>57634</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,21 +1813,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1829,12 +1835,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1842,13 +1849,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576992</v>
+        <v>576997</v>
       </c>
       <c r="R12" t="n">
-        <v>6379660</v>
+        <v>6379617</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1886,7 +1893,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1905,10 +1911,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123259419</v>
+        <v>123259930</v>
       </c>
       <c r="B13" t="n">
-        <v>57634</v>
+        <v>98370</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1917,53 +1923,49 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 11444, Grönlif, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576985</v>
+        <v>576949</v>
       </c>
       <c r="R13" t="n">
-        <v>6379714</v>
+        <v>6379790</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2001,6 +2003,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2019,10 +2022,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123259440</v>
+        <v>123259271</v>
       </c>
       <c r="B14" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2063,14 +2066,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444. Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576980</v>
+        <v>576994</v>
       </c>
       <c r="R14" t="n">
-        <v>6379697</v>
+        <v>6379690</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2130,10 +2133,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123259498</v>
+        <v>123259522</v>
       </c>
       <c r="B15" t="n">
-        <v>95139</v>
+        <v>98370</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2142,29 +2145,33 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -2174,10 +2181,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576965</v>
+        <v>576971</v>
       </c>
       <c r="R15" t="n">
-        <v>6379700</v>
+        <v>6379715</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2237,10 +2244,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123260011</v>
+        <v>123259209</v>
       </c>
       <c r="B16" t="n">
-        <v>90955</v>
+        <v>90957</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2288,10 +2295,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576847</v>
+        <v>576992</v>
       </c>
       <c r="R16" t="n">
-        <v>6379709</v>
+        <v>6379660</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2351,10 +2358,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123259084</v>
+        <v>123259183</v>
       </c>
       <c r="B17" t="n">
-        <v>92264</v>
+        <v>92238</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2363,30 +2370,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2398,14 +2405,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A 11444, Grönled, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577012</v>
+        <v>577000</v>
       </c>
       <c r="R17" t="n">
-        <v>6379533</v>
+        <v>6379640</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2465,7 +2472,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123259157</v>
+        <v>123259419</v>
       </c>
       <c r="B18" t="n">
         <v>57634</v>
@@ -2507,20 +2514,20 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444, Grönlif, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576997</v>
+        <v>576985</v>
       </c>
       <c r="R18" t="n">
-        <v>6379617</v>
+        <v>6379714</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2579,10 +2586,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123260939</v>
+        <v>123259498</v>
       </c>
       <c r="B19" t="n">
-        <v>98368</v>
+        <v>95141</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2591,33 +2598,29 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2627,10 +2630,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576951</v>
+        <v>576965</v>
       </c>
       <c r="R19" t="n">
-        <v>6379805</v>
+        <v>6379700</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2690,10 +2693,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123259271</v>
+        <v>123259974</v>
       </c>
       <c r="B20" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2734,14 +2737,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>A 11444. Grönlid, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576994</v>
+        <v>576950</v>
       </c>
       <c r="R20" t="n">
-        <v>6379690</v>
+        <v>6379824</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2801,10 +2804,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123259851</v>
+        <v>123259111</v>
       </c>
       <c r="B21" t="n">
-        <v>90955</v>
+        <v>92238</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2813,35 +2816,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2852,10 +2855,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>576835</v>
+        <v>577001</v>
       </c>
       <c r="R21" t="n">
-        <v>6379715</v>
+        <v>6379581</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2915,10 +2918,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123259974</v>
+        <v>123260939</v>
       </c>
       <c r="B22" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2963,10 +2966,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576950</v>
+        <v>576951</v>
       </c>
       <c r="R22" t="n">
-        <v>6379824</v>
+        <v>6379805</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3026,10 +3029,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123259628</v>
+        <v>123260011</v>
       </c>
       <c r="B23" t="n">
-        <v>57851</v>
+        <v>90957</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3038,25 +3041,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3064,27 +3067,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>A11444, Grönlid, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576883</v>
+        <v>576847</v>
       </c>
       <c r="R23" t="n">
-        <v>6379747</v>
+        <v>6379709</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3122,6 +3124,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3140,10 +3143,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123259828</v>
+        <v>123259440</v>
       </c>
       <c r="B24" t="n">
-        <v>90955</v>
+        <v>98370</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3152,38 +3155,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3191,10 +3191,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>576838</v>
+        <v>576980</v>
       </c>
       <c r="R24" t="n">
-        <v>6379654</v>
+        <v>6379697</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3254,10 +3254,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123259882</v>
+        <v>123259993</v>
       </c>
       <c r="B25" t="n">
-        <v>57497</v>
+        <v>90977</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3270,31 +3270,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3302,10 +3305,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>576832</v>
+        <v>576929</v>
       </c>
       <c r="R25" t="n">
-        <v>6379712</v>
+        <v>6379832</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3340,17 +3343,13 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Bearbetat torrträd</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3369,10 +3368,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123259460</v>
+        <v>123259084</v>
       </c>
       <c r="B26" t="n">
-        <v>92236</v>
+        <v>92266</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3381,28 +3380,32 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -3412,14 +3415,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444, Grönled, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>576977</v>
+        <v>577012</v>
       </c>
       <c r="R26" t="n">
-        <v>6379694</v>
+        <v>6379533</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3479,10 +3482,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123259332</v>
+        <v>123259471</v>
       </c>
       <c r="B27" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3523,14 +3526,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444, Grönlif, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>576987</v>
+        <v>576971</v>
       </c>
       <c r="R27" t="n">
-        <v>6379692</v>
+        <v>6379688</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3590,10 +3593,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123259910</v>
+        <v>123259851</v>
       </c>
       <c r="B28" t="n">
-        <v>91365</v>
+        <v>90957</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3602,25 +3605,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5420</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3630,7 +3633,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -3641,10 +3644,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>576891</v>
+        <v>576835</v>
       </c>
       <c r="R28" t="n">
-        <v>6379777</v>
+        <v>6379715</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3704,10 +3707,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123259131</v>
+        <v>123259828</v>
       </c>
       <c r="B29" t="n">
-        <v>92236</v>
+        <v>90957</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3716,25 +3719,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3744,7 +3747,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -3755,10 +3758,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577009</v>
+        <v>576838</v>
       </c>
       <c r="R29" t="n">
-        <v>6379596</v>
+        <v>6379654</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3818,10 +3821,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123259993</v>
+        <v>123259948</v>
       </c>
       <c r="B30" t="n">
-        <v>90975</v>
+        <v>98370</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3830,38 +3833,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3869,10 +3869,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>576929</v>
+        <v>576939</v>
       </c>
       <c r="R30" t="n">
-        <v>6379832</v>
+        <v>6379798</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3932,10 +3932,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123312502</v>
+        <v>123312904</v>
       </c>
       <c r="B31" t="n">
-        <v>95139</v>
+        <v>98370</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3944,29 +3944,33 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
@@ -3976,10 +3980,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>576740</v>
+        <v>576804</v>
       </c>
       <c r="R31" t="n">
-        <v>6379855</v>
+        <v>6379845</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4009,19 +4013,9 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>15:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4042,17 +4036,17 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+          <t>Per Muhr, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123312753</v>
+        <v>123312773</v>
       </c>
       <c r="B32" t="n">
-        <v>98368</v>
+        <v>105476</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4061,25 +4055,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4097,10 +4091,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>576835</v>
+        <v>576839</v>
       </c>
       <c r="R32" t="n">
-        <v>6379711</v>
+        <v>6379721</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4160,10 +4154,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123312524</v>
+        <v>123313067</v>
       </c>
       <c r="B33" t="n">
-        <v>92236</v>
+        <v>90977</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4172,25 +4166,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4211,10 +4205,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>576731</v>
+        <v>576682</v>
       </c>
       <c r="R33" t="n">
-        <v>6379842</v>
+        <v>6379963</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4244,19 +4238,9 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>15:50</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4398,10 +4382,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123312486</v>
+        <v>123312753</v>
       </c>
       <c r="B35" t="n">
-        <v>57851</v>
+        <v>98370</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4410,39 +4394,35 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4450,13 +4430,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>576693</v>
+        <v>576835</v>
       </c>
       <c r="R35" t="n">
-        <v>6379898</v>
+        <v>6379711</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4483,27 +4463,18 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4522,10 +4493,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123312904</v>
+        <v>123313080</v>
       </c>
       <c r="B36" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4556,11 +4527,7 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
@@ -4570,10 +4537,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>576804</v>
+        <v>576640</v>
       </c>
       <c r="R36" t="n">
-        <v>6379845</v>
+        <v>6379941</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4633,10 +4600,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123312808</v>
+        <v>123312569</v>
       </c>
       <c r="B37" t="n">
-        <v>97322</v>
+        <v>105476</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4649,31 +4616,27 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -4685,10 +4648,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>576804</v>
+        <v>576803</v>
       </c>
       <c r="R37" t="n">
-        <v>6379891</v>
+        <v>6379887</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4718,9 +4681,19 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4748,10 +4721,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123312896</v>
+        <v>123312993</v>
       </c>
       <c r="B38" t="n">
-        <v>105474</v>
+        <v>90977</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4760,35 +4733,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4796,10 +4772,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>576804</v>
+        <v>576745</v>
       </c>
       <c r="R38" t="n">
-        <v>6379845</v>
+        <v>6379872</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4859,10 +4835,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123312540</v>
+        <v>123312921</v>
       </c>
       <c r="B39" t="n">
-        <v>57851</v>
+        <v>98370</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4871,39 +4847,35 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4911,13 +4883,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>576808</v>
+        <v>576799</v>
       </c>
       <c r="R39" t="n">
-        <v>6379847</v>
+        <v>6379827</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4944,27 +4916,18 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4976,17 +4939,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+          <t>Per Muhr, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123313124</v>
+        <v>123313052</v>
       </c>
       <c r="B40" t="n">
-        <v>98368</v>
+        <v>91367</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4995,35 +4958,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5031,10 +4997,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>576507</v>
+        <v>576677</v>
       </c>
       <c r="R40" t="n">
-        <v>6379922</v>
+        <v>6379959</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5094,10 +5060,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123312569</v>
+        <v>123312896</v>
       </c>
       <c r="B41" t="n">
-        <v>105474</v>
+        <v>105476</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5142,10 +5108,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>576803</v>
+        <v>576804</v>
       </c>
       <c r="R41" t="n">
-        <v>6379887</v>
+        <v>6379845</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5175,19 +5141,9 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>15:50</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5208,17 +5164,17 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+          <t>Per Muhr, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123313080</v>
+        <v>123313124</v>
       </c>
       <c r="B42" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5249,7 +5205,11 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
@@ -5259,10 +5219,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>576640</v>
+        <v>576507</v>
       </c>
       <c r="R42" t="n">
-        <v>6379941</v>
+        <v>6379922</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5322,10 +5282,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123313052</v>
+        <v>123312524</v>
       </c>
       <c r="B43" t="n">
-        <v>91365</v>
+        <v>92238</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5338,26 +5298,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5373,10 +5333,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>576677</v>
+        <v>576731</v>
       </c>
       <c r="R43" t="n">
-        <v>6379959</v>
+        <v>6379842</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5406,9 +5366,19 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5436,10 +5406,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123312921</v>
+        <v>123313044</v>
       </c>
       <c r="B44" t="n">
-        <v>98368</v>
+        <v>91367</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5448,35 +5418,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5484,10 +5457,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>576799</v>
+        <v>576690</v>
       </c>
       <c r="R44" t="n">
-        <v>6379827</v>
+        <v>6379955</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5547,10 +5520,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123312935</v>
+        <v>123312958</v>
       </c>
       <c r="B45" t="n">
-        <v>98368</v>
+        <v>105476</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5559,25 +5532,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5595,10 +5568,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>576793</v>
+        <v>576745</v>
       </c>
       <c r="R45" t="n">
-        <v>6379822</v>
+        <v>6379872</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5658,10 +5631,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123312773</v>
+        <v>123312486</v>
       </c>
       <c r="B46" t="n">
-        <v>105474</v>
+        <v>57851</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5674,31 +5647,35 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5706,13 +5683,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>576839</v>
+        <v>576693</v>
       </c>
       <c r="R46" t="n">
-        <v>6379721</v>
+        <v>6379898</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5739,18 +5716,27 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5769,10 +5755,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123312958</v>
+        <v>123312540</v>
       </c>
       <c r="B47" t="n">
-        <v>105474</v>
+        <v>57851</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5785,31 +5771,35 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5817,13 +5807,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>576745</v>
+        <v>576808</v>
       </c>
       <c r="R47" t="n">
-        <v>6379872</v>
+        <v>6379847</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5850,18 +5840,27 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5873,17 +5872,17 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Per Muhr, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123313044</v>
+        <v>123312808</v>
       </c>
       <c r="B48" t="n">
-        <v>91365</v>
+        <v>97324</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5896,34 +5895,35 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5420</v>
+        <v>221945</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5931,10 +5931,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>576690</v>
+        <v>576804</v>
       </c>
       <c r="R48" t="n">
-        <v>6379955</v>
+        <v>6379891</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5994,10 +5994,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123312993</v>
+        <v>123312502</v>
       </c>
       <c r="B49" t="n">
-        <v>90975</v>
+        <v>95141</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6006,38 +6006,31 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6045,10 +6038,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>576745</v>
+        <v>576740</v>
       </c>
       <c r="R49" t="n">
-        <v>6379872</v>
+        <v>6379855</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6078,9 +6071,19 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6108,10 +6111,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123313067</v>
+        <v>123312935</v>
       </c>
       <c r="B50" t="n">
-        <v>90975</v>
+        <v>98370</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6120,38 +6123,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6159,10 +6159,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>576682</v>
+        <v>576793</v>
       </c>
       <c r="R50" t="n">
-        <v>6379963</v>
+        <v>6379822</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+          <t>Per Muhr, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>

--- a/artfynd/A 11444-2025 artfynd.xlsx
+++ b/artfynd/A 11444-2025 artfynd.xlsx
@@ -3254,10 +3254,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123259993</v>
+        <v>123259084</v>
       </c>
       <c r="B25" t="n">
-        <v>90977</v>
+        <v>92266</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3270,26 +3270,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>5449</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3301,14 +3301,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444, Grönled, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>576929</v>
+        <v>577012</v>
       </c>
       <c r="R25" t="n">
-        <v>6379832</v>
+        <v>6379533</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3368,10 +3368,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123259084</v>
+        <v>123259993</v>
       </c>
       <c r="B26" t="n">
-        <v>92266</v>
+        <v>90977</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3384,26 +3384,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5449</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3415,14 +3415,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>A 11444, Grönled, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577012</v>
+        <v>576929</v>
       </c>
       <c r="R26" t="n">
-        <v>6379533</v>
+        <v>6379832</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4268,10 +4268,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123313086</v>
+        <v>123312753</v>
       </c>
       <c r="B34" t="n">
-        <v>57851</v>
+        <v>98370</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4280,39 +4280,35 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4320,10 +4316,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>576640</v>
+        <v>576835</v>
       </c>
       <c r="R34" t="n">
-        <v>6379941</v>
+        <v>6379711</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4364,6 +4360,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4382,10 +4379,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123312753</v>
+        <v>123313086</v>
       </c>
       <c r="B35" t="n">
-        <v>98370</v>
+        <v>57851</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4394,35 +4391,39 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4430,10 +4431,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>576835</v>
+        <v>576640</v>
       </c>
       <c r="R35" t="n">
-        <v>6379711</v>
+        <v>6379941</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4474,7 +4475,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -5994,10 +5994,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123312502</v>
+        <v>123312935</v>
       </c>
       <c r="B49" t="n">
-        <v>95141</v>
+        <v>98370</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6006,29 +6006,33 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
@@ -6038,10 +6042,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>576740</v>
+        <v>576793</v>
       </c>
       <c r="R49" t="n">
-        <v>6379855</v>
+        <v>6379822</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6071,19 +6075,9 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>15:50</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6104,17 +6098,17 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+          <t>Per Muhr, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123312935</v>
+        <v>123312502</v>
       </c>
       <c r="B50" t="n">
-        <v>98370</v>
+        <v>95141</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6123,33 +6117,29 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
@@ -6159,10 +6149,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>576793</v>
+        <v>576740</v>
       </c>
       <c r="R50" t="n">
-        <v>6379822</v>
+        <v>6379855</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6192,9 +6182,19 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Per Muhr, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>

--- a/artfynd/A 11444-2025 artfynd.xlsx
+++ b/artfynd/A 11444-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123259332</v>
+        <v>123259910</v>
       </c>
       <c r="B2" t="n">
-        <v>98370</v>
+        <v>91373</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576987</v>
+        <v>576891</v>
       </c>
       <c r="R2" t="n">
-        <v>6379692</v>
+        <v>6379777</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123259882</v>
+        <v>123259131</v>
       </c>
       <c r="B3" t="n">
-        <v>57497</v>
+        <v>92244</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,35 +801,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576832</v>
+        <v>577009</v>
       </c>
       <c r="R3" t="n">
-        <v>6379712</v>
+        <v>6379596</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,17 +878,13 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bearbetat torrträd</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -901,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123259362</v>
+        <v>123259392</v>
       </c>
       <c r="B4" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -949,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576989</v>
+        <v>576988</v>
       </c>
       <c r="R4" t="n">
-        <v>6379691</v>
+        <v>6379698</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123259392</v>
+        <v>123259974</v>
       </c>
       <c r="B5" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576988</v>
+        <v>576950</v>
       </c>
       <c r="R5" t="n">
-        <v>6379698</v>
+        <v>6379824</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123259910</v>
+        <v>123260939</v>
       </c>
       <c r="B6" t="n">
-        <v>91367</v>
+        <v>98376</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,38 +1137,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1174,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576891</v>
+        <v>576951</v>
       </c>
       <c r="R6" t="n">
-        <v>6379777</v>
+        <v>6379805</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123259460</v>
+        <v>123259111</v>
       </c>
       <c r="B7" t="n">
-        <v>92238</v>
+        <v>92244</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,7 +1269,11 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -1284,10 +1287,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576977</v>
+        <v>577001</v>
       </c>
       <c r="R7" t="n">
-        <v>6379694</v>
+        <v>6379581</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1350,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123259312</v>
+        <v>123259271</v>
       </c>
       <c r="B8" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,14 +1394,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444. Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576990</v>
+        <v>576994</v>
       </c>
       <c r="R8" t="n">
-        <v>6379697</v>
+        <v>6379690</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1458,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123259131</v>
+        <v>123259628</v>
       </c>
       <c r="B9" t="n">
-        <v>92238</v>
+        <v>57851</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1474,21 +1477,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,26 +1499,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577009</v>
+        <v>576883</v>
       </c>
       <c r="R9" t="n">
-        <v>6379596</v>
+        <v>6379747</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1553,7 +1557,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1572,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123259554</v>
+        <v>123259209</v>
       </c>
       <c r="B10" t="n">
-        <v>105476</v>
+        <v>90963</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1584,35 +1587,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1620,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576891</v>
+        <v>576992</v>
       </c>
       <c r="R10" t="n">
-        <v>6379769</v>
+        <v>6379660</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,10 +1689,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123259628</v>
+        <v>123259157</v>
       </c>
       <c r="B11" t="n">
-        <v>57851</v>
+        <v>57634</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,25 +1701,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1731,14 +1737,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A11444, Grönlid, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576883</v>
+        <v>576997</v>
       </c>
       <c r="R11" t="n">
-        <v>6379747</v>
+        <v>6379617</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1797,10 +1803,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123259157</v>
+        <v>123259471</v>
       </c>
       <c r="B12" t="n">
-        <v>57634</v>
+        <v>98376</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1809,53 +1815,49 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444, Grönlif, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576997</v>
+        <v>576971</v>
       </c>
       <c r="R12" t="n">
-        <v>6379617</v>
+        <v>6379688</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1893,6 +1895,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1911,10 +1914,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123259930</v>
+        <v>123259084</v>
       </c>
       <c r="B13" t="n">
-        <v>98370</v>
+        <v>92272</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,46 +1926,49 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444, Grönled, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576949</v>
+        <v>577012</v>
       </c>
       <c r="R13" t="n">
-        <v>6379790</v>
+        <v>6379533</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2022,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123259271</v>
+        <v>123259522</v>
       </c>
       <c r="B14" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2066,14 +2072,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 11444. Grönlid, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576994</v>
+        <v>576971</v>
       </c>
       <c r="R14" t="n">
-        <v>6379690</v>
+        <v>6379715</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2133,10 +2139,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123259522</v>
+        <v>123259312</v>
       </c>
       <c r="B15" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2181,10 +2187,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576971</v>
+        <v>576990</v>
       </c>
       <c r="R15" t="n">
-        <v>6379715</v>
+        <v>6379697</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2244,10 +2250,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123259209</v>
+        <v>123259183</v>
       </c>
       <c r="B16" t="n">
-        <v>90957</v>
+        <v>92244</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2256,25 +2262,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2284,7 +2290,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -2295,10 +2301,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576992</v>
+        <v>577000</v>
       </c>
       <c r="R16" t="n">
-        <v>6379660</v>
+        <v>6379640</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2358,10 +2364,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123259183</v>
+        <v>123259993</v>
       </c>
       <c r="B17" t="n">
-        <v>92238</v>
+        <v>90983</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2370,25 +2376,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2409,10 +2415,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577000</v>
+        <v>576929</v>
       </c>
       <c r="R17" t="n">
-        <v>6379640</v>
+        <v>6379832</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2472,10 +2478,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123259419</v>
+        <v>123259948</v>
       </c>
       <c r="B18" t="n">
-        <v>57634</v>
+        <v>98376</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2484,53 +2490,49 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>A 11444, Grönlif, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576985</v>
+        <v>576939</v>
       </c>
       <c r="R18" t="n">
-        <v>6379714</v>
+        <v>6379798</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2568,6 +2570,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2586,10 +2589,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123259498</v>
+        <v>123259554</v>
       </c>
       <c r="B19" t="n">
-        <v>95141</v>
+        <v>105482</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2602,25 +2605,29 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2630,10 +2637,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576965</v>
+        <v>576891</v>
       </c>
       <c r="R19" t="n">
-        <v>6379700</v>
+        <v>6379769</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2693,10 +2700,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123259974</v>
+        <v>123259828</v>
       </c>
       <c r="B20" t="n">
-        <v>98370</v>
+        <v>90963</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2705,35 +2712,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2741,10 +2751,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576950</v>
+        <v>576838</v>
       </c>
       <c r="R20" t="n">
-        <v>6379824</v>
+        <v>6379654</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2804,10 +2814,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123259111</v>
+        <v>123259930</v>
       </c>
       <c r="B21" t="n">
-        <v>92238</v>
+        <v>98376</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2816,38 +2826,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2855,10 +2862,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577001</v>
+        <v>576949</v>
       </c>
       <c r="R21" t="n">
-        <v>6379581</v>
+        <v>6379790</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2918,10 +2925,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123260939</v>
+        <v>123259419</v>
       </c>
       <c r="B22" t="n">
-        <v>98370</v>
+        <v>57634</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2930,49 +2937,53 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444, Grönlif, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576951</v>
+        <v>576985</v>
       </c>
       <c r="R22" t="n">
-        <v>6379805</v>
+        <v>6379714</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3010,7 +3021,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3029,10 +3039,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123260011</v>
+        <v>123259460</v>
       </c>
       <c r="B23" t="n">
-        <v>90957</v>
+        <v>92244</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3041,35 +3051,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -3080,10 +3086,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576847</v>
+        <v>576977</v>
       </c>
       <c r="R23" t="n">
-        <v>6379709</v>
+        <v>6379694</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3143,10 +3149,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123259440</v>
+        <v>123260011</v>
       </c>
       <c r="B24" t="n">
-        <v>98370</v>
+        <v>90963</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3155,35 +3161,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3191,10 +3200,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>576980</v>
+        <v>576847</v>
       </c>
       <c r="R24" t="n">
-        <v>6379697</v>
+        <v>6379709</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3254,10 +3263,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123259084</v>
+        <v>123259440</v>
       </c>
       <c r="B25" t="n">
-        <v>92266</v>
+        <v>98376</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3266,49 +3275,46 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>A 11444, Grönled, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577012</v>
+        <v>576980</v>
       </c>
       <c r="R25" t="n">
-        <v>6379533</v>
+        <v>6379697</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3368,10 +3374,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123259993</v>
+        <v>123259851</v>
       </c>
       <c r="B26" t="n">
-        <v>90977</v>
+        <v>90963</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3384,21 +3390,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3408,7 +3414,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -3419,10 +3425,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>576929</v>
+        <v>576835</v>
       </c>
       <c r="R26" t="n">
-        <v>6379832</v>
+        <v>6379715</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3482,10 +3488,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123259471</v>
+        <v>123259498</v>
       </c>
       <c r="B27" t="n">
-        <v>98370</v>
+        <v>95147</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3494,46 +3500,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>A 11444, Grönlif, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>576971</v>
+        <v>576965</v>
       </c>
       <c r="R27" t="n">
-        <v>6379688</v>
+        <v>6379700</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3593,10 +3595,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123259851</v>
+        <v>123259882</v>
       </c>
       <c r="B28" t="n">
-        <v>90957</v>
+        <v>57497</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3609,34 +3611,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3644,10 +3643,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>576835</v>
+        <v>576832</v>
       </c>
       <c r="R28" t="n">
-        <v>6379715</v>
+        <v>6379712</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3682,13 +3681,17 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Bearbetat torrträd</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3707,10 +3710,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123259828</v>
+        <v>123259362</v>
       </c>
       <c r="B29" t="n">
-        <v>90957</v>
+        <v>98376</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3719,38 +3722,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>576838</v>
+        <v>576989</v>
       </c>
       <c r="R29" t="n">
-        <v>6379654</v>
+        <v>6379691</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3821,10 +3821,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123259948</v>
+        <v>123259332</v>
       </c>
       <c r="B30" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3869,10 +3869,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>576939</v>
+        <v>576987</v>
       </c>
       <c r="R30" t="n">
-        <v>6379798</v>
+        <v>6379692</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3932,10 +3932,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123312904</v>
+        <v>123313080</v>
       </c>
       <c r="B31" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3966,11 +3966,7 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
@@ -3980,10 +3976,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>576804</v>
+        <v>576640</v>
       </c>
       <c r="R31" t="n">
-        <v>6379845</v>
+        <v>6379941</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4036,17 +4032,17 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Per Muhr, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123312773</v>
+        <v>123312896</v>
       </c>
       <c r="B32" t="n">
-        <v>105476</v>
+        <v>105482</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4091,10 +4087,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>576839</v>
+        <v>576804</v>
       </c>
       <c r="R32" t="n">
-        <v>6379721</v>
+        <v>6379845</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4154,10 +4150,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123313067</v>
+        <v>123313086</v>
       </c>
       <c r="B33" t="n">
-        <v>90977</v>
+        <v>57851</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4166,38 +4162,39 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5442</v>
+        <v>103015</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4205,10 +4202,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>576682</v>
+        <v>576640</v>
       </c>
       <c r="R33" t="n">
-        <v>6379963</v>
+        <v>6379941</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4249,7 +4246,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4268,10 +4264,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123312753</v>
+        <v>123312808</v>
       </c>
       <c r="B34" t="n">
-        <v>98370</v>
+        <v>97330</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4280,31 +4276,35 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>576835</v>
+        <v>576804</v>
       </c>
       <c r="R34" t="n">
-        <v>6379711</v>
+        <v>6379891</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4379,10 +4379,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123313086</v>
+        <v>123313044</v>
       </c>
       <c r="B35" t="n">
-        <v>57851</v>
+        <v>91373</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4395,21 +4395,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103015</v>
+        <v>5420</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4417,13 +4417,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4431,10 +4430,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>576640</v>
+        <v>576690</v>
       </c>
       <c r="R35" t="n">
-        <v>6379941</v>
+        <v>6379955</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4475,6 +4474,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4493,10 +4493,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123313080</v>
+        <v>123313067</v>
       </c>
       <c r="B36" t="n">
-        <v>98370</v>
+        <v>90983</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4505,31 +4505,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4537,10 +4544,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>576640</v>
+        <v>576682</v>
       </c>
       <c r="R36" t="n">
-        <v>6379941</v>
+        <v>6379963</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4603,7 +4610,7 @@
         <v>123312569</v>
       </c>
       <c r="B37" t="n">
-        <v>105476</v>
+        <v>105482</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4721,10 +4728,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123312993</v>
+        <v>123312753</v>
       </c>
       <c r="B38" t="n">
-        <v>90977</v>
+        <v>98376</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4733,38 +4740,35 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4772,10 +4776,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>576745</v>
+        <v>576835</v>
       </c>
       <c r="R38" t="n">
-        <v>6379872</v>
+        <v>6379711</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4838,7 +4842,7 @@
         <v>123312921</v>
       </c>
       <c r="B39" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4939,7 +4943,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Per Muhr, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4949,7 +4953,7 @@
         <v>123313052</v>
       </c>
       <c r="B40" t="n">
-        <v>91367</v>
+        <v>91373</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5060,10 +5064,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123312896</v>
+        <v>123312486</v>
       </c>
       <c r="B41" t="n">
-        <v>105476</v>
+        <v>57851</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5076,31 +5080,35 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5108,13 +5116,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>576804</v>
+        <v>576693</v>
       </c>
       <c r="R41" t="n">
-        <v>6379845</v>
+        <v>6379898</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5141,18 +5149,27 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5164,17 +5181,17 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Per Muhr, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123313124</v>
+        <v>123312502</v>
       </c>
       <c r="B42" t="n">
-        <v>98370</v>
+        <v>95147</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5183,33 +5200,29 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
@@ -5219,10 +5232,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>576507</v>
+        <v>576740</v>
       </c>
       <c r="R42" t="n">
-        <v>6379922</v>
+        <v>6379855</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5252,9 +5265,19 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5282,10 +5305,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123312524</v>
+        <v>123312993</v>
       </c>
       <c r="B43" t="n">
-        <v>92238</v>
+        <v>90983</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5294,30 +5317,30 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5333,10 +5356,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>576731</v>
+        <v>576745</v>
       </c>
       <c r="R43" t="n">
-        <v>6379842</v>
+        <v>6379872</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5366,19 +5389,9 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>15:50</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5406,10 +5419,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123313044</v>
+        <v>123312773</v>
       </c>
       <c r="B44" t="n">
-        <v>91367</v>
+        <v>105482</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5422,34 +5435,31 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5420</v>
+        <v>221144</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5457,10 +5467,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>576690</v>
+        <v>576839</v>
       </c>
       <c r="R44" t="n">
-        <v>6379955</v>
+        <v>6379721</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5520,10 +5530,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123312958</v>
+        <v>123312904</v>
       </c>
       <c r="B45" t="n">
-        <v>105476</v>
+        <v>98376</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5532,25 +5542,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5568,10 +5578,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>576745</v>
+        <v>576804</v>
       </c>
       <c r="R45" t="n">
-        <v>6379872</v>
+        <v>6379845</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5631,10 +5641,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123312486</v>
+        <v>123312958</v>
       </c>
       <c r="B46" t="n">
-        <v>57851</v>
+        <v>105482</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5647,35 +5657,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5683,13 +5689,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>576693</v>
+        <v>576745</v>
       </c>
       <c r="R46" t="n">
-        <v>6379898</v>
+        <v>6379872</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5716,27 +5722,18 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5755,10 +5752,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123312540</v>
+        <v>123312935</v>
       </c>
       <c r="B47" t="n">
-        <v>57851</v>
+        <v>98376</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5767,39 +5764,35 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5807,13 +5800,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>576808</v>
+        <v>576793</v>
       </c>
       <c r="R47" t="n">
-        <v>6379847</v>
+        <v>6379822</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5840,27 +5833,18 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5879,10 +5863,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123312808</v>
+        <v>123313124</v>
       </c>
       <c r="B48" t="n">
-        <v>97324</v>
+        <v>98376</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5891,35 +5875,31 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -5931,10 +5911,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>576804</v>
+        <v>576507</v>
       </c>
       <c r="R48" t="n">
-        <v>6379891</v>
+        <v>6379922</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5994,10 +5974,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123312935</v>
+        <v>123312524</v>
       </c>
       <c r="B49" t="n">
-        <v>98370</v>
+        <v>92244</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6006,35 +5986,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6042,10 +6025,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>576793</v>
+        <v>576731</v>
       </c>
       <c r="R49" t="n">
-        <v>6379822</v>
+        <v>6379842</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6075,9 +6058,19 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6098,17 +6091,17 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Per Muhr, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123312502</v>
+        <v>123312540</v>
       </c>
       <c r="B50" t="n">
-        <v>95141</v>
+        <v>57851</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6121,27 +6114,35 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6149,13 +6150,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>576740</v>
+        <v>576808</v>
       </c>
       <c r="R50" t="n">
-        <v>6379855</v>
+        <v>6379847</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6203,7 +6204,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11444-2025 artfynd.xlsx
+++ b/artfynd/A 11444-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123259910</v>
+        <v>123259271</v>
       </c>
       <c r="B2" t="n">
-        <v>91373</v>
+        <v>98379</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,49 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444. Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576891</v>
+        <v>576994</v>
       </c>
       <c r="R2" t="n">
-        <v>6379777</v>
+        <v>6379690</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123259131</v>
+        <v>123259948</v>
       </c>
       <c r="B3" t="n">
-        <v>92244</v>
+        <v>98379</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,38 +798,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577009</v>
+        <v>576939</v>
       </c>
       <c r="R3" t="n">
-        <v>6379596</v>
+        <v>6379798</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123259392</v>
+        <v>123259183</v>
       </c>
       <c r="B4" t="n">
-        <v>98376</v>
+        <v>92247</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,35 +909,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576988</v>
+        <v>577000</v>
       </c>
       <c r="R4" t="n">
-        <v>6379698</v>
+        <v>6379640</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123259974</v>
+        <v>123259628</v>
       </c>
       <c r="B5" t="n">
-        <v>98376</v>
+        <v>57851</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,49 +1023,53 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576950</v>
+        <v>576883</v>
       </c>
       <c r="R5" t="n">
-        <v>6379824</v>
+        <v>6379747</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,7 +1107,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1125,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123260939</v>
+        <v>123259332</v>
       </c>
       <c r="B6" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576951</v>
+        <v>576987</v>
       </c>
       <c r="R6" t="n">
-        <v>6379805</v>
+        <v>6379692</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123259111</v>
+        <v>123259419</v>
       </c>
       <c r="B7" t="n">
-        <v>92244</v>
+        <v>57634</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,52 +1248,53 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444, Grönlif, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577001</v>
+        <v>576985</v>
       </c>
       <c r="R7" t="n">
-        <v>6379581</v>
+        <v>6379714</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1331,7 +1332,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1350,10 +1350,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123259271</v>
+        <v>123259460</v>
       </c>
       <c r="B8" t="n">
-        <v>98376</v>
+        <v>92247</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1362,46 +1362,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 11444. Grönlid, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576994</v>
+        <v>576977</v>
       </c>
       <c r="R8" t="n">
-        <v>6379690</v>
+        <v>6379694</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,10 +1460,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123259628</v>
+        <v>123259993</v>
       </c>
       <c r="B9" t="n">
-        <v>57851</v>
+        <v>90986</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1473,25 +1472,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1499,27 +1498,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A11444, Grönlid, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576883</v>
+        <v>576929</v>
       </c>
       <c r="R9" t="n">
-        <v>6379747</v>
+        <v>6379832</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1557,6 +1555,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1575,10 +1574,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123259209</v>
+        <v>123259312</v>
       </c>
       <c r="B10" t="n">
-        <v>90963</v>
+        <v>98379</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,38 +1586,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1626,10 +1622,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576992</v>
+        <v>576990</v>
       </c>
       <c r="R10" t="n">
-        <v>6379660</v>
+        <v>6379697</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1689,10 +1685,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123259157</v>
+        <v>123259362</v>
       </c>
       <c r="B11" t="n">
-        <v>57634</v>
+        <v>98379</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1701,39 +1697,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1741,13 +1733,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576997</v>
+        <v>576989</v>
       </c>
       <c r="R11" t="n">
-        <v>6379617</v>
+        <v>6379691</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1785,6 +1777,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1803,10 +1796,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123259471</v>
+        <v>123259828</v>
       </c>
       <c r="B12" t="n">
-        <v>98376</v>
+        <v>90966</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1815,46 +1808,49 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 11444, Grönlif, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576971</v>
+        <v>576838</v>
       </c>
       <c r="R12" t="n">
-        <v>6379688</v>
+        <v>6379654</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1914,10 +1910,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123259084</v>
+        <v>123259498</v>
       </c>
       <c r="B13" t="n">
-        <v>92272</v>
+        <v>95150</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1926,49 +1922,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5449</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 11444, Grönled, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577012</v>
+        <v>576965</v>
       </c>
       <c r="R13" t="n">
-        <v>6379533</v>
+        <v>6379700</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2028,10 +2017,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123259522</v>
+        <v>123259392</v>
       </c>
       <c r="B14" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2076,10 +2065,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576971</v>
+        <v>576988</v>
       </c>
       <c r="R14" t="n">
-        <v>6379715</v>
+        <v>6379698</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2139,10 +2128,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123259312</v>
+        <v>123259157</v>
       </c>
       <c r="B15" t="n">
-        <v>98376</v>
+        <v>57634</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2151,35 +2140,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2187,13 +2180,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576990</v>
+        <v>576997</v>
       </c>
       <c r="R15" t="n">
-        <v>6379697</v>
+        <v>6379617</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2231,7 +2224,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2250,10 +2242,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123259183</v>
+        <v>123259471</v>
       </c>
       <c r="B16" t="n">
-        <v>92244</v>
+        <v>98379</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2262,49 +2254,46 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444, Grönlif, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577000</v>
+        <v>576971</v>
       </c>
       <c r="R16" t="n">
-        <v>6379640</v>
+        <v>6379688</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2364,10 +2353,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123259993</v>
+        <v>123259974</v>
       </c>
       <c r="B17" t="n">
-        <v>90983</v>
+        <v>98379</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2376,38 +2365,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2415,10 +2401,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576929</v>
+        <v>576950</v>
       </c>
       <c r="R17" t="n">
-        <v>6379832</v>
+        <v>6379824</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2478,10 +2464,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123259948</v>
+        <v>123260939</v>
       </c>
       <c r="B18" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2526,10 +2512,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576939</v>
+        <v>576951</v>
       </c>
       <c r="R18" t="n">
-        <v>6379798</v>
+        <v>6379805</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2589,10 +2575,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123259554</v>
+        <v>123259209</v>
       </c>
       <c r="B19" t="n">
-        <v>105482</v>
+        <v>90966</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2601,35 +2587,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2637,10 +2626,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576891</v>
+        <v>576992</v>
       </c>
       <c r="R19" t="n">
-        <v>6379769</v>
+        <v>6379660</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2700,10 +2689,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123259828</v>
+        <v>123260011</v>
       </c>
       <c r="B20" t="n">
-        <v>90963</v>
+        <v>90966</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2751,10 +2740,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576838</v>
+        <v>576847</v>
       </c>
       <c r="R20" t="n">
-        <v>6379654</v>
+        <v>6379709</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2814,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123259930</v>
+        <v>123259882</v>
       </c>
       <c r="B21" t="n">
-        <v>98376</v>
+        <v>57497</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2826,35 +2815,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2862,10 +2851,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>576949</v>
+        <v>576832</v>
       </c>
       <c r="R21" t="n">
-        <v>6379790</v>
+        <v>6379712</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2900,13 +2889,17 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Bearbetat torrträd</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2925,10 +2918,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123259419</v>
+        <v>123259910</v>
       </c>
       <c r="B22" t="n">
-        <v>57634</v>
+        <v>91376</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2937,25 +2930,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>5420</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2963,27 +2956,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>A 11444, Grönlif, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576985</v>
+        <v>576891</v>
       </c>
       <c r="R22" t="n">
-        <v>6379714</v>
+        <v>6379777</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3021,6 +3013,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3039,10 +3032,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123259460</v>
+        <v>123259111</v>
       </c>
       <c r="B23" t="n">
-        <v>92244</v>
+        <v>92247</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3072,7 +3065,11 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -3086,10 +3083,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576977</v>
+        <v>577001</v>
       </c>
       <c r="R23" t="n">
-        <v>6379694</v>
+        <v>6379581</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3149,10 +3146,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123260011</v>
+        <v>123259522</v>
       </c>
       <c r="B24" t="n">
-        <v>90963</v>
+        <v>98379</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3161,38 +3158,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3200,10 +3194,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>576847</v>
+        <v>576971</v>
       </c>
       <c r="R24" t="n">
-        <v>6379709</v>
+        <v>6379715</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3263,10 +3257,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123259440</v>
+        <v>123259851</v>
       </c>
       <c r="B25" t="n">
-        <v>98376</v>
+        <v>90966</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3275,35 +3269,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3311,10 +3308,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>576980</v>
+        <v>576835</v>
       </c>
       <c r="R25" t="n">
-        <v>6379697</v>
+        <v>6379715</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3374,10 +3371,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123259851</v>
+        <v>123259440</v>
       </c>
       <c r="B26" t="n">
-        <v>90963</v>
+        <v>98379</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3386,38 +3383,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3425,10 +3419,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>576835</v>
+        <v>576980</v>
       </c>
       <c r="R26" t="n">
-        <v>6379715</v>
+        <v>6379697</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3488,10 +3482,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123259498</v>
+        <v>123259131</v>
       </c>
       <c r="B27" t="n">
-        <v>95147</v>
+        <v>92247</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3504,27 +3498,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3532,10 +3533,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>576965</v>
+        <v>577009</v>
       </c>
       <c r="R27" t="n">
-        <v>6379700</v>
+        <v>6379596</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3595,10 +3596,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123259882</v>
+        <v>123259554</v>
       </c>
       <c r="B28" t="n">
-        <v>57497</v>
+        <v>105485</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3607,35 +3608,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3643,10 +3644,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>576832</v>
+        <v>576891</v>
       </c>
       <c r="R28" t="n">
-        <v>6379712</v>
+        <v>6379769</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3681,17 +3682,13 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Bearbetat torrträd</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3710,10 +3707,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123259362</v>
+        <v>123259930</v>
       </c>
       <c r="B29" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3758,10 +3755,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>576989</v>
+        <v>576949</v>
       </c>
       <c r="R29" t="n">
-        <v>6379691</v>
+        <v>6379790</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3821,10 +3818,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123259332</v>
+        <v>123259084</v>
       </c>
       <c r="B30" t="n">
-        <v>98376</v>
+        <v>92275</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3833,46 +3830,49 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444, Grönled, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>576987</v>
+        <v>577012</v>
       </c>
       <c r="R30" t="n">
-        <v>6379692</v>
+        <v>6379533</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3932,10 +3932,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123313080</v>
+        <v>123312935</v>
       </c>
       <c r="B31" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3966,7 +3966,11 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
@@ -3976,10 +3980,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>576640</v>
+        <v>576793</v>
       </c>
       <c r="R31" t="n">
-        <v>6379941</v>
+        <v>6379822</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4039,10 +4043,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123312896</v>
+        <v>123313080</v>
       </c>
       <c r="B32" t="n">
-        <v>105482</v>
+        <v>98379</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4051,33 +4055,29 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
@@ -4087,10 +4087,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>576804</v>
+        <v>576640</v>
       </c>
       <c r="R32" t="n">
-        <v>6379845</v>
+        <v>6379941</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4150,10 +4150,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123313086</v>
+        <v>123312958</v>
       </c>
       <c r="B33" t="n">
-        <v>57851</v>
+        <v>105485</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4166,35 +4166,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4202,10 +4198,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>576640</v>
+        <v>576745</v>
       </c>
       <c r="R33" t="n">
-        <v>6379941</v>
+        <v>6379872</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4246,6 +4242,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4264,10 +4261,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123312808</v>
+        <v>123312773</v>
       </c>
       <c r="B34" t="n">
-        <v>97330</v>
+        <v>105485</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4280,31 +4277,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -4316,10 +4309,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>576804</v>
+        <v>576839</v>
       </c>
       <c r="R34" t="n">
-        <v>6379891</v>
+        <v>6379721</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4379,10 +4372,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123313044</v>
+        <v>123312896</v>
       </c>
       <c r="B35" t="n">
-        <v>91373</v>
+        <v>105485</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4395,34 +4388,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5420</v>
+        <v>221144</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4430,10 +4420,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>576690</v>
+        <v>576804</v>
       </c>
       <c r="R35" t="n">
-        <v>6379955</v>
+        <v>6379845</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4493,10 +4483,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123313067</v>
+        <v>123313052</v>
       </c>
       <c r="B36" t="n">
-        <v>90983</v>
+        <v>91376</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4505,30 +4495,30 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4544,10 +4534,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>576682</v>
+        <v>576677</v>
       </c>
       <c r="R36" t="n">
-        <v>6379963</v>
+        <v>6379959</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4607,10 +4597,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123312569</v>
+        <v>123313086</v>
       </c>
       <c r="B37" t="n">
-        <v>105482</v>
+        <v>57851</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4623,31 +4613,35 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4655,10 +4649,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>576803</v>
+        <v>576640</v>
       </c>
       <c r="R37" t="n">
-        <v>6379887</v>
+        <v>6379941</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4688,28 +4682,17 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4728,10 +4711,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123312753</v>
+        <v>123312904</v>
       </c>
       <c r="B38" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4776,10 +4759,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>576835</v>
+        <v>576804</v>
       </c>
       <c r="R38" t="n">
-        <v>6379711</v>
+        <v>6379845</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4839,10 +4822,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123312921</v>
+        <v>123313124</v>
       </c>
       <c r="B39" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4887,10 +4870,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>576799</v>
+        <v>576507</v>
       </c>
       <c r="R39" t="n">
-        <v>6379827</v>
+        <v>6379922</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4950,10 +4933,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123313052</v>
+        <v>123312808</v>
       </c>
       <c r="B40" t="n">
-        <v>91373</v>
+        <v>97333</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4966,21 +4949,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5420</v>
+        <v>221945</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4990,10 +4973,11 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5001,10 +4985,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>576677</v>
+        <v>576804</v>
       </c>
       <c r="R40" t="n">
-        <v>6379959</v>
+        <v>6379891</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5064,10 +5048,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123312486</v>
+        <v>123313044</v>
       </c>
       <c r="B41" t="n">
-        <v>57851</v>
+        <v>91376</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5080,21 +5064,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103015</v>
+        <v>5420</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5102,13 +5086,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5116,13 +5099,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>576693</v>
+        <v>576690</v>
       </c>
       <c r="R41" t="n">
-        <v>6379898</v>
+        <v>6379955</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5149,27 +5132,18 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5188,10 +5162,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123312502</v>
+        <v>123312540</v>
       </c>
       <c r="B42" t="n">
-        <v>95147</v>
+        <v>57851</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5204,27 +5178,35 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5232,13 +5214,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>576740</v>
+        <v>576808</v>
       </c>
       <c r="R42" t="n">
-        <v>6379855</v>
+        <v>6379847</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5286,7 +5268,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5305,10 +5286,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123312993</v>
+        <v>123312502</v>
       </c>
       <c r="B43" t="n">
-        <v>90983</v>
+        <v>95150</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5317,38 +5298,31 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5356,10 +5330,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>576745</v>
+        <v>576740</v>
       </c>
       <c r="R43" t="n">
-        <v>6379872</v>
+        <v>6379855</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5389,9 +5363,19 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5419,10 +5403,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123312773</v>
+        <v>123312524</v>
       </c>
       <c r="B44" t="n">
-        <v>105482</v>
+        <v>92247</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5435,31 +5419,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5467,10 +5454,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>576839</v>
+        <v>576731</v>
       </c>
       <c r="R44" t="n">
-        <v>6379721</v>
+        <v>6379842</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5500,9 +5487,19 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5530,10 +5527,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123312904</v>
+        <v>123312569</v>
       </c>
       <c r="B45" t="n">
-        <v>98376</v>
+        <v>105485</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5542,25 +5539,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5578,10 +5575,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>576804</v>
+        <v>576803</v>
       </c>
       <c r="R45" t="n">
-        <v>6379845</v>
+        <v>6379887</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5611,9 +5608,19 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5641,10 +5648,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123312958</v>
+        <v>123313067</v>
       </c>
       <c r="B46" t="n">
-        <v>105482</v>
+        <v>90986</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5653,35 +5660,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5689,10 +5699,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>576745</v>
+        <v>576682</v>
       </c>
       <c r="R46" t="n">
-        <v>6379872</v>
+        <v>6379963</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5752,10 +5762,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123312935</v>
+        <v>123312921</v>
       </c>
       <c r="B47" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5800,10 +5810,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>576793</v>
+        <v>576799</v>
       </c>
       <c r="R47" t="n">
-        <v>6379822</v>
+        <v>6379827</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5863,10 +5873,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123313124</v>
+        <v>123312753</v>
       </c>
       <c r="B48" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5911,10 +5921,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>576507</v>
+        <v>576835</v>
       </c>
       <c r="R48" t="n">
-        <v>6379922</v>
+        <v>6379711</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5974,10 +5984,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123312524</v>
+        <v>123312993</v>
       </c>
       <c r="B49" t="n">
-        <v>92244</v>
+        <v>90986</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5986,30 +5996,30 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6025,10 +6035,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>576731</v>
+        <v>576745</v>
       </c>
       <c r="R49" t="n">
-        <v>6379842</v>
+        <v>6379872</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6058,19 +6068,9 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>15:50</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6098,7 +6098,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123312540</v>
+        <v>123312486</v>
       </c>
       <c r="B50" t="n">
         <v>57851</v>
@@ -6150,10 +6150,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>576808</v>
+        <v>576693</v>
       </c>
       <c r="R50" t="n">
-        <v>6379847</v>
+        <v>6379898</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>

--- a/artfynd/A 11444-2025 artfynd.xlsx
+++ b/artfynd/A 11444-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123259271</v>
+        <v>123259828</v>
       </c>
       <c r="B2" t="n">
-        <v>98379</v>
+        <v>90983</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,49 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 11444. Grönlid, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576994</v>
+        <v>576838</v>
       </c>
       <c r="R2" t="n">
-        <v>6379690</v>
+        <v>6379654</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123259948</v>
+        <v>123259209</v>
       </c>
       <c r="B3" t="n">
-        <v>98379</v>
+        <v>90983</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,35 +801,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576939</v>
+        <v>576992</v>
       </c>
       <c r="R3" t="n">
-        <v>6379798</v>
+        <v>6379660</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123259183</v>
+        <v>123259362</v>
       </c>
       <c r="B4" t="n">
-        <v>92247</v>
+        <v>98396</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,38 +915,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -948,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577000</v>
+        <v>576989</v>
       </c>
       <c r="R4" t="n">
-        <v>6379640</v>
+        <v>6379691</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123259628</v>
+        <v>123260939</v>
       </c>
       <c r="B5" t="n">
-        <v>57851</v>
+        <v>98396</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,53 +1026,49 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A11444, Grönlid, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576883</v>
+        <v>576951</v>
       </c>
       <c r="R5" t="n">
-        <v>6379747</v>
+        <v>6379805</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1107,6 +1106,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1125,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123259332</v>
+        <v>123259084</v>
       </c>
       <c r="B6" t="n">
-        <v>98379</v>
+        <v>92292</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,46 +1137,49 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444, Grönled, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576987</v>
+        <v>577012</v>
       </c>
       <c r="R6" t="n">
-        <v>6379692</v>
+        <v>6379533</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123259419</v>
+        <v>123259910</v>
       </c>
       <c r="B7" t="n">
-        <v>57634</v>
+        <v>91393</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,25 +1251,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>5420</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,27 +1277,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 11444, Grönlif, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576985</v>
+        <v>576891</v>
       </c>
       <c r="R7" t="n">
-        <v>6379714</v>
+        <v>6379777</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1332,6 +1334,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1350,10 +1353,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123259312</v>
+        <v>123259498</v>
       </c>
       <c r="B8" t="n">
-        <v>98379</v>
+        <v>95167</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1362,33 +1365,29 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1398,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576990</v>
+        <v>576965</v>
       </c>
       <c r="R8" t="n">
-        <v>6379697</v>
+        <v>6379700</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,10 +1460,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123259460</v>
+        <v>123259628</v>
       </c>
       <c r="B9" t="n">
-        <v>92247</v>
+        <v>57857</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1477,44 +1476,49 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576977</v>
+        <v>576883</v>
       </c>
       <c r="R9" t="n">
-        <v>6379694</v>
+        <v>6379747</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1552,7 +1556,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1571,10 +1574,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123259993</v>
+        <v>123259392</v>
       </c>
       <c r="B10" t="n">
-        <v>90986</v>
+        <v>98396</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,38 +1586,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576929</v>
+        <v>576988</v>
       </c>
       <c r="R10" t="n">
-        <v>6379832</v>
+        <v>6379698</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1685,10 +1685,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123259828</v>
+        <v>123260011</v>
       </c>
       <c r="B11" t="n">
-        <v>90966</v>
+        <v>90983</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,10 +1736,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576838</v>
+        <v>576847</v>
       </c>
       <c r="R11" t="n">
-        <v>6379654</v>
+        <v>6379709</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1799,10 +1799,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123259362</v>
+        <v>123259993</v>
       </c>
       <c r="B12" t="n">
-        <v>98379</v>
+        <v>91003</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,35 +1811,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1847,10 +1850,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576989</v>
+        <v>576929</v>
       </c>
       <c r="R12" t="n">
-        <v>6379691</v>
+        <v>6379832</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1910,10 +1913,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123259498</v>
+        <v>123259312</v>
       </c>
       <c r="B13" t="n">
-        <v>95150</v>
+        <v>98396</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1922,29 +1925,33 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1954,10 +1961,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576965</v>
+        <v>576990</v>
       </c>
       <c r="R13" t="n">
-        <v>6379700</v>
+        <v>6379697</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2017,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123259392</v>
+        <v>123259460</v>
       </c>
       <c r="B14" t="n">
-        <v>98379</v>
+        <v>92264</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2029,35 +2036,34 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2065,10 +2071,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576988</v>
+        <v>576977</v>
       </c>
       <c r="R14" t="n">
-        <v>6379698</v>
+        <v>6379694</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2128,10 +2134,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123259157</v>
+        <v>123259440</v>
       </c>
       <c r="B15" t="n">
-        <v>57634</v>
+        <v>98396</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2140,39 +2146,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2180,13 +2182,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576997</v>
+        <v>576980</v>
       </c>
       <c r="R15" t="n">
-        <v>6379617</v>
+        <v>6379697</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2224,6 +2226,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2242,10 +2245,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123259471</v>
+        <v>123259419</v>
       </c>
       <c r="B16" t="n">
-        <v>98379</v>
+        <v>57640</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2254,35 +2257,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2290,13 +2297,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576971</v>
+        <v>576985</v>
       </c>
       <c r="R16" t="n">
-        <v>6379688</v>
+        <v>6379714</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2334,7 +2341,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2353,10 +2359,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123259974</v>
+        <v>123259271</v>
       </c>
       <c r="B17" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2397,14 +2403,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444. Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576950</v>
+        <v>576994</v>
       </c>
       <c r="R17" t="n">
-        <v>6379824</v>
+        <v>6379690</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2464,10 +2470,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123260939</v>
+        <v>123259157</v>
       </c>
       <c r="B18" t="n">
-        <v>98379</v>
+        <v>57640</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2476,35 +2482,39 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2512,13 +2522,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576951</v>
+        <v>576997</v>
       </c>
       <c r="R18" t="n">
-        <v>6379805</v>
+        <v>6379617</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2556,7 +2566,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2575,10 +2584,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123259209</v>
+        <v>123259930</v>
       </c>
       <c r="B19" t="n">
-        <v>90966</v>
+        <v>98396</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2587,38 +2596,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2626,10 +2632,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576992</v>
+        <v>576949</v>
       </c>
       <c r="R19" t="n">
-        <v>6379660</v>
+        <v>6379790</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2689,10 +2695,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123260011</v>
+        <v>123259332</v>
       </c>
       <c r="B20" t="n">
-        <v>90966</v>
+        <v>98396</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2701,38 +2707,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2740,10 +2743,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576847</v>
+        <v>576987</v>
       </c>
       <c r="R20" t="n">
-        <v>6379709</v>
+        <v>6379692</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2806,7 +2809,7 @@
         <v>123259882</v>
       </c>
       <c r="B21" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2918,10 +2921,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123259910</v>
+        <v>123259554</v>
       </c>
       <c r="B22" t="n">
-        <v>91376</v>
+        <v>105502</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2934,34 +2937,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5420</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>576891</v>
       </c>
       <c r="R22" t="n">
-        <v>6379777</v>
+        <v>6379769</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3032,10 +3032,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123259111</v>
+        <v>123259974</v>
       </c>
       <c r="B23" t="n">
-        <v>92247</v>
+        <v>98396</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3044,38 +3044,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3083,10 +3080,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577001</v>
+        <v>576950</v>
       </c>
       <c r="R23" t="n">
-        <v>6379581</v>
+        <v>6379824</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3146,10 +3143,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123259522</v>
+        <v>123259851</v>
       </c>
       <c r="B24" t="n">
-        <v>98379</v>
+        <v>90983</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3158,35 +3155,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>576971</v>
+        <v>576835</v>
       </c>
       <c r="R24" t="n">
         <v>6379715</v>
@@ -3257,10 +3257,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123259851</v>
+        <v>123259471</v>
       </c>
       <c r="B25" t="n">
-        <v>90966</v>
+        <v>98396</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3269,49 +3269,46 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444, Grönlif, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>576835</v>
+        <v>576971</v>
       </c>
       <c r="R25" t="n">
-        <v>6379715</v>
+        <v>6379688</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3371,10 +3368,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123259440</v>
+        <v>123259948</v>
       </c>
       <c r="B26" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3419,10 +3416,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>576980</v>
+        <v>576939</v>
       </c>
       <c r="R26" t="n">
-        <v>6379697</v>
+        <v>6379798</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3482,10 +3479,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123259131</v>
+        <v>123259183</v>
       </c>
       <c r="B27" t="n">
-        <v>92247</v>
+        <v>92264</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3533,10 +3530,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577009</v>
+        <v>577000</v>
       </c>
       <c r="R27" t="n">
-        <v>6379596</v>
+        <v>6379640</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3596,10 +3593,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123259554</v>
+        <v>123259131</v>
       </c>
       <c r="B28" t="n">
-        <v>105485</v>
+        <v>92264</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3612,31 +3609,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3644,10 +3644,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>576891</v>
+        <v>577009</v>
       </c>
       <c r="R28" t="n">
-        <v>6379769</v>
+        <v>6379596</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3707,10 +3707,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123259930</v>
+        <v>123259111</v>
       </c>
       <c r="B29" t="n">
-        <v>98379</v>
+        <v>92264</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3719,35 +3719,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3755,10 +3758,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>576949</v>
+        <v>577001</v>
       </c>
       <c r="R29" t="n">
-        <v>6379790</v>
+        <v>6379581</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3818,10 +3821,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123259084</v>
+        <v>123259522</v>
       </c>
       <c r="B30" t="n">
-        <v>92275</v>
+        <v>98396</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3830,49 +3833,46 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>A 11444, Grönled, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577012</v>
+        <v>576971</v>
       </c>
       <c r="R30" t="n">
-        <v>6379533</v>
+        <v>6379715</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3932,10 +3932,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123312935</v>
+        <v>123313080</v>
       </c>
       <c r="B31" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3966,11 +3966,7 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
@@ -3980,10 +3976,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>576793</v>
+        <v>576640</v>
       </c>
       <c r="R31" t="n">
-        <v>6379822</v>
+        <v>6379941</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4043,10 +4039,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123313080</v>
+        <v>123312524</v>
       </c>
       <c r="B32" t="n">
-        <v>98379</v>
+        <v>92264</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4055,31 +4051,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4087,10 +4090,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>576640</v>
+        <v>576731</v>
       </c>
       <c r="R32" t="n">
-        <v>6379941</v>
+        <v>6379842</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4120,9 +4123,19 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4150,10 +4163,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123312958</v>
+        <v>123312993</v>
       </c>
       <c r="B33" t="n">
-        <v>105485</v>
+        <v>91003</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4162,35 +4175,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4261,10 +4277,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123312773</v>
+        <v>123312502</v>
       </c>
       <c r="B34" t="n">
-        <v>105485</v>
+        <v>95167</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4277,29 +4293,25 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
@@ -4309,10 +4321,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>576839</v>
+        <v>576740</v>
       </c>
       <c r="R34" t="n">
-        <v>6379721</v>
+        <v>6379855</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4342,9 +4354,19 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4372,10 +4394,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123312896</v>
+        <v>123312486</v>
       </c>
       <c r="B35" t="n">
-        <v>105485</v>
+        <v>57857</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4388,31 +4410,35 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4420,13 +4446,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>576804</v>
+        <v>576693</v>
       </c>
       <c r="R35" t="n">
-        <v>6379845</v>
+        <v>6379898</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4453,18 +4479,27 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4483,10 +4518,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123313052</v>
+        <v>123312808</v>
       </c>
       <c r="B36" t="n">
-        <v>91376</v>
+        <v>97350</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4499,21 +4534,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5420</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4523,10 +4558,11 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4534,10 +4570,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>576677</v>
+        <v>576804</v>
       </c>
       <c r="R36" t="n">
-        <v>6379959</v>
+        <v>6379891</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4597,10 +4633,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123313086</v>
+        <v>123312935</v>
       </c>
       <c r="B37" t="n">
-        <v>57851</v>
+        <v>98396</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4609,39 +4645,35 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4649,10 +4681,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>576640</v>
+        <v>576793</v>
       </c>
       <c r="R37" t="n">
-        <v>6379941</v>
+        <v>6379822</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4693,6 +4725,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4711,10 +4744,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123312904</v>
+        <v>123312753</v>
       </c>
       <c r="B38" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4759,10 +4792,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>576804</v>
+        <v>576835</v>
       </c>
       <c r="R38" t="n">
-        <v>6379845</v>
+        <v>6379711</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4822,10 +4855,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123313124</v>
+        <v>123312569</v>
       </c>
       <c r="B39" t="n">
-        <v>98379</v>
+        <v>105502</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4834,25 +4867,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4870,10 +4903,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>576507</v>
+        <v>576803</v>
       </c>
       <c r="R39" t="n">
-        <v>6379922</v>
+        <v>6379887</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4903,9 +4936,19 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4933,10 +4976,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123312808</v>
+        <v>123312896</v>
       </c>
       <c r="B40" t="n">
-        <v>97333</v>
+        <v>105502</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4949,31 +4992,27 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -4988,7 +5027,7 @@
         <v>576804</v>
       </c>
       <c r="R40" t="n">
-        <v>6379891</v>
+        <v>6379845</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5048,10 +5087,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123313044</v>
+        <v>123313052</v>
       </c>
       <c r="B41" t="n">
-        <v>91376</v>
+        <v>91393</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5083,7 +5122,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5099,10 +5138,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>576690</v>
+        <v>576677</v>
       </c>
       <c r="R41" t="n">
-        <v>6379955</v>
+        <v>6379959</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5162,10 +5201,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123312540</v>
+        <v>123313086</v>
       </c>
       <c r="B42" t="n">
-        <v>57851</v>
+        <v>57857</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5214,13 +5253,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>576808</v>
+        <v>576640</v>
       </c>
       <c r="R42" t="n">
-        <v>6379847</v>
+        <v>6379941</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5247,19 +5286,9 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>15:50</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5286,10 +5315,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123312502</v>
+        <v>123312921</v>
       </c>
       <c r="B43" t="n">
-        <v>95150</v>
+        <v>98396</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5298,29 +5327,33 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
@@ -5330,10 +5363,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>576740</v>
+        <v>576799</v>
       </c>
       <c r="R43" t="n">
-        <v>6379855</v>
+        <v>6379827</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5363,19 +5396,9 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>15:50</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5403,10 +5426,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123312524</v>
+        <v>123312540</v>
       </c>
       <c r="B44" t="n">
-        <v>92247</v>
+        <v>57857</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5419,34 +5442,35 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5454,13 +5478,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>576731</v>
+        <v>576808</v>
       </c>
       <c r="R44" t="n">
-        <v>6379842</v>
+        <v>6379847</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5508,7 +5532,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5527,10 +5550,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123312569</v>
+        <v>123313044</v>
       </c>
       <c r="B45" t="n">
-        <v>105485</v>
+        <v>91393</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5543,31 +5566,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221144</v>
+        <v>5420</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5575,10 +5601,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>576803</v>
+        <v>576690</v>
       </c>
       <c r="R45" t="n">
-        <v>6379887</v>
+        <v>6379955</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5608,19 +5634,9 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>15:50</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5651,7 +5667,7 @@
         <v>123313067</v>
       </c>
       <c r="B46" t="n">
-        <v>90986</v>
+        <v>91003</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5762,10 +5778,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123312921</v>
+        <v>123312773</v>
       </c>
       <c r="B47" t="n">
-        <v>98379</v>
+        <v>105502</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5774,25 +5790,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5810,10 +5826,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>576799</v>
+        <v>576839</v>
       </c>
       <c r="R47" t="n">
-        <v>6379827</v>
+        <v>6379721</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5873,10 +5889,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123312753</v>
+        <v>123312958</v>
       </c>
       <c r="B48" t="n">
-        <v>98379</v>
+        <v>105502</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5885,25 +5901,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5921,10 +5937,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>576835</v>
+        <v>576745</v>
       </c>
       <c r="R48" t="n">
-        <v>6379711</v>
+        <v>6379872</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5984,10 +6000,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123312993</v>
+        <v>123313124</v>
       </c>
       <c r="B49" t="n">
-        <v>90986</v>
+        <v>98396</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5996,38 +6012,35 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6035,10 +6048,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>576745</v>
+        <v>576507</v>
       </c>
       <c r="R49" t="n">
-        <v>6379872</v>
+        <v>6379922</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6098,10 +6111,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123312486</v>
+        <v>123312904</v>
       </c>
       <c r="B50" t="n">
-        <v>57851</v>
+        <v>98396</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6110,39 +6123,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6150,13 +6159,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>576693</v>
+        <v>576804</v>
       </c>
       <c r="R50" t="n">
-        <v>6379898</v>
+        <v>6379845</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6183,27 +6192,18 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11444-2025 artfynd.xlsx
+++ b/artfynd/A 11444-2025 artfynd.xlsx
@@ -3593,10 +3593,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123259131</v>
+        <v>123259522</v>
       </c>
       <c r="B28" t="n">
-        <v>92264</v>
+        <v>98396</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3605,38 +3605,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3644,10 +3641,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577009</v>
+        <v>576971</v>
       </c>
       <c r="R28" t="n">
-        <v>6379596</v>
+        <v>6379715</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3707,7 +3704,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123259111</v>
+        <v>123259131</v>
       </c>
       <c r="B29" t="n">
         <v>92264</v>
@@ -3742,7 +3739,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3758,10 +3755,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577001</v>
+        <v>577009</v>
       </c>
       <c r="R29" t="n">
-        <v>6379581</v>
+        <v>6379596</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3821,10 +3818,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123259522</v>
+        <v>123259111</v>
       </c>
       <c r="B30" t="n">
-        <v>98396</v>
+        <v>92264</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3833,35 +3830,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3869,10 +3869,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>576971</v>
+        <v>577001</v>
       </c>
       <c r="R30" t="n">
-        <v>6379715</v>
+        <v>6379581</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -5201,10 +5201,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123313086</v>
+        <v>123312921</v>
       </c>
       <c r="B42" t="n">
-        <v>57857</v>
+        <v>98396</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5213,39 +5213,35 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5253,10 +5249,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>576640</v>
+        <v>576799</v>
       </c>
       <c r="R42" t="n">
-        <v>6379941</v>
+        <v>6379827</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5297,6 +5293,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5315,10 +5312,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123312921</v>
+        <v>123313086</v>
       </c>
       <c r="B43" t="n">
-        <v>98396</v>
+        <v>57857</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5327,35 +5324,39 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5363,10 +5364,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>576799</v>
+        <v>576640</v>
       </c>
       <c r="R43" t="n">
-        <v>6379827</v>
+        <v>6379941</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5407,7 +5408,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11444-2025 artfynd.xlsx
+++ b/artfynd/A 11444-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123259828</v>
+        <v>123259362</v>
       </c>
       <c r="B2" t="n">
-        <v>90983</v>
+        <v>98396</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576838</v>
+        <v>576989</v>
       </c>
       <c r="R2" t="n">
-        <v>6379654</v>
+        <v>6379691</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123259209</v>
+        <v>123260939</v>
       </c>
       <c r="B3" t="n">
-        <v>90983</v>
+        <v>98396</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,38 +798,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576992</v>
+        <v>576951</v>
       </c>
       <c r="R3" t="n">
-        <v>6379660</v>
+        <v>6379805</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123259362</v>
+        <v>123259828</v>
       </c>
       <c r="B4" t="n">
-        <v>98396</v>
+        <v>90983</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,35 +909,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576989</v>
+        <v>576838</v>
       </c>
       <c r="R4" t="n">
-        <v>6379691</v>
+        <v>6379654</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123260939</v>
+        <v>123259209</v>
       </c>
       <c r="B5" t="n">
-        <v>98396</v>
+        <v>90983</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,35 +1023,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576951</v>
+        <v>576992</v>
       </c>
       <c r="R5" t="n">
-        <v>6379805</v>
+        <v>6379660</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123259628</v>
+        <v>123260011</v>
       </c>
       <c r="B9" t="n">
-        <v>57857</v>
+        <v>90983</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1472,25 +1472,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1498,27 +1498,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A11444, Grönlid, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576883</v>
+        <v>576847</v>
       </c>
       <c r="R9" t="n">
-        <v>6379747</v>
+        <v>6379709</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1556,6 +1555,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1574,10 +1574,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123259392</v>
+        <v>123259993</v>
       </c>
       <c r="B10" t="n">
-        <v>98396</v>
+        <v>91003</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1586,35 +1586,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1622,10 +1625,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576988</v>
+        <v>576929</v>
       </c>
       <c r="R10" t="n">
-        <v>6379698</v>
+        <v>6379832</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1685,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123260011</v>
+        <v>123259628</v>
       </c>
       <c r="B11" t="n">
-        <v>90983</v>
+        <v>57857</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1697,25 +1700,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1723,26 +1726,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576847</v>
+        <v>576883</v>
       </c>
       <c r="R11" t="n">
-        <v>6379709</v>
+        <v>6379747</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1780,7 +1784,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1799,10 +1802,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123259993</v>
+        <v>123259392</v>
       </c>
       <c r="B12" t="n">
-        <v>91003</v>
+        <v>98396</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,38 +1814,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1850,10 +1850,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576929</v>
+        <v>576988</v>
       </c>
       <c r="R12" t="n">
-        <v>6379832</v>
+        <v>6379698</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -4976,10 +4976,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123312896</v>
+        <v>123313052</v>
       </c>
       <c r="B40" t="n">
-        <v>105502</v>
+        <v>91393</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4992,31 +4992,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221144</v>
+        <v>5420</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5024,10 +5027,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>576804</v>
+        <v>576677</v>
       </c>
       <c r="R40" t="n">
-        <v>6379845</v>
+        <v>6379959</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5087,10 +5090,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123313052</v>
+        <v>123312896</v>
       </c>
       <c r="B41" t="n">
-        <v>91393</v>
+        <v>105502</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5103,34 +5106,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5420</v>
+        <v>221144</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5138,10 +5138,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>576677</v>
+        <v>576804</v>
       </c>
       <c r="R41" t="n">
-        <v>6379959</v>
+        <v>6379845</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5201,10 +5201,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123312921</v>
+        <v>123313086</v>
       </c>
       <c r="B42" t="n">
-        <v>98396</v>
+        <v>57857</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5213,35 +5213,39 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5249,10 +5253,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>576799</v>
+        <v>576640</v>
       </c>
       <c r="R42" t="n">
-        <v>6379827</v>
+        <v>6379941</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5293,7 +5297,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5312,10 +5315,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123313086</v>
+        <v>123312921</v>
       </c>
       <c r="B43" t="n">
-        <v>57857</v>
+        <v>98396</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5324,39 +5327,35 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5364,10 +5363,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>576640</v>
+        <v>576799</v>
       </c>
       <c r="R43" t="n">
-        <v>6379941</v>
+        <v>6379827</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5408,6 +5407,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11444-2025 artfynd.xlsx
+++ b/artfynd/A 11444-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123259362</v>
+        <v>123259828</v>
       </c>
       <c r="B2" t="n">
-        <v>98396</v>
+        <v>90983</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576989</v>
+        <v>576838</v>
       </c>
       <c r="R2" t="n">
-        <v>6379691</v>
+        <v>6379654</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123260939</v>
+        <v>123259209</v>
       </c>
       <c r="B3" t="n">
-        <v>98396</v>
+        <v>90983</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,35 +801,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576951</v>
+        <v>576992</v>
       </c>
       <c r="R3" t="n">
-        <v>6379805</v>
+        <v>6379660</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123259828</v>
+        <v>123259362</v>
       </c>
       <c r="B4" t="n">
-        <v>90983</v>
+        <v>98396</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,38 +915,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -948,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576838</v>
+        <v>576989</v>
       </c>
       <c r="R4" t="n">
-        <v>6379654</v>
+        <v>6379691</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123259209</v>
+        <v>123260939</v>
       </c>
       <c r="B5" t="n">
-        <v>90983</v>
+        <v>98396</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,38 +1026,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576992</v>
+        <v>576951</v>
       </c>
       <c r="R5" t="n">
-        <v>6379660</v>
+        <v>6379805</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123260011</v>
+        <v>123259628</v>
       </c>
       <c r="B9" t="n">
-        <v>90983</v>
+        <v>57857</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1472,25 +1472,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1498,26 +1498,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576847</v>
+        <v>576883</v>
       </c>
       <c r="R9" t="n">
-        <v>6379709</v>
+        <v>6379747</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1555,7 +1556,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1574,10 +1574,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123259993</v>
+        <v>123259392</v>
       </c>
       <c r="B10" t="n">
-        <v>91003</v>
+        <v>98396</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1586,38 +1586,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1625,10 +1622,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576929</v>
+        <v>576988</v>
       </c>
       <c r="R10" t="n">
-        <v>6379832</v>
+        <v>6379698</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1688,10 +1685,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123259628</v>
+        <v>123260011</v>
       </c>
       <c r="B11" t="n">
-        <v>57857</v>
+        <v>90983</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1700,25 +1697,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1726,27 +1723,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A11444, Grönlid, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576883</v>
+        <v>576847</v>
       </c>
       <c r="R11" t="n">
-        <v>6379747</v>
+        <v>6379709</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1784,6 +1780,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1802,10 +1799,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123259392</v>
+        <v>123259993</v>
       </c>
       <c r="B12" t="n">
-        <v>98396</v>
+        <v>91003</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1814,35 +1811,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1850,10 +1850,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576988</v>
+        <v>576929</v>
       </c>
       <c r="R12" t="n">
-        <v>6379698</v>
+        <v>6379832</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2806,10 +2806,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123259882</v>
+        <v>123259554</v>
       </c>
       <c r="B21" t="n">
-        <v>57503</v>
+        <v>105502</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2818,35 +2818,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2854,10 +2854,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>576832</v>
+        <v>576891</v>
       </c>
       <c r="R21" t="n">
-        <v>6379712</v>
+        <v>6379769</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2892,17 +2892,13 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Bearbetat torrträd</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2921,10 +2917,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123259554</v>
+        <v>123259882</v>
       </c>
       <c r="B22" t="n">
-        <v>105502</v>
+        <v>57503</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2933,35 +2929,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2969,10 +2965,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576891</v>
+        <v>576832</v>
       </c>
       <c r="R22" t="n">
-        <v>6379769</v>
+        <v>6379712</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3007,13 +3003,17 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Bearbetat torrträd</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -4976,10 +4976,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123313052</v>
+        <v>123312896</v>
       </c>
       <c r="B40" t="n">
-        <v>91393</v>
+        <v>105502</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4992,34 +4992,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5420</v>
+        <v>221144</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5027,10 +5024,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>576677</v>
+        <v>576804</v>
       </c>
       <c r="R40" t="n">
-        <v>6379959</v>
+        <v>6379845</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5090,10 +5087,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123312896</v>
+        <v>123313052</v>
       </c>
       <c r="B41" t="n">
-        <v>105502</v>
+        <v>91393</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5106,31 +5103,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221144</v>
+        <v>5420</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5138,10 +5138,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>576804</v>
+        <v>576677</v>
       </c>
       <c r="R41" t="n">
-        <v>6379845</v>
+        <v>6379959</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5201,10 +5201,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123313086</v>
+        <v>123312921</v>
       </c>
       <c r="B42" t="n">
-        <v>57857</v>
+        <v>98396</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5213,39 +5213,35 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5253,10 +5249,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>576640</v>
+        <v>576799</v>
       </c>
       <c r="R42" t="n">
-        <v>6379941</v>
+        <v>6379827</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5297,6 +5293,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5315,10 +5312,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123312921</v>
+        <v>123313086</v>
       </c>
       <c r="B43" t="n">
-        <v>98396</v>
+        <v>57857</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5327,35 +5324,39 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5363,10 +5364,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>576799</v>
+        <v>576640</v>
       </c>
       <c r="R43" t="n">
-        <v>6379827</v>
+        <v>6379941</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5407,7 +5408,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11444-2025 artfynd.xlsx
+++ b/artfynd/A 11444-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123259828</v>
+        <v>123259498</v>
       </c>
       <c r="B2" t="n">
-        <v>90983</v>
+        <v>95173</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576838</v>
+        <v>576965</v>
       </c>
       <c r="R2" t="n">
-        <v>6379654</v>
+        <v>6379700</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123259209</v>
+        <v>123259312</v>
       </c>
       <c r="B3" t="n">
-        <v>90983</v>
+        <v>98502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,38 +794,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576992</v>
+        <v>576990</v>
       </c>
       <c r="R3" t="n">
-        <v>6379660</v>
+        <v>6379697</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123259362</v>
+        <v>123259974</v>
       </c>
       <c r="B4" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576989</v>
+        <v>576950</v>
       </c>
       <c r="R4" t="n">
-        <v>6379691</v>
+        <v>6379824</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123260939</v>
+        <v>123259554</v>
       </c>
       <c r="B5" t="n">
-        <v>98396</v>
+        <v>105518</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,25 +1016,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1062,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576951</v>
+        <v>576891</v>
       </c>
       <c r="R5" t="n">
-        <v>6379805</v>
+        <v>6379769</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123259084</v>
+        <v>123259948</v>
       </c>
       <c r="B6" t="n">
-        <v>92292</v>
+        <v>98502</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,49 +1127,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 11444, Grönled, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577012</v>
+        <v>576939</v>
       </c>
       <c r="R6" t="n">
-        <v>6379533</v>
+        <v>6379798</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1239,10 +1226,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123259910</v>
+        <v>123259628</v>
       </c>
       <c r="B7" t="n">
-        <v>91393</v>
+        <v>57860</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1255,21 +1242,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5420</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1277,26 +1264,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576891</v>
+        <v>576883</v>
       </c>
       <c r="R7" t="n">
-        <v>6379777</v>
+        <v>6379747</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1334,7 +1322,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1353,10 +1340,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123259498</v>
+        <v>123259157</v>
       </c>
       <c r="B8" t="n">
-        <v>95167</v>
+        <v>57643</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1365,31 +1352,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1397,13 +1392,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576965</v>
+        <v>576997</v>
       </c>
       <c r="R8" t="n">
-        <v>6379700</v>
+        <v>6379617</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1441,7 +1436,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1460,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123259628</v>
+        <v>123259522</v>
       </c>
       <c r="B9" t="n">
-        <v>57857</v>
+        <v>98502</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1472,53 +1466,49 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A11444, Grönlid, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576883</v>
+        <v>576971</v>
       </c>
       <c r="R9" t="n">
-        <v>6379747</v>
+        <v>6379715</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1556,6 +1546,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1574,10 +1565,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123259392</v>
+        <v>123259993</v>
       </c>
       <c r="B10" t="n">
-        <v>98396</v>
+        <v>91008</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1586,35 +1577,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1622,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576988</v>
+        <v>576929</v>
       </c>
       <c r="R10" t="n">
-        <v>6379698</v>
+        <v>6379832</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1685,10 +1679,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123260011</v>
+        <v>123259910</v>
       </c>
       <c r="B11" t="n">
-        <v>90983</v>
+        <v>91398</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1697,25 +1691,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>5420</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1725,7 +1719,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1736,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576847</v>
+        <v>576891</v>
       </c>
       <c r="R11" t="n">
-        <v>6379709</v>
+        <v>6379777</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1799,10 +1793,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123259993</v>
+        <v>123259828</v>
       </c>
       <c r="B12" t="n">
-        <v>91003</v>
+        <v>90988</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1815,21 +1809,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1839,7 +1833,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1850,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576929</v>
+        <v>576838</v>
       </c>
       <c r="R12" t="n">
-        <v>6379832</v>
+        <v>6379654</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1913,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123259312</v>
+        <v>123259392</v>
       </c>
       <c r="B13" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1961,10 +1955,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576990</v>
+        <v>576988</v>
       </c>
       <c r="R13" t="n">
-        <v>6379697</v>
+        <v>6379698</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2027,7 +2021,7 @@
         <v>123259460</v>
       </c>
       <c r="B14" t="n">
-        <v>92264</v>
+        <v>92269</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2134,10 +2128,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123259440</v>
+        <v>123259362</v>
       </c>
       <c r="B15" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2182,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576980</v>
+        <v>576989</v>
       </c>
       <c r="R15" t="n">
-        <v>6379697</v>
+        <v>6379691</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2245,10 +2239,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123259419</v>
+        <v>123259332</v>
       </c>
       <c r="B16" t="n">
-        <v>57640</v>
+        <v>98502</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2257,53 +2251,49 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>A 11444, Grönlif, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576985</v>
+        <v>576987</v>
       </c>
       <c r="R16" t="n">
-        <v>6379714</v>
+        <v>6379692</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2341,6 +2331,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2359,10 +2350,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123259271</v>
+        <v>123260939</v>
       </c>
       <c r="B17" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2403,14 +2394,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A 11444. Grönlid, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576994</v>
+        <v>576951</v>
       </c>
       <c r="R17" t="n">
-        <v>6379690</v>
+        <v>6379805</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2470,10 +2461,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123259157</v>
+        <v>123259111</v>
       </c>
       <c r="B18" t="n">
-        <v>57640</v>
+        <v>92269</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2482,39 +2473,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2522,13 +2512,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576997</v>
+        <v>577001</v>
       </c>
       <c r="R18" t="n">
-        <v>6379617</v>
+        <v>6379581</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2566,6 +2556,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2584,10 +2575,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123259930</v>
+        <v>123259209</v>
       </c>
       <c r="B19" t="n">
-        <v>98396</v>
+        <v>90988</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2596,35 +2587,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2632,10 +2626,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576949</v>
+        <v>576992</v>
       </c>
       <c r="R19" t="n">
-        <v>6379790</v>
+        <v>6379660</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2695,10 +2689,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123259332</v>
+        <v>123259851</v>
       </c>
       <c r="B20" t="n">
-        <v>98396</v>
+        <v>90988</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2707,35 +2701,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2743,10 +2740,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576987</v>
+        <v>576835</v>
       </c>
       <c r="R20" t="n">
-        <v>6379692</v>
+        <v>6379715</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2806,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123259554</v>
+        <v>123259440</v>
       </c>
       <c r="B21" t="n">
-        <v>105502</v>
+        <v>98502</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2818,25 +2815,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2854,10 +2851,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>576891</v>
+        <v>576980</v>
       </c>
       <c r="R21" t="n">
-        <v>6379769</v>
+        <v>6379697</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2917,10 +2914,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123259882</v>
+        <v>123259419</v>
       </c>
       <c r="B22" t="n">
-        <v>57503</v>
+        <v>57643</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2933,45 +2930,49 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444, Grönlif, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576832</v>
+        <v>576985</v>
       </c>
       <c r="R22" t="n">
-        <v>6379712</v>
+        <v>6379714</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3001,11 +3002,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Bearbetat torrträd</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3032,10 +3028,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123259974</v>
+        <v>123259930</v>
       </c>
       <c r="B23" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3080,10 +3076,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576950</v>
+        <v>576949</v>
       </c>
       <c r="R23" t="n">
-        <v>6379824</v>
+        <v>6379790</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3143,10 +3139,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123259851</v>
+        <v>123259271</v>
       </c>
       <c r="B24" t="n">
-        <v>90983</v>
+        <v>98502</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3155,49 +3151,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444. Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>576835</v>
+        <v>576994</v>
       </c>
       <c r="R24" t="n">
-        <v>6379715</v>
+        <v>6379690</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3257,10 +3250,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123259471</v>
+        <v>123259084</v>
       </c>
       <c r="B25" t="n">
-        <v>98396</v>
+        <v>92297</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3269,46 +3262,49 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>A 11444, Grönlif, Sm</t>
+          <t>A 11444, Grönled, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>576971</v>
+        <v>577012</v>
       </c>
       <c r="R25" t="n">
-        <v>6379688</v>
+        <v>6379533</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3368,10 +3364,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123259948</v>
+        <v>123259882</v>
       </c>
       <c r="B26" t="n">
-        <v>98396</v>
+        <v>57506</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3380,35 +3376,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3416,10 +3412,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>576939</v>
+        <v>576832</v>
       </c>
       <c r="R26" t="n">
-        <v>6379798</v>
+        <v>6379712</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3454,13 +3450,17 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Bearbetat torrträd</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3479,10 +3479,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123259183</v>
+        <v>123259471</v>
       </c>
       <c r="B27" t="n">
-        <v>92264</v>
+        <v>98502</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3491,49 +3491,46 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444, Grönlif, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577000</v>
+        <v>576971</v>
       </c>
       <c r="R27" t="n">
-        <v>6379640</v>
+        <v>6379688</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3593,10 +3590,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123259522</v>
+        <v>123259183</v>
       </c>
       <c r="B28" t="n">
-        <v>98396</v>
+        <v>92269</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3605,35 +3602,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>576971</v>
+        <v>577000</v>
       </c>
       <c r="R28" t="n">
-        <v>6379715</v>
+        <v>6379640</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3704,10 +3704,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123259131</v>
+        <v>123260011</v>
       </c>
       <c r="B29" t="n">
-        <v>92264</v>
+        <v>90988</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3716,25 +3716,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -3755,10 +3755,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577009</v>
+        <v>576847</v>
       </c>
       <c r="R29" t="n">
-        <v>6379596</v>
+        <v>6379709</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3818,10 +3818,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123259111</v>
+        <v>123259131</v>
       </c>
       <c r="B30" t="n">
-        <v>92264</v>
+        <v>92269</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3869,10 +3869,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577001</v>
+        <v>577009</v>
       </c>
       <c r="R30" t="n">
-        <v>6379581</v>
+        <v>6379596</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3932,10 +3932,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123313080</v>
+        <v>123313086</v>
       </c>
       <c r="B31" t="n">
-        <v>98396</v>
+        <v>57860</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3944,31 +3944,39 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4020,7 +4028,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4039,10 +4046,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123312524</v>
+        <v>123313080</v>
       </c>
       <c r="B32" t="n">
-        <v>92264</v>
+        <v>98502</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4051,38 +4058,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>576731</v>
+        <v>576640</v>
       </c>
       <c r="R32" t="n">
-        <v>6379842</v>
+        <v>6379941</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4123,19 +4123,9 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>15:50</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4163,10 +4153,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123312993</v>
+        <v>123313124</v>
       </c>
       <c r="B33" t="n">
-        <v>91003</v>
+        <v>98502</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4175,38 +4165,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4214,10 +4201,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>576745</v>
+        <v>576507</v>
       </c>
       <c r="R33" t="n">
-        <v>6379872</v>
+        <v>6379922</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4277,10 +4264,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123312502</v>
+        <v>123313067</v>
       </c>
       <c r="B34" t="n">
-        <v>95167</v>
+        <v>91008</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4289,31 +4276,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4321,10 +4315,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>576740</v>
+        <v>576682</v>
       </c>
       <c r="R34" t="n">
-        <v>6379855</v>
+        <v>6379963</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4354,19 +4348,9 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>15:50</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4394,10 +4378,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123312486</v>
+        <v>123312896</v>
       </c>
       <c r="B35" t="n">
-        <v>57857</v>
+        <v>105518</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4410,35 +4394,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4446,13 +4426,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>576693</v>
+        <v>576804</v>
       </c>
       <c r="R35" t="n">
-        <v>6379898</v>
+        <v>6379845</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4479,27 +4459,18 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4518,10 +4489,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123312808</v>
+        <v>123312958</v>
       </c>
       <c r="B36" t="n">
-        <v>97350</v>
+        <v>105518</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4534,31 +4505,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -4570,10 +4537,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>576804</v>
+        <v>576745</v>
       </c>
       <c r="R36" t="n">
-        <v>6379891</v>
+        <v>6379872</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4633,10 +4600,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123312935</v>
+        <v>123312502</v>
       </c>
       <c r="B37" t="n">
-        <v>98396</v>
+        <v>95173</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4645,33 +4612,29 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
@@ -4681,10 +4644,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>576793</v>
+        <v>576740</v>
       </c>
       <c r="R37" t="n">
-        <v>6379822</v>
+        <v>6379855</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4714,9 +4677,19 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4744,10 +4717,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123312753</v>
+        <v>123312524</v>
       </c>
       <c r="B38" t="n">
-        <v>98396</v>
+        <v>92269</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4756,35 +4729,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4792,10 +4768,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>576835</v>
+        <v>576731</v>
       </c>
       <c r="R38" t="n">
-        <v>6379711</v>
+        <v>6379842</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4825,9 +4801,19 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4855,10 +4841,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123312569</v>
+        <v>123312935</v>
       </c>
       <c r="B39" t="n">
-        <v>105502</v>
+        <v>98502</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4867,25 +4853,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4903,10 +4889,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>576803</v>
+        <v>576793</v>
       </c>
       <c r="R39" t="n">
-        <v>6379887</v>
+        <v>6379822</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4936,19 +4922,9 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>15:50</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4976,10 +4952,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123312896</v>
+        <v>123312486</v>
       </c>
       <c r="B40" t="n">
-        <v>105502</v>
+        <v>57860</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4992,31 +4968,35 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5024,13 +5004,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>576804</v>
+        <v>576693</v>
       </c>
       <c r="R40" t="n">
-        <v>6379845</v>
+        <v>6379898</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5057,18 +5037,27 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5087,10 +5076,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123313052</v>
+        <v>123313044</v>
       </c>
       <c r="B41" t="n">
-        <v>91393</v>
+        <v>91398</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5122,7 +5111,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5138,10 +5127,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>576677</v>
+        <v>576690</v>
       </c>
       <c r="R41" t="n">
-        <v>6379959</v>
+        <v>6379955</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5201,10 +5190,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123312921</v>
+        <v>123312773</v>
       </c>
       <c r="B42" t="n">
-        <v>98396</v>
+        <v>105518</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5213,25 +5202,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5249,10 +5238,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>576799</v>
+        <v>576839</v>
       </c>
       <c r="R42" t="n">
-        <v>6379827</v>
+        <v>6379721</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5312,10 +5301,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123313086</v>
+        <v>123312808</v>
       </c>
       <c r="B43" t="n">
-        <v>57857</v>
+        <v>97367</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5328,35 +5317,35 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5364,10 +5353,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>576640</v>
+        <v>576804</v>
       </c>
       <c r="R43" t="n">
-        <v>6379941</v>
+        <v>6379891</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5408,6 +5397,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5426,10 +5416,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123312540</v>
+        <v>123312921</v>
       </c>
       <c r="B44" t="n">
-        <v>57857</v>
+        <v>98502</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5438,39 +5428,35 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5478,13 +5464,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>576808</v>
+        <v>576799</v>
       </c>
       <c r="R44" t="n">
-        <v>6379847</v>
+        <v>6379827</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5511,27 +5497,18 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5550,10 +5527,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123313044</v>
+        <v>123312540</v>
       </c>
       <c r="B45" t="n">
-        <v>91393</v>
+        <v>57860</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5566,21 +5543,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5420</v>
+        <v>103015</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5588,12 +5565,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5601,13 +5579,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>576690</v>
+        <v>576808</v>
       </c>
       <c r="R45" t="n">
-        <v>6379955</v>
+        <v>6379847</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5634,18 +5612,27 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5664,10 +5651,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123313067</v>
+        <v>123312569</v>
       </c>
       <c r="B46" t="n">
-        <v>91003</v>
+        <v>105518</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5676,38 +5663,35 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5715,10 +5699,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>576682</v>
+        <v>576803</v>
       </c>
       <c r="R46" t="n">
-        <v>6379963</v>
+        <v>6379887</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5748,9 +5732,19 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5778,10 +5772,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123312773</v>
+        <v>123312904</v>
       </c>
       <c r="B47" t="n">
-        <v>105502</v>
+        <v>98502</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5790,25 +5784,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5826,10 +5820,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>576839</v>
+        <v>576804</v>
       </c>
       <c r="R47" t="n">
-        <v>6379721</v>
+        <v>6379845</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5889,10 +5883,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123312958</v>
+        <v>123313052</v>
       </c>
       <c r="B48" t="n">
-        <v>105502</v>
+        <v>91398</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5905,31 +5899,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221144</v>
+        <v>5420</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5937,10 +5934,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>576745</v>
+        <v>576677</v>
       </c>
       <c r="R48" t="n">
-        <v>6379872</v>
+        <v>6379959</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6000,10 +5997,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123313124</v>
+        <v>123312753</v>
       </c>
       <c r="B49" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6048,10 +6045,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>576507</v>
+        <v>576835</v>
       </c>
       <c r="R49" t="n">
-        <v>6379922</v>
+        <v>6379711</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6111,10 +6108,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123312904</v>
+        <v>123312993</v>
       </c>
       <c r="B50" t="n">
-        <v>98396</v>
+        <v>91008</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6123,35 +6120,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6159,10 +6159,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>576804</v>
+        <v>576745</v>
       </c>
       <c r="R50" t="n">
-        <v>6379845</v>
+        <v>6379872</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 11444-2025 artfynd.xlsx
+++ b/artfynd/A 11444-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123259498</v>
+        <v>123259993</v>
       </c>
       <c r="B2" t="n">
-        <v>95173</v>
+        <v>91010</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576965</v>
+        <v>576929</v>
       </c>
       <c r="R2" t="n">
-        <v>6379700</v>
+        <v>6379832</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123259312</v>
+        <v>123259828</v>
       </c>
       <c r="B3" t="n">
-        <v>98502</v>
+        <v>90990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,35 +801,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576990</v>
+        <v>576838</v>
       </c>
       <c r="R3" t="n">
-        <v>6379697</v>
+        <v>6379654</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123259974</v>
+        <v>123259460</v>
       </c>
       <c r="B4" t="n">
-        <v>98502</v>
+        <v>92271</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,35 +915,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -941,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576950</v>
+        <v>576977</v>
       </c>
       <c r="R4" t="n">
-        <v>6379824</v>
+        <v>6379694</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123259554</v>
+        <v>123259312</v>
       </c>
       <c r="B5" t="n">
-        <v>105518</v>
+        <v>98504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,25 +1025,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1052,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576891</v>
+        <v>576990</v>
       </c>
       <c r="R5" t="n">
-        <v>6379769</v>
+        <v>6379697</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123259948</v>
+        <v>123259498</v>
       </c>
       <c r="B6" t="n">
-        <v>98502</v>
+        <v>95175</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,33 +1136,29 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1163,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576939</v>
+        <v>576965</v>
       </c>
       <c r="R6" t="n">
-        <v>6379798</v>
+        <v>6379700</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,10 +1231,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123259628</v>
+        <v>123259332</v>
       </c>
       <c r="B7" t="n">
-        <v>57860</v>
+        <v>98504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1238,53 +1243,49 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A11444, Grönlid, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576883</v>
+        <v>576987</v>
       </c>
       <c r="R7" t="n">
-        <v>6379747</v>
+        <v>6379692</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1322,6 +1323,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1343,7 +1345,7 @@
         <v>123259157</v>
       </c>
       <c r="B8" t="n">
-        <v>57643</v>
+        <v>57644</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1454,10 +1456,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123259522</v>
+        <v>123259183</v>
       </c>
       <c r="B9" t="n">
-        <v>98502</v>
+        <v>92271</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1466,35 +1468,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1502,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576971</v>
+        <v>577000</v>
       </c>
       <c r="R9" t="n">
-        <v>6379715</v>
+        <v>6379640</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1565,10 +1570,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123259993</v>
+        <v>123259522</v>
       </c>
       <c r="B10" t="n">
-        <v>91008</v>
+        <v>98504</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1577,38 +1582,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1616,10 +1618,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576929</v>
+        <v>576971</v>
       </c>
       <c r="R10" t="n">
-        <v>6379832</v>
+        <v>6379715</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,10 +1681,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123259910</v>
+        <v>123259554</v>
       </c>
       <c r="B11" t="n">
-        <v>91398</v>
+        <v>105520</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,34 +1697,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5420</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1733,7 +1732,7 @@
         <v>576891</v>
       </c>
       <c r="R11" t="n">
-        <v>6379777</v>
+        <v>6379769</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1793,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123259828</v>
+        <v>123259930</v>
       </c>
       <c r="B12" t="n">
-        <v>90988</v>
+        <v>98504</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1805,38 +1804,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1844,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576838</v>
+        <v>576949</v>
       </c>
       <c r="R12" t="n">
-        <v>6379654</v>
+        <v>6379790</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,10 +1903,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123259392</v>
+        <v>123259419</v>
       </c>
       <c r="B13" t="n">
-        <v>98502</v>
+        <v>57644</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,49 +1915,53 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444, Grönlif, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576988</v>
+        <v>576985</v>
       </c>
       <c r="R13" t="n">
-        <v>6379698</v>
+        <v>6379714</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1999,7 +1999,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2018,10 +2017,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123259460</v>
+        <v>123259974</v>
       </c>
       <c r="B14" t="n">
-        <v>92269</v>
+        <v>98504</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2030,34 +2029,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2065,10 +2065,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576977</v>
+        <v>576950</v>
       </c>
       <c r="R14" t="n">
-        <v>6379694</v>
+        <v>6379824</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2128,10 +2128,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123259362</v>
+        <v>123259882</v>
       </c>
       <c r="B15" t="n">
-        <v>98502</v>
+        <v>57507</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2140,35 +2140,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2176,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576989</v>
+        <v>576832</v>
       </c>
       <c r="R15" t="n">
-        <v>6379691</v>
+        <v>6379712</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2214,13 +2214,17 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Bearbetat torrträd</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2239,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123259332</v>
+        <v>123259851</v>
       </c>
       <c r="B16" t="n">
-        <v>98502</v>
+        <v>90990</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2251,35 +2255,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2287,10 +2294,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576987</v>
+        <v>576835</v>
       </c>
       <c r="R16" t="n">
-        <v>6379692</v>
+        <v>6379715</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2350,10 +2357,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123260939</v>
+        <v>123259362</v>
       </c>
       <c r="B17" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2398,10 +2405,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576951</v>
+        <v>576989</v>
       </c>
       <c r="R17" t="n">
-        <v>6379805</v>
+        <v>6379691</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2461,10 +2468,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123259111</v>
+        <v>123259440</v>
       </c>
       <c r="B18" t="n">
-        <v>92269</v>
+        <v>98504</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2473,38 +2480,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2512,10 +2516,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577001</v>
+        <v>576980</v>
       </c>
       <c r="R18" t="n">
-        <v>6379581</v>
+        <v>6379697</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2575,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123259209</v>
+        <v>123259392</v>
       </c>
       <c r="B19" t="n">
-        <v>90988</v>
+        <v>98504</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2587,38 +2591,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2626,10 +2627,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576992</v>
+        <v>576988</v>
       </c>
       <c r="R19" t="n">
-        <v>6379660</v>
+        <v>6379698</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2689,10 +2690,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123259851</v>
+        <v>123259209</v>
       </c>
       <c r="B20" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2740,10 +2741,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576835</v>
+        <v>576992</v>
       </c>
       <c r="R20" t="n">
-        <v>6379715</v>
+        <v>6379660</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2803,10 +2804,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123259440</v>
+        <v>123259131</v>
       </c>
       <c r="B21" t="n">
-        <v>98502</v>
+        <v>92271</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2815,35 +2816,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2851,10 +2855,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>576980</v>
+        <v>577009</v>
       </c>
       <c r="R21" t="n">
-        <v>6379697</v>
+        <v>6379596</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2914,10 +2918,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123259419</v>
+        <v>123259628</v>
       </c>
       <c r="B22" t="n">
-        <v>57643</v>
+        <v>57861</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2926,25 +2930,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2956,20 +2960,20 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>A 11444, Grönlif, Sm</t>
+          <t>A11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576985</v>
+        <v>576883</v>
       </c>
       <c r="R22" t="n">
-        <v>6379714</v>
+        <v>6379747</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3028,10 +3032,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123259930</v>
+        <v>123259271</v>
       </c>
       <c r="B23" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3072,14 +3076,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444. Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576949</v>
+        <v>576994</v>
       </c>
       <c r="R23" t="n">
-        <v>6379790</v>
+        <v>6379690</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3139,10 +3143,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123259271</v>
+        <v>123259910</v>
       </c>
       <c r="B24" t="n">
-        <v>98502</v>
+        <v>91400</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3151,46 +3155,49 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>A 11444. Grönlid, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>576994</v>
+        <v>576891</v>
       </c>
       <c r="R24" t="n">
-        <v>6379690</v>
+        <v>6379777</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3250,10 +3257,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123259084</v>
+        <v>123259111</v>
       </c>
       <c r="B25" t="n">
-        <v>92297</v>
+        <v>92271</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3262,30 +3269,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3297,14 +3304,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>A 11444, Grönled, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577012</v>
+        <v>577001</v>
       </c>
       <c r="R25" t="n">
-        <v>6379533</v>
+        <v>6379581</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3364,10 +3371,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123259882</v>
+        <v>123259948</v>
       </c>
       <c r="B26" t="n">
-        <v>57506</v>
+        <v>98504</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3376,35 +3383,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3412,10 +3419,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>576832</v>
+        <v>576939</v>
       </c>
       <c r="R26" t="n">
-        <v>6379712</v>
+        <v>6379798</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3450,17 +3457,13 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Bearbetat torrträd</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3482,7 +3485,7 @@
         <v>123259471</v>
       </c>
       <c r="B27" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3590,10 +3593,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123259183</v>
+        <v>123259084</v>
       </c>
       <c r="B28" t="n">
-        <v>92269</v>
+        <v>92299</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3602,30 +3605,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3637,14 +3640,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444, Grönled, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577000</v>
+        <v>577012</v>
       </c>
       <c r="R28" t="n">
-        <v>6379640</v>
+        <v>6379533</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3707,7 +3710,7 @@
         <v>123260011</v>
       </c>
       <c r="B29" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3818,10 +3821,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123259131</v>
+        <v>123260939</v>
       </c>
       <c r="B30" t="n">
-        <v>92269</v>
+        <v>98504</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3830,38 +3833,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3869,10 +3869,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>577009</v>
+        <v>576951</v>
       </c>
       <c r="R30" t="n">
-        <v>6379596</v>
+        <v>6379805</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3932,10 +3932,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123313086</v>
+        <v>123312935</v>
       </c>
       <c r="B31" t="n">
-        <v>57860</v>
+        <v>98504</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3944,39 +3944,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3984,10 +3980,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>576640</v>
+        <v>576793</v>
       </c>
       <c r="R31" t="n">
-        <v>6379941</v>
+        <v>6379822</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4028,6 +4024,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4046,10 +4043,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123313080</v>
+        <v>123312921</v>
       </c>
       <c r="B32" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4080,7 +4077,11 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
@@ -4090,10 +4091,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>576640</v>
+        <v>576799</v>
       </c>
       <c r="R32" t="n">
-        <v>6379941</v>
+        <v>6379827</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4153,10 +4154,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123313124</v>
+        <v>123312524</v>
       </c>
       <c r="B33" t="n">
-        <v>98502</v>
+        <v>92271</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4165,35 +4166,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4201,10 +4205,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>576507</v>
+        <v>576731</v>
       </c>
       <c r="R33" t="n">
-        <v>6379922</v>
+        <v>6379842</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4234,9 +4238,19 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4264,10 +4278,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123313067</v>
+        <v>123312540</v>
       </c>
       <c r="B34" t="n">
-        <v>91008</v>
+        <v>57861</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4276,38 +4290,39 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5442</v>
+        <v>103015</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4315,13 +4330,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>576682</v>
+        <v>576808</v>
       </c>
       <c r="R34" t="n">
-        <v>6379963</v>
+        <v>6379847</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4348,18 +4363,27 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4378,10 +4402,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123312896</v>
+        <v>123312958</v>
       </c>
       <c r="B35" t="n">
-        <v>105518</v>
+        <v>105520</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4426,10 +4450,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>576804</v>
+        <v>576745</v>
       </c>
       <c r="R35" t="n">
-        <v>6379845</v>
+        <v>6379872</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4489,10 +4513,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123312958</v>
+        <v>123313067</v>
       </c>
       <c r="B36" t="n">
-        <v>105518</v>
+        <v>91010</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4501,35 +4525,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4537,10 +4564,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>576745</v>
+        <v>576682</v>
       </c>
       <c r="R36" t="n">
-        <v>6379872</v>
+        <v>6379963</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4600,10 +4627,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123312502</v>
+        <v>123312993</v>
       </c>
       <c r="B37" t="n">
-        <v>95173</v>
+        <v>91010</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4612,31 +4639,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4644,10 +4678,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>576740</v>
+        <v>576745</v>
       </c>
       <c r="R37" t="n">
-        <v>6379855</v>
+        <v>6379872</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4677,19 +4711,9 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>15:50</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4717,10 +4741,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123312524</v>
+        <v>123313086</v>
       </c>
       <c r="B38" t="n">
-        <v>92269</v>
+        <v>57861</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4733,34 +4757,35 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4768,10 +4793,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>576731</v>
+        <v>576640</v>
       </c>
       <c r="R38" t="n">
-        <v>6379842</v>
+        <v>6379941</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4801,28 +4826,17 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4841,10 +4855,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123312935</v>
+        <v>123312753</v>
       </c>
       <c r="B39" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4889,10 +4903,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>576793</v>
+        <v>576835</v>
       </c>
       <c r="R39" t="n">
-        <v>6379822</v>
+        <v>6379711</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4952,10 +4966,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123312486</v>
+        <v>123313052</v>
       </c>
       <c r="B40" t="n">
-        <v>57860</v>
+        <v>91400</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4968,35 +4982,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103015</v>
+        <v>5420</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5004,13 +5017,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>576693</v>
+        <v>576677</v>
       </c>
       <c r="R40" t="n">
-        <v>6379898</v>
+        <v>6379959</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5037,27 +5050,18 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5076,10 +5080,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123313044</v>
+        <v>123313080</v>
       </c>
       <c r="B41" t="n">
-        <v>91398</v>
+        <v>98504</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5088,38 +5092,31 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5127,10 +5124,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>576690</v>
+        <v>576640</v>
       </c>
       <c r="R41" t="n">
-        <v>6379955</v>
+        <v>6379941</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5190,10 +5187,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123312773</v>
+        <v>123313044</v>
       </c>
       <c r="B42" t="n">
-        <v>105518</v>
+        <v>91400</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5206,31 +5203,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221144</v>
+        <v>5420</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5238,10 +5238,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>576839</v>
+        <v>576690</v>
       </c>
       <c r="R42" t="n">
-        <v>6379721</v>
+        <v>6379955</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5301,10 +5301,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123312808</v>
+        <v>123313124</v>
       </c>
       <c r="B43" t="n">
-        <v>97367</v>
+        <v>98504</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5313,35 +5313,31 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -5353,10 +5349,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>576804</v>
+        <v>576507</v>
       </c>
       <c r="R43" t="n">
-        <v>6379891</v>
+        <v>6379922</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5416,10 +5412,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123312921</v>
+        <v>123312569</v>
       </c>
       <c r="B44" t="n">
-        <v>98502</v>
+        <v>105520</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5428,25 +5424,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5464,10 +5460,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>576799</v>
+        <v>576803</v>
       </c>
       <c r="R44" t="n">
-        <v>6379827</v>
+        <v>6379887</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5497,9 +5493,19 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5527,10 +5533,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123312540</v>
+        <v>123312486</v>
       </c>
       <c r="B45" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5579,10 +5585,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>576808</v>
+        <v>576693</v>
       </c>
       <c r="R45" t="n">
-        <v>6379847</v>
+        <v>6379898</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5651,10 +5657,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123312569</v>
+        <v>123312808</v>
       </c>
       <c r="B46" t="n">
-        <v>105518</v>
+        <v>97369</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5667,27 +5673,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -5699,10 +5709,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>576803</v>
+        <v>576804</v>
       </c>
       <c r="R46" t="n">
-        <v>6379887</v>
+        <v>6379891</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5732,19 +5742,9 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>15:50</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5772,10 +5772,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123312904</v>
+        <v>123312502</v>
       </c>
       <c r="B47" t="n">
-        <v>98502</v>
+        <v>95175</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5784,33 +5784,29 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
@@ -5820,10 +5816,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>576804</v>
+        <v>576740</v>
       </c>
       <c r="R47" t="n">
-        <v>6379845</v>
+        <v>6379855</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5853,9 +5849,19 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5883,10 +5889,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123313052</v>
+        <v>123312904</v>
       </c>
       <c r="B48" t="n">
-        <v>91398</v>
+        <v>98504</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5895,38 +5901,35 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5934,10 +5937,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>576677</v>
+        <v>576804</v>
       </c>
       <c r="R48" t="n">
-        <v>6379959</v>
+        <v>6379845</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5997,10 +6000,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123312753</v>
+        <v>123312773</v>
       </c>
       <c r="B49" t="n">
-        <v>98502</v>
+        <v>105520</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6009,25 +6012,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6045,10 +6048,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>576835</v>
+        <v>576839</v>
       </c>
       <c r="R49" t="n">
-        <v>6379711</v>
+        <v>6379721</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6108,10 +6111,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123312993</v>
+        <v>123312896</v>
       </c>
       <c r="B50" t="n">
-        <v>91008</v>
+        <v>105520</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6120,38 +6123,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6159,10 +6159,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>576745</v>
+        <v>576804</v>
       </c>
       <c r="R50" t="n">
-        <v>6379872</v>
+        <v>6379845</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 11444-2025 artfynd.xlsx
+++ b/artfynd/A 11444-2025 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123259828</v>
+        <v>123259498</v>
       </c>
       <c r="B3" t="n">
-        <v>90990</v>
+        <v>95175</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,38 +801,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576838</v>
+        <v>576965</v>
       </c>
       <c r="R3" t="n">
-        <v>6379654</v>
+        <v>6379700</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123259460</v>
+        <v>123259828</v>
       </c>
       <c r="B4" t="n">
-        <v>92271</v>
+        <v>90990</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,31 +908,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -950,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576977</v>
+        <v>576838</v>
       </c>
       <c r="R4" t="n">
-        <v>6379694</v>
+        <v>6379654</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123259312</v>
+        <v>123259460</v>
       </c>
       <c r="B5" t="n">
-        <v>98504</v>
+        <v>92271</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,35 +1022,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1061,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576990</v>
+        <v>576977</v>
       </c>
       <c r="R5" t="n">
-        <v>6379697</v>
+        <v>6379694</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123259498</v>
+        <v>123259312</v>
       </c>
       <c r="B6" t="n">
-        <v>95175</v>
+        <v>98504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,29 +1132,33 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576965</v>
+        <v>576990</v>
       </c>
       <c r="R6" t="n">
-        <v>6379700</v>
+        <v>6379697</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -3593,10 +3593,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123259084</v>
+        <v>123260011</v>
       </c>
       <c r="B28" t="n">
-        <v>92299</v>
+        <v>90990</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3609,45 +3609,45 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5449</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>A 11444, Grönled, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577012</v>
+        <v>576847</v>
       </c>
       <c r="R28" t="n">
-        <v>6379533</v>
+        <v>6379709</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3707,10 +3707,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123260011</v>
+        <v>123259084</v>
       </c>
       <c r="B29" t="n">
-        <v>90990</v>
+        <v>92299</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3723,45 +3723,45 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>5449</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444, Grönled, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>576847</v>
+        <v>577012</v>
       </c>
       <c r="R29" t="n">
-        <v>6379709</v>
+        <v>6379533</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4402,10 +4402,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123312958</v>
+        <v>123313067</v>
       </c>
       <c r="B35" t="n">
-        <v>105520</v>
+        <v>91010</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4414,35 +4414,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4450,10 +4453,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>576745</v>
+        <v>576682</v>
       </c>
       <c r="R35" t="n">
-        <v>6379872</v>
+        <v>6379963</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4513,10 +4516,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123313067</v>
+        <v>123312958</v>
       </c>
       <c r="B36" t="n">
-        <v>91010</v>
+        <v>105520</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4525,38 +4528,35 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4564,10 +4564,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>576682</v>
+        <v>576745</v>
       </c>
       <c r="R36" t="n">
-        <v>6379963</v>
+        <v>6379872</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4966,10 +4966,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123313052</v>
+        <v>123313080</v>
       </c>
       <c r="B40" t="n">
-        <v>91400</v>
+        <v>98504</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4978,38 +4978,31 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5017,10 +5010,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>576677</v>
+        <v>576640</v>
       </c>
       <c r="R40" t="n">
-        <v>6379959</v>
+        <v>6379941</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5080,10 +5073,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123313080</v>
+        <v>123313052</v>
       </c>
       <c r="B41" t="n">
-        <v>98504</v>
+        <v>91400</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5092,31 +5085,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5124,10 +5124,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>576640</v>
+        <v>576677</v>
       </c>
       <c r="R41" t="n">
-        <v>6379941</v>
+        <v>6379959</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 11444-2025 artfynd.xlsx
+++ b/artfynd/A 11444-2025 artfynd.xlsx
@@ -1342,10 +1342,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123259157</v>
+        <v>123259183</v>
       </c>
       <c r="B8" t="n">
-        <v>57644</v>
+        <v>92271</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1354,25 +1354,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1380,13 +1380,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1394,13 +1393,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576997</v>
+        <v>577000</v>
       </c>
       <c r="R8" t="n">
-        <v>6379617</v>
+        <v>6379640</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1438,6 +1437,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123259183</v>
+        <v>123259157</v>
       </c>
       <c r="B9" t="n">
-        <v>92271</v>
+        <v>57644</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,25 +1468,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1494,12 +1494,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1507,13 +1508,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577000</v>
+        <v>576997</v>
       </c>
       <c r="R9" t="n">
-        <v>6379640</v>
+        <v>6379617</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1551,7 +1552,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1903,10 +1903,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123259419</v>
+        <v>123259974</v>
       </c>
       <c r="B13" t="n">
-        <v>57644</v>
+        <v>98504</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1915,53 +1915,49 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 11444, Grönlif, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576985</v>
+        <v>576950</v>
       </c>
       <c r="R13" t="n">
-        <v>6379714</v>
+        <v>6379824</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1999,6 +1995,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2017,10 +2014,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123259974</v>
+        <v>123259419</v>
       </c>
       <c r="B14" t="n">
-        <v>98504</v>
+        <v>57644</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2029,49 +2026,53 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444, Grönlif, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576950</v>
+        <v>576985</v>
       </c>
       <c r="R14" t="n">
-        <v>6379824</v>
+        <v>6379714</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2109,7 +2110,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -4402,10 +4402,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123313067</v>
+        <v>123312958</v>
       </c>
       <c r="B35" t="n">
-        <v>91010</v>
+        <v>105520</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4414,38 +4414,35 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4453,10 +4450,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>576682</v>
+        <v>576745</v>
       </c>
       <c r="R35" t="n">
-        <v>6379963</v>
+        <v>6379872</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4516,10 +4513,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123312958</v>
+        <v>123313067</v>
       </c>
       <c r="B36" t="n">
-        <v>105520</v>
+        <v>91010</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4528,35 +4525,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4564,10 +4564,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>576745</v>
+        <v>576682</v>
       </c>
       <c r="R36" t="n">
-        <v>6379872</v>
+        <v>6379963</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4966,10 +4966,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123313080</v>
+        <v>123313052</v>
       </c>
       <c r="B40" t="n">
-        <v>98504</v>
+        <v>91400</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4978,31 +4978,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5010,10 +5017,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>576640</v>
+        <v>576677</v>
       </c>
       <c r="R40" t="n">
-        <v>6379941</v>
+        <v>6379959</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5073,10 +5080,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123313052</v>
+        <v>123313080</v>
       </c>
       <c r="B41" t="n">
-        <v>91400</v>
+        <v>98504</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5085,38 +5092,31 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5124,10 +5124,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>576677</v>
+        <v>576640</v>
       </c>
       <c r="R41" t="n">
-        <v>6379959</v>
+        <v>6379941</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 11444-2025 artfynd.xlsx
+++ b/artfynd/A 11444-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123259993</v>
+        <v>123259628</v>
       </c>
       <c r="B2" t="n">
-        <v>91010</v>
+        <v>57861</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,26 +713,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576929</v>
+        <v>576883</v>
       </c>
       <c r="R2" t="n">
-        <v>6379832</v>
+        <v>6379747</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -770,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123259498</v>
+        <v>123259522</v>
       </c>
       <c r="B3" t="n">
-        <v>95175</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,29 +801,33 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -833,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576965</v>
+        <v>576971</v>
       </c>
       <c r="R3" t="n">
-        <v>6379700</v>
+        <v>6379715</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123259828</v>
+        <v>123259460</v>
       </c>
       <c r="B4" t="n">
-        <v>90990</v>
+        <v>92271</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,35 +912,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576838</v>
+        <v>576977</v>
       </c>
       <c r="R4" t="n">
-        <v>6379654</v>
+        <v>6379694</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123259460</v>
+        <v>123259131</v>
       </c>
       <c r="B5" t="n">
         <v>92271</v>
@@ -1043,7 +1043,11 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -1057,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576977</v>
+        <v>577009</v>
       </c>
       <c r="R5" t="n">
-        <v>6379694</v>
+        <v>6379596</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123259312</v>
+        <v>123259332</v>
       </c>
       <c r="B6" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576990</v>
+        <v>576987</v>
       </c>
       <c r="R6" t="n">
-        <v>6379697</v>
+        <v>6379692</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123259332</v>
+        <v>123259392</v>
       </c>
       <c r="B7" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1279,10 +1283,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576987</v>
+        <v>576988</v>
       </c>
       <c r="R7" t="n">
-        <v>6379692</v>
+        <v>6379698</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1342,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123259183</v>
+        <v>123259157</v>
       </c>
       <c r="B8" t="n">
-        <v>92271</v>
+        <v>57644</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1354,25 +1358,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1380,12 +1384,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1393,13 +1398,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577000</v>
+        <v>576997</v>
       </c>
       <c r="R8" t="n">
-        <v>6379640</v>
+        <v>6379617</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1437,7 +1442,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1456,10 +1460,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123259157</v>
+        <v>123259930</v>
       </c>
       <c r="B9" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,39 +1472,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1508,13 +1508,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576997</v>
+        <v>576949</v>
       </c>
       <c r="R9" t="n">
-        <v>6379617</v>
+        <v>6379790</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1552,6 +1552,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1570,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123259522</v>
+        <v>123259312</v>
       </c>
       <c r="B10" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1618,10 +1619,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576971</v>
+        <v>576990</v>
       </c>
       <c r="R10" t="n">
-        <v>6379715</v>
+        <v>6379697</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,10 +1682,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123259554</v>
+        <v>123259084</v>
       </c>
       <c r="B11" t="n">
-        <v>105520</v>
+        <v>92299</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1693,46 +1694,49 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>5449</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444, Grönled, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576891</v>
+        <v>577012</v>
       </c>
       <c r="R11" t="n">
-        <v>6379769</v>
+        <v>6379533</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,10 +1796,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123259930</v>
+        <v>123259271</v>
       </c>
       <c r="B12" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,14 +1840,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444. Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576949</v>
+        <v>576994</v>
       </c>
       <c r="R12" t="n">
-        <v>6379790</v>
+        <v>6379690</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123259974</v>
+        <v>123259882</v>
       </c>
       <c r="B13" t="n">
-        <v>98504</v>
+        <v>57507</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1915,35 +1919,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1951,10 +1955,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576950</v>
+        <v>576832</v>
       </c>
       <c r="R13" t="n">
-        <v>6379824</v>
+        <v>6379712</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1989,13 +1993,17 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Bearbetat torrträd</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2128,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123259882</v>
+        <v>123259948</v>
       </c>
       <c r="B15" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2140,35 +2148,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2176,10 +2184,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576832</v>
+        <v>576939</v>
       </c>
       <c r="R15" t="n">
-        <v>6379712</v>
+        <v>6379798</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2214,17 +2222,13 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Bearbetat torrträd</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2243,10 +2247,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123259851</v>
+        <v>123260939</v>
       </c>
       <c r="B16" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2255,38 +2259,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2294,10 +2295,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576835</v>
+        <v>576951</v>
       </c>
       <c r="R16" t="n">
-        <v>6379715</v>
+        <v>6379805</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2357,10 +2358,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123259362</v>
+        <v>123259440</v>
       </c>
       <c r="B17" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2405,10 +2406,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576989</v>
+        <v>576980</v>
       </c>
       <c r="R17" t="n">
-        <v>6379691</v>
+        <v>6379697</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2468,10 +2469,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123259440</v>
+        <v>123259471</v>
       </c>
       <c r="B18" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2512,14 +2513,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444, Grönlif, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576980</v>
+        <v>576971</v>
       </c>
       <c r="R18" t="n">
-        <v>6379697</v>
+        <v>6379688</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2579,10 +2580,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123259392</v>
+        <v>123259362</v>
       </c>
       <c r="B19" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2627,10 +2628,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576988</v>
+        <v>576989</v>
       </c>
       <c r="R19" t="n">
-        <v>6379698</v>
+        <v>6379691</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2690,7 +2691,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123259209</v>
+        <v>123260011</v>
       </c>
       <c r="B20" t="n">
         <v>90990</v>
@@ -2741,10 +2742,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576992</v>
+        <v>576847</v>
       </c>
       <c r="R20" t="n">
-        <v>6379660</v>
+        <v>6379709</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2804,7 +2805,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123259131</v>
+        <v>123259111</v>
       </c>
       <c r="B21" t="n">
         <v>92271</v>
@@ -2839,7 +2840,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2855,10 +2856,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577009</v>
+        <v>577001</v>
       </c>
       <c r="R21" t="n">
-        <v>6379596</v>
+        <v>6379581</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2918,10 +2919,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123259628</v>
+        <v>123259209</v>
       </c>
       <c r="B22" t="n">
-        <v>57861</v>
+        <v>90990</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2930,25 +2931,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2956,27 +2957,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>A11444, Grönlid, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576883</v>
+        <v>576992</v>
       </c>
       <c r="R22" t="n">
-        <v>6379747</v>
+        <v>6379660</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3014,6 +3014,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3032,10 +3033,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123259271</v>
+        <v>123259851</v>
       </c>
       <c r="B23" t="n">
-        <v>98504</v>
+        <v>90990</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3044,46 +3045,49 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>A 11444. Grönlid, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576994</v>
+        <v>576835</v>
       </c>
       <c r="R23" t="n">
-        <v>6379690</v>
+        <v>6379715</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3143,10 +3147,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123259910</v>
+        <v>123259828</v>
       </c>
       <c r="B24" t="n">
-        <v>91400</v>
+        <v>90990</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3155,25 +3159,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5420</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3183,7 +3187,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -3194,10 +3198,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>576891</v>
+        <v>576838</v>
       </c>
       <c r="R24" t="n">
-        <v>6379777</v>
+        <v>6379654</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3257,7 +3261,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123259111</v>
+        <v>123259183</v>
       </c>
       <c r="B25" t="n">
         <v>92271</v>
@@ -3292,7 +3296,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3308,10 +3312,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577001</v>
+        <v>577000</v>
       </c>
       <c r="R25" t="n">
-        <v>6379581</v>
+        <v>6379640</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3371,10 +3375,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123259948</v>
+        <v>123259910</v>
       </c>
       <c r="B26" t="n">
-        <v>98504</v>
+        <v>91400</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3383,35 +3387,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3419,10 +3426,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>576939</v>
+        <v>576891</v>
       </c>
       <c r="R26" t="n">
-        <v>6379798</v>
+        <v>6379777</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3482,10 +3489,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123259471</v>
+        <v>123259498</v>
       </c>
       <c r="B27" t="n">
-        <v>98504</v>
+        <v>95683</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3494,46 +3501,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>A 11444, Grönlif, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>576971</v>
+        <v>576965</v>
       </c>
       <c r="R27" t="n">
-        <v>6379688</v>
+        <v>6379700</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3593,10 +3596,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123260011</v>
+        <v>123259993</v>
       </c>
       <c r="B28" t="n">
-        <v>90990</v>
+        <v>91010</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3609,21 +3612,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3633,7 +3636,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -3644,10 +3647,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>576847</v>
+        <v>576929</v>
       </c>
       <c r="R28" t="n">
-        <v>6379709</v>
+        <v>6379832</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3707,10 +3710,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123259084</v>
+        <v>123259974</v>
       </c>
       <c r="B29" t="n">
-        <v>92299</v>
+        <v>98079</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3719,49 +3722,46 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>A 11444, Grönled, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>577012</v>
+        <v>576950</v>
       </c>
       <c r="R29" t="n">
-        <v>6379533</v>
+        <v>6379824</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3821,10 +3821,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123260939</v>
+        <v>123259554</v>
       </c>
       <c r="B30" t="n">
-        <v>98504</v>
+        <v>105095</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3833,25 +3833,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3869,10 +3869,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>576951</v>
+        <v>576891</v>
       </c>
       <c r="R30" t="n">
-        <v>6379805</v>
+        <v>6379769</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3932,10 +3932,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123312935</v>
+        <v>123313086</v>
       </c>
       <c r="B31" t="n">
-        <v>98504</v>
+        <v>57861</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3944,35 +3944,39 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3980,10 +3984,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>576793</v>
+        <v>576640</v>
       </c>
       <c r="R31" t="n">
-        <v>6379822</v>
+        <v>6379941</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4024,7 +4028,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4043,10 +4046,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123312921</v>
+        <v>123312808</v>
       </c>
       <c r="B32" t="n">
-        <v>98504</v>
+        <v>96957</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4055,31 +4058,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -4091,10 +4098,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>576799</v>
+        <v>576804</v>
       </c>
       <c r="R32" t="n">
-        <v>6379827</v>
+        <v>6379891</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4154,10 +4161,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123312524</v>
+        <v>123313052</v>
       </c>
       <c r="B33" t="n">
-        <v>92271</v>
+        <v>91400</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4170,26 +4177,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4205,10 +4212,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>576731</v>
+        <v>576677</v>
       </c>
       <c r="R33" t="n">
-        <v>6379842</v>
+        <v>6379959</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4238,19 +4245,9 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>15:50</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4278,10 +4275,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123312540</v>
+        <v>123312993</v>
       </c>
       <c r="B34" t="n">
-        <v>57861</v>
+        <v>91010</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4290,25 +4287,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103015</v>
+        <v>5442</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4316,13 +4313,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4330,13 +4326,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>576808</v>
+        <v>576745</v>
       </c>
       <c r="R34" t="n">
-        <v>6379847</v>
+        <v>6379872</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4363,27 +4359,18 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4402,10 +4389,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123312958</v>
+        <v>123312524</v>
       </c>
       <c r="B35" t="n">
-        <v>105520</v>
+        <v>92271</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4418,31 +4405,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4450,10 +4440,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>576745</v>
+        <v>576731</v>
       </c>
       <c r="R35" t="n">
-        <v>6379872</v>
+        <v>6379842</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4483,9 +4473,19 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4513,10 +4513,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123313067</v>
+        <v>123312753</v>
       </c>
       <c r="B36" t="n">
-        <v>91010</v>
+        <v>98079</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4525,38 +4525,35 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4564,10 +4561,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>576682</v>
+        <v>576835</v>
       </c>
       <c r="R36" t="n">
-        <v>6379963</v>
+        <v>6379711</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4627,10 +4624,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123312993</v>
+        <v>123312935</v>
       </c>
       <c r="B37" t="n">
-        <v>91010</v>
+        <v>98079</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4639,38 +4636,35 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4678,10 +4672,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>576745</v>
+        <v>576793</v>
       </c>
       <c r="R37" t="n">
-        <v>6379872</v>
+        <v>6379822</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4741,10 +4735,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123313086</v>
+        <v>123312502</v>
       </c>
       <c r="B38" t="n">
-        <v>57861</v>
+        <v>95683</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4757,35 +4751,27 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4793,10 +4779,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>576640</v>
+        <v>576740</v>
       </c>
       <c r="R38" t="n">
-        <v>6379941</v>
+        <v>6379855</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4826,17 +4812,28 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4855,10 +4852,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123312753</v>
+        <v>123312773</v>
       </c>
       <c r="B39" t="n">
-        <v>98504</v>
+        <v>105095</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4867,25 +4864,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4903,10 +4900,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>576835</v>
+        <v>576839</v>
       </c>
       <c r="R39" t="n">
-        <v>6379711</v>
+        <v>6379721</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4966,10 +4963,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123313052</v>
+        <v>123312540</v>
       </c>
       <c r="B40" t="n">
-        <v>91400</v>
+        <v>57861</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4982,34 +4979,35 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5420</v>
+        <v>103015</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5017,13 +5015,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>576677</v>
+        <v>576808</v>
       </c>
       <c r="R40" t="n">
-        <v>6379959</v>
+        <v>6379847</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5050,18 +5048,27 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5080,10 +5087,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123313080</v>
+        <v>123312896</v>
       </c>
       <c r="B41" t="n">
-        <v>98504</v>
+        <v>105095</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5092,29 +5099,33 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
@@ -5124,10 +5135,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>576640</v>
+        <v>576804</v>
       </c>
       <c r="R41" t="n">
-        <v>6379941</v>
+        <v>6379845</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5187,10 +5198,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123313044</v>
+        <v>123312486</v>
       </c>
       <c r="B42" t="n">
-        <v>91400</v>
+        <v>57861</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5203,21 +5214,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5420</v>
+        <v>103015</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5225,12 +5236,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5238,13 +5250,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>576690</v>
+        <v>576693</v>
       </c>
       <c r="R42" t="n">
-        <v>6379955</v>
+        <v>6379898</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5271,18 +5283,27 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5301,10 +5322,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123313124</v>
+        <v>123313080</v>
       </c>
       <c r="B43" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5335,11 +5356,7 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
@@ -5349,10 +5366,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>576507</v>
+        <v>576640</v>
       </c>
       <c r="R43" t="n">
-        <v>6379922</v>
+        <v>6379941</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5412,10 +5429,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123312569</v>
+        <v>123313124</v>
       </c>
       <c r="B44" t="n">
-        <v>105520</v>
+        <v>98079</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5424,25 +5441,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5460,10 +5477,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>576803</v>
+        <v>576507</v>
       </c>
       <c r="R44" t="n">
-        <v>6379887</v>
+        <v>6379922</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5493,19 +5510,9 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>15:50</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5533,10 +5540,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123312486</v>
+        <v>123312904</v>
       </c>
       <c r="B45" t="n">
-        <v>57861</v>
+        <v>98079</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5545,39 +5552,35 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5585,13 +5588,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>576693</v>
+        <v>576804</v>
       </c>
       <c r="R45" t="n">
-        <v>6379898</v>
+        <v>6379845</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5618,27 +5621,18 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5657,10 +5651,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123312808</v>
+        <v>123313067</v>
       </c>
       <c r="B46" t="n">
-        <v>97369</v>
+        <v>91010</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5669,39 +5663,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221945</v>
+        <v>5442</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5709,10 +5702,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>576804</v>
+        <v>576682</v>
       </c>
       <c r="R46" t="n">
-        <v>6379891</v>
+        <v>6379963</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5772,10 +5765,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123312502</v>
+        <v>123312921</v>
       </c>
       <c r="B47" t="n">
-        <v>95175</v>
+        <v>98079</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5784,29 +5777,33 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
@@ -5816,10 +5813,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>576740</v>
+        <v>576799</v>
       </c>
       <c r="R47" t="n">
-        <v>6379855</v>
+        <v>6379827</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5849,19 +5846,9 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>15:50</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5889,10 +5876,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123312904</v>
+        <v>123313044</v>
       </c>
       <c r="B48" t="n">
-        <v>98504</v>
+        <v>91400</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5901,35 +5888,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5937,10 +5927,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>576804</v>
+        <v>576690</v>
       </c>
       <c r="R48" t="n">
-        <v>6379845</v>
+        <v>6379955</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6000,10 +5990,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123312773</v>
+        <v>123312569</v>
       </c>
       <c r="B49" t="n">
-        <v>105520</v>
+        <v>105095</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6048,10 +6038,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>576839</v>
+        <v>576803</v>
       </c>
       <c r="R49" t="n">
-        <v>6379721</v>
+        <v>6379887</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6081,9 +6071,19 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6111,10 +6111,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123312896</v>
+        <v>123312958</v>
       </c>
       <c r="B50" t="n">
-        <v>105520</v>
+        <v>105095</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6159,10 +6159,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>576804</v>
+        <v>576745</v>
       </c>
       <c r="R50" t="n">
-        <v>6379845</v>
+        <v>6379872</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 11444-2025 artfynd.xlsx
+++ b/artfynd/A 11444-2025 artfynd.xlsx
@@ -1124,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123259332</v>
+        <v>123259157</v>
       </c>
       <c r="B6" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,35 +1136,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1172,13 +1176,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576987</v>
+        <v>576997</v>
       </c>
       <c r="R6" t="n">
-        <v>6379692</v>
+        <v>6379617</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,7 +1220,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1235,7 +1238,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123259392</v>
+        <v>123259332</v>
       </c>
       <c r="B7" t="n">
         <v>98079</v>
@@ -1283,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576988</v>
+        <v>576987</v>
       </c>
       <c r="R7" t="n">
-        <v>6379698</v>
+        <v>6379692</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1346,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123259157</v>
+        <v>123259392</v>
       </c>
       <c r="B8" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1358,39 +1361,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1398,13 +1397,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576997</v>
+        <v>576988</v>
       </c>
       <c r="R8" t="n">
-        <v>6379617</v>
+        <v>6379698</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1442,6 +1441,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11444-2025 artfynd.xlsx
+++ b/artfynd/A 11444-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123259628</v>
+        <v>123259392</v>
       </c>
       <c r="B2" t="n">
-        <v>57861</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,53 +687,49 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A11444, Grönlid, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576883</v>
+        <v>576988</v>
       </c>
       <c r="R2" t="n">
-        <v>6379747</v>
+        <v>6379698</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123259522</v>
+        <v>123259628</v>
       </c>
       <c r="B3" t="n">
-        <v>98079</v>
+        <v>57861</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,49 +798,53 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576971</v>
+        <v>576883</v>
       </c>
       <c r="R3" t="n">
-        <v>6379715</v>
+        <v>6379747</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +882,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123259460</v>
+        <v>123259930</v>
       </c>
       <c r="B4" t="n">
-        <v>92271</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,34 +912,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -947,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576977</v>
+        <v>576949</v>
       </c>
       <c r="R4" t="n">
-        <v>6379694</v>
+        <v>6379790</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123259131</v>
+        <v>123259419</v>
       </c>
       <c r="B5" t="n">
-        <v>92271</v>
+        <v>57644</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1048,26 +1049,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444, Grönlif, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577009</v>
+        <v>576985</v>
       </c>
       <c r="R5" t="n">
-        <v>6379596</v>
+        <v>6379714</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,7 +1107,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1124,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123259157</v>
+        <v>123259362</v>
       </c>
       <c r="B6" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,39 +1137,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1176,13 +1173,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576997</v>
+        <v>576989</v>
       </c>
       <c r="R6" t="n">
-        <v>6379617</v>
+        <v>6379691</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1220,6 +1217,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1238,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123259332</v>
+        <v>123259209</v>
       </c>
       <c r="B7" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,35 +1248,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1286,10 +1287,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576987</v>
+        <v>576992</v>
       </c>
       <c r="R7" t="n">
-        <v>6379692</v>
+        <v>6379660</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,10 +1350,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123259392</v>
+        <v>123259498</v>
       </c>
       <c r="B8" t="n">
-        <v>98079</v>
+        <v>95683</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1361,33 +1362,29 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1397,10 +1394,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576988</v>
+        <v>576965</v>
       </c>
       <c r="R8" t="n">
-        <v>6379698</v>
+        <v>6379700</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123259930</v>
+        <v>123259084</v>
       </c>
       <c r="B9" t="n">
-        <v>98079</v>
+        <v>92299</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1472,46 +1469,49 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444, Grönled, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576949</v>
+        <v>577012</v>
       </c>
       <c r="R9" t="n">
-        <v>6379790</v>
+        <v>6379533</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123259312</v>
+        <v>123259882</v>
       </c>
       <c r="B10" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,35 +1583,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576990</v>
+        <v>576832</v>
       </c>
       <c r="R10" t="n">
-        <v>6379697</v>
+        <v>6379712</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1657,13 +1657,17 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Bearbetat torrträd</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1682,10 +1686,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123259084</v>
+        <v>123259948</v>
       </c>
       <c r="B11" t="n">
-        <v>92299</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1694,49 +1698,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 11444, Grönled, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577012</v>
+        <v>576939</v>
       </c>
       <c r="R11" t="n">
-        <v>6379533</v>
+        <v>6379798</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1796,10 +1797,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123259271</v>
+        <v>123259993</v>
       </c>
       <c r="B12" t="n">
-        <v>98079</v>
+        <v>91010</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1808,46 +1809,49 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 11444. Grönlid, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576994</v>
+        <v>576929</v>
       </c>
       <c r="R12" t="n">
-        <v>6379690</v>
+        <v>6379832</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,10 +1911,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123259882</v>
+        <v>123259157</v>
       </c>
       <c r="B13" t="n">
-        <v>57507</v>
+        <v>57644</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,29 +1927,33 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1955,13 +1963,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576832</v>
+        <v>576997</v>
       </c>
       <c r="R13" t="n">
-        <v>6379712</v>
+        <v>6379617</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1991,11 +1999,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Bearbetat torrträd</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2022,10 +2025,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123259419</v>
+        <v>123259522</v>
       </c>
       <c r="B14" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2034,53 +2037,49 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 11444, Grönlif, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576985</v>
+        <v>576971</v>
       </c>
       <c r="R14" t="n">
-        <v>6379714</v>
+        <v>6379715</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2118,6 +2117,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2136,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123259948</v>
+        <v>123259460</v>
       </c>
       <c r="B15" t="n">
-        <v>98079</v>
+        <v>92271</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2148,35 +2148,34 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2184,10 +2183,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576939</v>
+        <v>576977</v>
       </c>
       <c r="R15" t="n">
-        <v>6379798</v>
+        <v>6379694</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2247,10 +2246,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123260939</v>
+        <v>123260011</v>
       </c>
       <c r="B16" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2259,35 +2258,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2295,10 +2297,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576951</v>
+        <v>576847</v>
       </c>
       <c r="R16" t="n">
-        <v>6379805</v>
+        <v>6379709</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2358,7 +2360,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123259440</v>
+        <v>123259332</v>
       </c>
       <c r="B17" t="n">
         <v>98079</v>
@@ -2406,10 +2408,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576980</v>
+        <v>576987</v>
       </c>
       <c r="R17" t="n">
-        <v>6379697</v>
+        <v>6379692</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2469,10 +2471,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123259471</v>
+        <v>123259554</v>
       </c>
       <c r="B18" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2481,25 +2483,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2513,14 +2515,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>A 11444, Grönlif, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576971</v>
+        <v>576891</v>
       </c>
       <c r="R18" t="n">
-        <v>6379688</v>
+        <v>6379769</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2580,7 +2582,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123259362</v>
+        <v>123259440</v>
       </c>
       <c r="B19" t="n">
         <v>98079</v>
@@ -2628,10 +2630,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576989</v>
+        <v>576980</v>
       </c>
       <c r="R19" t="n">
-        <v>6379691</v>
+        <v>6379697</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2691,7 +2693,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123260011</v>
+        <v>123259851</v>
       </c>
       <c r="B20" t="n">
         <v>90990</v>
@@ -2742,10 +2744,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576847</v>
+        <v>576835</v>
       </c>
       <c r="R20" t="n">
-        <v>6379709</v>
+        <v>6379715</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2805,7 +2807,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123259111</v>
+        <v>123259131</v>
       </c>
       <c r="B21" t="n">
         <v>92271</v>
@@ -2840,7 +2842,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2856,10 +2858,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577001</v>
+        <v>577009</v>
       </c>
       <c r="R21" t="n">
-        <v>6379581</v>
+        <v>6379596</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2919,10 +2921,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123259209</v>
+        <v>123259910</v>
       </c>
       <c r="B22" t="n">
-        <v>90990</v>
+        <v>91400</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2931,25 +2933,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5420</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2959,7 +2961,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -2970,10 +2972,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576992</v>
+        <v>576891</v>
       </c>
       <c r="R22" t="n">
-        <v>6379660</v>
+        <v>6379777</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3033,7 +3035,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123259851</v>
+        <v>123259828</v>
       </c>
       <c r="B23" t="n">
         <v>90990</v>
@@ -3084,10 +3086,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576835</v>
+        <v>576838</v>
       </c>
       <c r="R23" t="n">
-        <v>6379715</v>
+        <v>6379654</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3147,10 +3149,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123259828</v>
+        <v>123260939</v>
       </c>
       <c r="B24" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3159,38 +3161,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3198,10 +3197,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>576838</v>
+        <v>576951</v>
       </c>
       <c r="R24" t="n">
-        <v>6379654</v>
+        <v>6379805</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3261,10 +3260,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123259183</v>
+        <v>123259271</v>
       </c>
       <c r="B25" t="n">
-        <v>92271</v>
+        <v>98079</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3273,49 +3272,46 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444. Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577000</v>
+        <v>576994</v>
       </c>
       <c r="R25" t="n">
-        <v>6379640</v>
+        <v>6379690</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3375,10 +3371,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123259910</v>
+        <v>123259974</v>
       </c>
       <c r="B26" t="n">
-        <v>91400</v>
+        <v>98079</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3387,38 +3383,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3426,10 +3419,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>576891</v>
+        <v>576950</v>
       </c>
       <c r="R26" t="n">
-        <v>6379777</v>
+        <v>6379824</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3489,10 +3482,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123259498</v>
+        <v>123259183</v>
       </c>
       <c r="B27" t="n">
-        <v>95683</v>
+        <v>92271</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3505,27 +3498,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3533,10 +3533,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>576965</v>
+        <v>577000</v>
       </c>
       <c r="R27" t="n">
-        <v>6379700</v>
+        <v>6379640</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3596,10 +3596,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123259993</v>
+        <v>123259111</v>
       </c>
       <c r="B28" t="n">
-        <v>91010</v>
+        <v>92271</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3608,30 +3608,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3647,10 +3647,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>576929</v>
+        <v>577001</v>
       </c>
       <c r="R28" t="n">
-        <v>6379832</v>
+        <v>6379581</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3710,7 +3710,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123259974</v>
+        <v>123259312</v>
       </c>
       <c r="B29" t="n">
         <v>98079</v>
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>576950</v>
+        <v>576990</v>
       </c>
       <c r="R29" t="n">
-        <v>6379824</v>
+        <v>6379697</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3821,10 +3821,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123259554</v>
+        <v>123259471</v>
       </c>
       <c r="B30" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3833,25 +3833,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3865,14 +3865,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444, Grönlif, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>576891</v>
+        <v>576971</v>
       </c>
       <c r="R30" t="n">
-        <v>6379769</v>
+        <v>6379688</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3932,10 +3932,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123313086</v>
+        <v>123313067</v>
       </c>
       <c r="B31" t="n">
-        <v>57861</v>
+        <v>91010</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3944,39 +3944,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103015</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3984,10 +3983,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>576640</v>
+        <v>576682</v>
       </c>
       <c r="R31" t="n">
-        <v>6379941</v>
+        <v>6379963</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4028,6 +4027,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4046,10 +4046,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123312808</v>
+        <v>123313080</v>
       </c>
       <c r="B32" t="n">
-        <v>96957</v>
+        <v>98079</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4058,37 +4058,29 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
@@ -4098,10 +4090,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>576804</v>
+        <v>576640</v>
       </c>
       <c r="R32" t="n">
-        <v>6379891</v>
+        <v>6379941</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4161,10 +4153,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123313052</v>
+        <v>123312773</v>
       </c>
       <c r="B33" t="n">
-        <v>91400</v>
+        <v>105095</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4177,34 +4169,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5420</v>
+        <v>221144</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4212,10 +4201,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>576677</v>
+        <v>576839</v>
       </c>
       <c r="R33" t="n">
-        <v>6379959</v>
+        <v>6379721</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4389,10 +4378,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123312524</v>
+        <v>123312486</v>
       </c>
       <c r="B35" t="n">
-        <v>92271</v>
+        <v>57861</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4405,34 +4394,35 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4440,13 +4430,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>576731</v>
+        <v>576693</v>
       </c>
       <c r="R35" t="n">
-        <v>6379842</v>
+        <v>6379898</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4494,7 +4484,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4735,10 +4724,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123312502</v>
+        <v>123312904</v>
       </c>
       <c r="B38" t="n">
-        <v>95683</v>
+        <v>98079</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4747,29 +4736,33 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -4779,10 +4772,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>576740</v>
+        <v>576804</v>
       </c>
       <c r="R38" t="n">
-        <v>6379855</v>
+        <v>6379845</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4812,19 +4805,9 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>15:50</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4852,10 +4835,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123312773</v>
+        <v>123313044</v>
       </c>
       <c r="B39" t="n">
-        <v>105095</v>
+        <v>91400</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4868,31 +4851,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221144</v>
+        <v>5420</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4900,10 +4886,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>576839</v>
+        <v>576690</v>
       </c>
       <c r="R39" t="n">
-        <v>6379721</v>
+        <v>6379955</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4963,7 +4949,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123312540</v>
+        <v>123313086</v>
       </c>
       <c r="B40" t="n">
         <v>57861</v>
@@ -5015,13 +5001,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>576808</v>
+        <v>576640</v>
       </c>
       <c r="R40" t="n">
-        <v>6379847</v>
+        <v>6379941</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5048,19 +5034,9 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>15:50</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5087,10 +5063,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123312896</v>
+        <v>123312524</v>
       </c>
       <c r="B41" t="n">
-        <v>105095</v>
+        <v>92271</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5103,31 +5079,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5135,10 +5114,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>576804</v>
+        <v>576731</v>
       </c>
       <c r="R41" t="n">
-        <v>6379845</v>
+        <v>6379842</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5168,9 +5147,19 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5198,10 +5187,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123312486</v>
+        <v>123312808</v>
       </c>
       <c r="B42" t="n">
-        <v>57861</v>
+        <v>96957</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5214,35 +5203,35 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5250,13 +5239,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>576693</v>
+        <v>576804</v>
       </c>
       <c r="R42" t="n">
-        <v>6379898</v>
+        <v>6379891</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5283,27 +5272,18 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5322,10 +5302,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123313080</v>
+        <v>123312958</v>
       </c>
       <c r="B43" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5334,29 +5314,33 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
@@ -5366,10 +5350,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>576640</v>
+        <v>576745</v>
       </c>
       <c r="R43" t="n">
-        <v>6379941</v>
+        <v>6379872</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5429,10 +5413,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123313124</v>
+        <v>123313052</v>
       </c>
       <c r="B44" t="n">
-        <v>98079</v>
+        <v>91400</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5441,35 +5425,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5477,10 +5464,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>576507</v>
+        <v>576677</v>
       </c>
       <c r="R44" t="n">
-        <v>6379922</v>
+        <v>6379959</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5540,10 +5527,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123312904</v>
+        <v>123312540</v>
       </c>
       <c r="B45" t="n">
-        <v>98079</v>
+        <v>57861</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5552,35 +5539,39 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5588,13 +5579,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>576804</v>
+        <v>576808</v>
       </c>
       <c r="R45" t="n">
-        <v>6379845</v>
+        <v>6379847</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5621,18 +5612,27 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5651,10 +5651,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123313067</v>
+        <v>123312569</v>
       </c>
       <c r="B46" t="n">
-        <v>91010</v>
+        <v>105095</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5663,38 +5663,35 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5702,10 +5699,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>576682</v>
+        <v>576803</v>
       </c>
       <c r="R46" t="n">
-        <v>6379963</v>
+        <v>6379887</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5735,9 +5732,19 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5765,10 +5772,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123312921</v>
+        <v>123312502</v>
       </c>
       <c r="B47" t="n">
-        <v>98079</v>
+        <v>95683</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5777,33 +5784,29 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
@@ -5813,10 +5816,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>576799</v>
+        <v>576740</v>
       </c>
       <c r="R47" t="n">
-        <v>6379827</v>
+        <v>6379855</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5846,9 +5849,19 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5876,10 +5889,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123313044</v>
+        <v>123312921</v>
       </c>
       <c r="B48" t="n">
-        <v>91400</v>
+        <v>98079</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5888,38 +5901,35 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5927,10 +5937,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>576690</v>
+        <v>576799</v>
       </c>
       <c r="R48" t="n">
-        <v>6379955</v>
+        <v>6379827</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5990,7 +6000,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123312569</v>
+        <v>123312896</v>
       </c>
       <c r="B49" t="n">
         <v>105095</v>
@@ -6038,10 +6048,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>576803</v>
+        <v>576804</v>
       </c>
       <c r="R49" t="n">
-        <v>6379887</v>
+        <v>6379845</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6071,19 +6081,9 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>15:50</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6111,10 +6111,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123312958</v>
+        <v>123313124</v>
       </c>
       <c r="B50" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6123,25 +6123,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6159,10 +6159,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>576745</v>
+        <v>576507</v>
       </c>
       <c r="R50" t="n">
-        <v>6379872</v>
+        <v>6379922</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 11444-2025 artfynd.xlsx
+++ b/artfynd/A 11444-2025 artfynd.xlsx
@@ -3932,10 +3932,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123313067</v>
+        <v>123313086</v>
       </c>
       <c r="B31" t="n">
-        <v>91010</v>
+        <v>57861</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3944,38 +3944,39 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3983,10 +3984,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>576682</v>
+        <v>576640</v>
       </c>
       <c r="R31" t="n">
-        <v>6379963</v>
+        <v>6379941</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4027,7 +4028,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4046,7 +4046,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123313080</v>
+        <v>123312935</v>
       </c>
       <c r="B32" t="n">
         <v>98079</v>
@@ -4080,7 +4080,11 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
@@ -4090,10 +4094,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>576640</v>
+        <v>576793</v>
       </c>
       <c r="R32" t="n">
-        <v>6379941</v>
+        <v>6379822</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4153,10 +4157,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123312773</v>
+        <v>123312921</v>
       </c>
       <c r="B33" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4165,25 +4169,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4201,10 +4205,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>576839</v>
+        <v>576799</v>
       </c>
       <c r="R33" t="n">
-        <v>6379721</v>
+        <v>6379827</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4264,10 +4268,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123312993</v>
+        <v>123312569</v>
       </c>
       <c r="B34" t="n">
-        <v>91010</v>
+        <v>105095</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4276,38 +4280,35 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4315,10 +4316,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>576745</v>
+        <v>576803</v>
       </c>
       <c r="R34" t="n">
-        <v>6379872</v>
+        <v>6379887</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4348,9 +4349,19 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4378,10 +4389,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123312486</v>
+        <v>123312753</v>
       </c>
       <c r="B35" t="n">
-        <v>57861</v>
+        <v>98079</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4390,39 +4401,35 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4430,13 +4437,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>576693</v>
+        <v>576835</v>
       </c>
       <c r="R35" t="n">
-        <v>6379898</v>
+        <v>6379711</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4463,27 +4470,18 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4502,7 +4500,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123312753</v>
+        <v>123313080</v>
       </c>
       <c r="B36" t="n">
         <v>98079</v>
@@ -4536,11 +4534,7 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
@@ -4550,10 +4544,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>576835</v>
+        <v>576640</v>
       </c>
       <c r="R36" t="n">
-        <v>6379711</v>
+        <v>6379941</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4613,10 +4607,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123312935</v>
+        <v>123312808</v>
       </c>
       <c r="B37" t="n">
-        <v>98079</v>
+        <v>96957</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4625,31 +4619,35 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -4661,10 +4659,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>576793</v>
+        <v>576804</v>
       </c>
       <c r="R37" t="n">
-        <v>6379822</v>
+        <v>6379891</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4724,10 +4722,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123312904</v>
+        <v>123313044</v>
       </c>
       <c r="B38" t="n">
-        <v>98079</v>
+        <v>91400</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4736,35 +4734,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4772,10 +4773,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>576804</v>
+        <v>576690</v>
       </c>
       <c r="R38" t="n">
-        <v>6379845</v>
+        <v>6379955</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4835,10 +4836,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123313044</v>
+        <v>123312540</v>
       </c>
       <c r="B39" t="n">
-        <v>91400</v>
+        <v>57861</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4851,21 +4852,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5420</v>
+        <v>103015</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4873,12 +4874,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4886,13 +4888,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>576690</v>
+        <v>576808</v>
       </c>
       <c r="R39" t="n">
-        <v>6379955</v>
+        <v>6379847</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4919,18 +4921,27 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4949,10 +4960,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123313086</v>
+        <v>123312958</v>
       </c>
       <c r="B40" t="n">
-        <v>57861</v>
+        <v>105095</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4965,35 +4976,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5001,10 +5008,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>576640</v>
+        <v>576745</v>
       </c>
       <c r="R40" t="n">
-        <v>6379941</v>
+        <v>6379872</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5045,6 +5052,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5063,10 +5071,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123312524</v>
+        <v>123312896</v>
       </c>
       <c r="B41" t="n">
-        <v>92271</v>
+        <v>105095</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5079,34 +5087,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5114,10 +5119,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>576731</v>
+        <v>576804</v>
       </c>
       <c r="R41" t="n">
-        <v>6379842</v>
+        <v>6379845</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5147,19 +5152,9 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>15:50</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5187,10 +5182,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123312808</v>
+        <v>123313067</v>
       </c>
       <c r="B42" t="n">
-        <v>96957</v>
+        <v>91010</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5199,39 +5194,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>5442</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5239,10 +5233,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>576804</v>
+        <v>576682</v>
       </c>
       <c r="R42" t="n">
-        <v>6379891</v>
+        <v>6379963</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5302,7 +5296,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123312958</v>
+        <v>123312773</v>
       </c>
       <c r="B43" t="n">
         <v>105095</v>
@@ -5350,10 +5344,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>576745</v>
+        <v>576839</v>
       </c>
       <c r="R43" t="n">
-        <v>6379872</v>
+        <v>6379721</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5413,10 +5407,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123313052</v>
+        <v>123312993</v>
       </c>
       <c r="B44" t="n">
-        <v>91400</v>
+        <v>91010</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5425,30 +5419,30 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5420</v>
+        <v>5442</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5464,10 +5458,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>576677</v>
+        <v>576745</v>
       </c>
       <c r="R44" t="n">
-        <v>6379959</v>
+        <v>6379872</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5527,10 +5521,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123312540</v>
+        <v>123312502</v>
       </c>
       <c r="B45" t="n">
-        <v>57861</v>
+        <v>95683</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5543,35 +5537,27 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5579,13 +5565,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>576808</v>
+        <v>576740</v>
       </c>
       <c r="R45" t="n">
-        <v>6379847</v>
+        <v>6379855</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5633,6 +5619,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5651,10 +5638,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123312569</v>
+        <v>123313052</v>
       </c>
       <c r="B46" t="n">
-        <v>105095</v>
+        <v>91400</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5667,31 +5654,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221144</v>
+        <v>5420</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5699,10 +5689,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>576803</v>
+        <v>576677</v>
       </c>
       <c r="R46" t="n">
-        <v>6379887</v>
+        <v>6379959</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5732,19 +5722,9 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>15:50</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5772,10 +5752,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123312502</v>
+        <v>123312486</v>
       </c>
       <c r="B47" t="n">
-        <v>95683</v>
+        <v>57861</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5788,27 +5768,35 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5816,13 +5804,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>576740</v>
+        <v>576693</v>
       </c>
       <c r="R47" t="n">
-        <v>6379855</v>
+        <v>6379898</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5870,7 +5858,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5889,7 +5876,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123312921</v>
+        <v>123312904</v>
       </c>
       <c r="B48" t="n">
         <v>98079</v>
@@ -5937,10 +5924,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>576799</v>
+        <v>576804</v>
       </c>
       <c r="R48" t="n">
-        <v>6379827</v>
+        <v>6379845</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6000,10 +5987,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123312896</v>
+        <v>123313124</v>
       </c>
       <c r="B49" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6012,25 +5999,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6048,10 +6035,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>576804</v>
+        <v>576507</v>
       </c>
       <c r="R49" t="n">
-        <v>6379845</v>
+        <v>6379922</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6111,10 +6098,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123313124</v>
+        <v>123312524</v>
       </c>
       <c r="B50" t="n">
-        <v>98079</v>
+        <v>92271</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6123,35 +6110,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6159,10 +6149,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>576507</v>
+        <v>576731</v>
       </c>
       <c r="R50" t="n">
-        <v>6379922</v>
+        <v>6379842</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6192,9 +6182,19 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 11444-2025 artfynd.xlsx
+++ b/artfynd/A 11444-2025 artfynd.xlsx
@@ -3932,10 +3932,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123313086</v>
+        <v>123312896</v>
       </c>
       <c r="B31" t="n">
-        <v>57861</v>
+        <v>105095</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3948,35 +3948,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3984,10 +3980,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>576640</v>
+        <v>576804</v>
       </c>
       <c r="R31" t="n">
-        <v>6379941</v>
+        <v>6379845</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4028,6 +4024,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4046,10 +4043,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123312935</v>
+        <v>123313067</v>
       </c>
       <c r="B32" t="n">
-        <v>98079</v>
+        <v>91010</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4058,35 +4055,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4094,10 +4094,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>576793</v>
+        <v>576682</v>
       </c>
       <c r="R32" t="n">
-        <v>6379822</v>
+        <v>6379963</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4157,10 +4157,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123312921</v>
+        <v>123312773</v>
       </c>
       <c r="B33" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4169,25 +4169,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4205,10 +4205,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>576799</v>
+        <v>576839</v>
       </c>
       <c r="R33" t="n">
-        <v>6379827</v>
+        <v>6379721</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4268,7 +4268,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123312569</v>
+        <v>123312958</v>
       </c>
       <c r="B34" t="n">
         <v>105095</v>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>576803</v>
+        <v>576745</v>
       </c>
       <c r="R34" t="n">
-        <v>6379887</v>
+        <v>6379872</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4349,19 +4349,9 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>15:50</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4389,7 +4379,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123312753</v>
+        <v>123312935</v>
       </c>
       <c r="B35" t="n">
         <v>98079</v>
@@ -4437,10 +4427,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>576835</v>
+        <v>576793</v>
       </c>
       <c r="R35" t="n">
-        <v>6379711</v>
+        <v>6379822</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4500,10 +4490,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123313080</v>
+        <v>123312540</v>
       </c>
       <c r="B36" t="n">
-        <v>98079</v>
+        <v>57861</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4512,31 +4502,39 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4544,13 +4542,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>576640</v>
+        <v>576808</v>
       </c>
       <c r="R36" t="n">
-        <v>6379941</v>
+        <v>6379847</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4577,18 +4575,27 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4722,10 +4729,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123313044</v>
+        <v>123312486</v>
       </c>
       <c r="B38" t="n">
-        <v>91400</v>
+        <v>57861</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4738,21 +4745,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5420</v>
+        <v>103015</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4760,12 +4767,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4773,13 +4781,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>576690</v>
+        <v>576693</v>
       </c>
       <c r="R38" t="n">
-        <v>6379955</v>
+        <v>6379898</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4806,18 +4814,27 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4836,10 +4853,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123312540</v>
+        <v>123313052</v>
       </c>
       <c r="B39" t="n">
-        <v>57861</v>
+        <v>91400</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4852,35 +4869,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103015</v>
+        <v>5420</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4888,13 +4904,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>576808</v>
+        <v>576677</v>
       </c>
       <c r="R39" t="n">
-        <v>6379847</v>
+        <v>6379959</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4921,27 +4937,18 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4960,10 +4967,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123312958</v>
+        <v>123312904</v>
       </c>
       <c r="B40" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4972,25 +4979,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5008,10 +5015,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>576745</v>
+        <v>576804</v>
       </c>
       <c r="R40" t="n">
-        <v>6379872</v>
+        <v>6379845</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5071,10 +5078,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123312896</v>
+        <v>123313124</v>
       </c>
       <c r="B41" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5083,25 +5090,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5119,10 +5126,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>576804</v>
+        <v>576507</v>
       </c>
       <c r="R41" t="n">
-        <v>6379845</v>
+        <v>6379922</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5182,10 +5189,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123313067</v>
+        <v>123313086</v>
       </c>
       <c r="B42" t="n">
-        <v>91010</v>
+        <v>57861</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5194,38 +5201,39 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5442</v>
+        <v>103015</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5233,10 +5241,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>576682</v>
+        <v>576640</v>
       </c>
       <c r="R42" t="n">
-        <v>6379963</v>
+        <v>6379941</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5277,7 +5285,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5296,10 +5303,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123312773</v>
+        <v>123312753</v>
       </c>
       <c r="B43" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5308,25 +5315,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5344,10 +5351,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>576839</v>
+        <v>576835</v>
       </c>
       <c r="R43" t="n">
-        <v>6379721</v>
+        <v>6379711</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5400,17 +5407,17 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+          <t>Per Muhr, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123312993</v>
+        <v>123312921</v>
       </c>
       <c r="B44" t="n">
-        <v>91010</v>
+        <v>98079</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5419,38 +5426,35 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5458,10 +5462,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>576745</v>
+        <v>576799</v>
       </c>
       <c r="R44" t="n">
-        <v>6379872</v>
+        <v>6379827</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5521,10 +5525,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123312502</v>
+        <v>123312524</v>
       </c>
       <c r="B45" t="n">
-        <v>95683</v>
+        <v>92271</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5537,27 +5541,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5565,10 +5576,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>576740</v>
+        <v>576731</v>
       </c>
       <c r="R45" t="n">
-        <v>6379855</v>
+        <v>6379842</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5638,10 +5649,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123313052</v>
+        <v>123312993</v>
       </c>
       <c r="B46" t="n">
-        <v>91400</v>
+        <v>91010</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5650,30 +5661,30 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5420</v>
+        <v>5442</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5689,10 +5700,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>576677</v>
+        <v>576745</v>
       </c>
       <c r="R46" t="n">
-        <v>6379959</v>
+        <v>6379872</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5752,10 +5763,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123312486</v>
+        <v>123312569</v>
       </c>
       <c r="B47" t="n">
-        <v>57861</v>
+        <v>105095</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5768,35 +5779,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5804,13 +5811,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>576693</v>
+        <v>576803</v>
       </c>
       <c r="R47" t="n">
-        <v>6379898</v>
+        <v>6379887</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5858,6 +5865,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5876,10 +5884,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123312904</v>
+        <v>123312502</v>
       </c>
       <c r="B48" t="n">
-        <v>98079</v>
+        <v>95683</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5888,33 +5896,29 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
@@ -5924,10 +5928,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>576804</v>
+        <v>576740</v>
       </c>
       <c r="R48" t="n">
-        <v>6379845</v>
+        <v>6379855</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5957,9 +5961,19 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5987,7 +6001,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123313124</v>
+        <v>123313080</v>
       </c>
       <c r="B49" t="n">
         <v>98079</v>
@@ -6021,11 +6035,7 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
@@ -6035,10 +6045,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>576507</v>
+        <v>576640</v>
       </c>
       <c r="R49" t="n">
-        <v>6379922</v>
+        <v>6379941</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6098,10 +6108,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123312524</v>
+        <v>123313044</v>
       </c>
       <c r="B50" t="n">
-        <v>92271</v>
+        <v>91400</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6114,26 +6124,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6149,10 +6159,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>576731</v>
+        <v>576690</v>
       </c>
       <c r="R50" t="n">
-        <v>6379842</v>
+        <v>6379955</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6182,19 +6192,9 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>15:50</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 11444-2025 artfynd.xlsx
+++ b/artfynd/A 11444-2025 artfynd.xlsx
@@ -4490,10 +4490,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123312540</v>
+        <v>123312808</v>
       </c>
       <c r="B36" t="n">
-        <v>57861</v>
+        <v>96957</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4506,35 +4506,35 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4542,13 +4542,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>576808</v>
+        <v>576804</v>
       </c>
       <c r="R36" t="n">
-        <v>6379847</v>
+        <v>6379891</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4575,27 +4575,18 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4614,10 +4605,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123312808</v>
+        <v>123312540</v>
       </c>
       <c r="B37" t="n">
-        <v>96957</v>
+        <v>57861</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4630,35 +4621,35 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4666,13 +4657,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>576804</v>
+        <v>576808</v>
       </c>
       <c r="R37" t="n">
-        <v>6379891</v>
+        <v>6379847</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4699,18 +4690,27 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11444-2025 artfynd.xlsx
+++ b/artfynd/A 11444-2025 artfynd.xlsx
@@ -1550,7 +1550,7 @@
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">

--- a/artfynd/A 11444-2025 artfynd.xlsx
+++ b/artfynd/A 11444-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,47 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123259392</v>
+        <v>123259209</v>
       </c>
       <c r="B2" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576988</v>
+        <v>576992</v>
       </c>
       <c r="R2" t="n">
-        <v>6379698</v>
+        <v>6379660</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,37 +784,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123259628</v>
+        <v>123259828</v>
       </c>
       <c r="B3" t="n">
-        <v>57861</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -824,27 +817,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A11444, Grönlid, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576883</v>
+        <v>576838</v>
       </c>
       <c r="R3" t="n">
-        <v>6379747</v>
+        <v>6379654</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,6 +874,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,47 +893,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123259930</v>
+        <v>123259851</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -948,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576949</v>
+        <v>576835</v>
       </c>
       <c r="R4" t="n">
-        <v>6379790</v>
+        <v>6379715</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,15 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123259419</v>
+        <v>123260011</v>
       </c>
       <c r="B5" t="n">
-        <v>57644</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +1013,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1049,27 +1035,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 11444, Grönlif, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576985</v>
+        <v>576847</v>
       </c>
       <c r="R5" t="n">
-        <v>6379714</v>
+        <v>6379709</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1107,6 +1092,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1125,45 +1111,36 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123259362</v>
+        <v>123259498</v>
       </c>
       <c r="B6" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1173,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576989</v>
+        <v>576965</v>
       </c>
       <c r="R6" t="n">
-        <v>6379691</v>
+        <v>6379700</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,50 +1213,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123259209</v>
+        <v>123312502</v>
       </c>
       <c r="B7" t="n">
-        <v>90990</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1287,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576992</v>
+        <v>576740</v>
       </c>
       <c r="R7" t="n">
-        <v>6379660</v>
+        <v>6379855</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,12 +1282,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,50 +1318,52 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123259498</v>
+        <v>123259111</v>
       </c>
       <c r="B8" t="n">
-        <v>95683</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1394,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576965</v>
+        <v>577001</v>
       </c>
       <c r="R8" t="n">
-        <v>6379700</v>
+        <v>6379581</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,15 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123259084</v>
+        <v>123259131</v>
       </c>
       <c r="B9" t="n">
-        <v>92299</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,26 +1445,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1504,14 +1476,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 11444, Grönled, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577012</v>
+        <v>577009</v>
       </c>
       <c r="R9" t="n">
-        <v>6379533</v>
+        <v>6379596</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1550,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
@@ -1571,15 +1543,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123259882</v>
+        <v>123259183</v>
       </c>
       <c r="B10" t="n">
-        <v>57507</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,31 +1554,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1619,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576832</v>
+        <v>577000</v>
       </c>
       <c r="R10" t="n">
-        <v>6379712</v>
+        <v>6379640</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1657,17 +1627,13 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Bearbetat torrträd</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1686,47 +1652,41 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123259948</v>
+        <v>123259460</v>
       </c>
       <c r="B11" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1734,10 +1694,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576939</v>
+        <v>576977</v>
       </c>
       <c r="R11" t="n">
-        <v>6379798</v>
+        <v>6379694</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1797,15 +1757,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123259993</v>
+        <v>123312524</v>
       </c>
       <c r="B12" t="n">
-        <v>91010</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1813,26 +1768,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1848,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576929</v>
+        <v>576731</v>
       </c>
       <c r="R12" t="n">
-        <v>6379832</v>
+        <v>6379842</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1878,12 +1833,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1904,44 +1869,39 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123259157</v>
+        <v>123259910</v>
       </c>
       <c r="B13" t="n">
-        <v>57644</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>5420</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1949,13 +1909,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1963,13 +1922,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576997</v>
+        <v>576891</v>
       </c>
       <c r="R13" t="n">
-        <v>6379617</v>
+        <v>6379777</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2007,6 +1966,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2025,47 +1985,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123259522</v>
+        <v>123313044</v>
       </c>
       <c r="B14" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2073,10 +2031,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576971</v>
+        <v>576690</v>
       </c>
       <c r="R14" t="n">
-        <v>6379715</v>
+        <v>6379955</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2103,12 +2061,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2129,22 +2087,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123259460</v>
+        <v>123313052</v>
       </c>
       <c r="B15" t="n">
-        <v>92271</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2152,24 +2105,28 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -2183,10 +2140,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576977</v>
+        <v>576677</v>
       </c>
       <c r="R15" t="n">
-        <v>6379694</v>
+        <v>6379959</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2213,12 +2170,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2239,22 +2196,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123260011</v>
+        <v>123259993</v>
       </c>
       <c r="B16" t="n">
-        <v>90990</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2262,21 +2214,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2286,7 +2238,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -2297,10 +2249,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576847</v>
+        <v>576929</v>
       </c>
       <c r="R16" t="n">
-        <v>6379709</v>
+        <v>6379832</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2360,47 +2312,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123259332</v>
+        <v>123312993</v>
       </c>
       <c r="B17" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2408,10 +2358,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576987</v>
+        <v>576745</v>
       </c>
       <c r="R17" t="n">
-        <v>6379692</v>
+        <v>6379872</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2438,12 +2388,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2464,54 +2414,52 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123259554</v>
+        <v>123313067</v>
       </c>
       <c r="B18" t="n">
-        <v>105095</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2519,10 +2467,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576891</v>
+        <v>576682</v>
       </c>
       <c r="R18" t="n">
-        <v>6379769</v>
+        <v>6379963</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2549,12 +2497,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2575,54 +2523,49 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123259440</v>
+        <v>123259882</v>
       </c>
       <c r="B19" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2630,10 +2573,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576980</v>
+        <v>576832</v>
       </c>
       <c r="R19" t="n">
-        <v>6379697</v>
+        <v>6379712</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2668,13 +2611,17 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Bearbetat torrträd</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2693,37 +2640,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123259851</v>
+        <v>123259628</v>
       </c>
       <c r="B20" t="n">
-        <v>90990</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2731,26 +2673,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576835</v>
+        <v>576883</v>
       </c>
       <c r="R20" t="n">
-        <v>6379715</v>
+        <v>6379747</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2788,7 +2731,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2807,15 +2749,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123259131</v>
+        <v>123259757</v>
       </c>
       <c r="B21" t="n">
-        <v>92271</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2823,21 +2760,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2845,12 +2782,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2858,13 +2796,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577009</v>
+        <v>576870</v>
       </c>
       <c r="R21" t="n">
-        <v>6379596</v>
+        <v>6379674</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2902,7 +2840,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2921,15 +2858,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123259910</v>
+        <v>123312486</v>
       </c>
       <c r="B22" t="n">
-        <v>91400</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2937,21 +2869,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5420</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2959,12 +2891,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2972,13 +2905,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576891</v>
+        <v>576693</v>
       </c>
       <c r="R22" t="n">
-        <v>6379777</v>
+        <v>6379898</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3002,12 +2935,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3016,7 +2959,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3028,44 +2970,39 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123259828</v>
+        <v>123312540</v>
       </c>
       <c r="B23" t="n">
-        <v>90990</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3073,12 +3010,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3086,13 +3024,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576838</v>
+        <v>576808</v>
       </c>
       <c r="R23" t="n">
-        <v>6379654</v>
+        <v>6379847</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3116,12 +3054,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3130,7 +3078,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3142,54 +3089,53 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123260939</v>
+        <v>123313086</v>
       </c>
       <c r="B24" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3197,10 +3143,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>576951</v>
+        <v>576640</v>
       </c>
       <c r="R24" t="n">
-        <v>6379805</v>
+        <v>6379941</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3227,12 +3173,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3241,7 +3187,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3253,68 +3198,67 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123259271</v>
+        <v>123259157</v>
       </c>
       <c r="B25" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>A 11444. Grönlid, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>576994</v>
+        <v>576997</v>
       </c>
       <c r="R25" t="n">
-        <v>6379690</v>
+        <v>6379617</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3352,7 +3296,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3371,61 +3314,60 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123259974</v>
+        <v>123259419</v>
       </c>
       <c r="B26" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444, Grönlif, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>576950</v>
+        <v>576985</v>
       </c>
       <c r="R26" t="n">
-        <v>6379824</v>
+        <v>6379714</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3463,7 +3405,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3482,37 +3423,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123259183</v>
+        <v>123312463</v>
       </c>
       <c r="B27" t="n">
-        <v>92271</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3520,12 +3456,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3533,13 +3470,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577000</v>
+        <v>576650</v>
       </c>
       <c r="R27" t="n">
-        <v>6379640</v>
+        <v>6379729</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3563,12 +3500,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3577,7 +3524,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3589,57 +3535,49 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123259111</v>
+        <v>123259239</v>
       </c>
       <c r="B28" t="n">
-        <v>92271</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3647,10 +3585,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577001</v>
+        <v>576999</v>
       </c>
       <c r="R28" t="n">
-        <v>6379581</v>
+        <v>6379686</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3710,15 +3648,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123259312</v>
+        <v>123259271</v>
       </c>
       <c r="B29" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3754,14 +3687,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444. Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>576990</v>
+        <v>576994</v>
       </c>
       <c r="R29" t="n">
-        <v>6379697</v>
+        <v>6379690</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3821,15 +3754,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123259471</v>
+        <v>123259312</v>
       </c>
       <c r="B30" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3865,14 +3793,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>A 11444, Grönlif, Sm</t>
+          <t>A 11444, Grönlid, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>576971</v>
+        <v>576990</v>
       </c>
       <c r="R30" t="n">
-        <v>6379688</v>
+        <v>6379697</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3932,37 +3860,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123312896</v>
+        <v>123259332</v>
       </c>
       <c r="B31" t="n">
-        <v>105095</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3980,10 +3903,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>576804</v>
+        <v>576987</v>
       </c>
       <c r="R31" t="n">
-        <v>6379845</v>
+        <v>6379692</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4010,12 +3933,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4036,57 +3959,49 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123313067</v>
+        <v>123259362</v>
       </c>
       <c r="B32" t="n">
-        <v>91010</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4094,10 +4009,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>576682</v>
+        <v>576989</v>
       </c>
       <c r="R32" t="n">
-        <v>6379963</v>
+        <v>6379691</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4124,12 +4039,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4150,44 +4065,39 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123312773</v>
+        <v>123259392</v>
       </c>
       <c r="B33" t="n">
-        <v>105095</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4205,10 +4115,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>576839</v>
+        <v>576988</v>
       </c>
       <c r="R33" t="n">
-        <v>6379721</v>
+        <v>6379698</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4235,12 +4145,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4261,44 +4171,39 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123312958</v>
+        <v>123259440</v>
       </c>
       <c r="B34" t="n">
-        <v>105095</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4316,10 +4221,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>576745</v>
+        <v>576980</v>
       </c>
       <c r="R34" t="n">
-        <v>6379872</v>
+        <v>6379697</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4346,12 +4251,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4372,22 +4277,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123312935</v>
+        <v>123259471</v>
       </c>
       <c r="B35" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4423,14 +4323,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>A 11444, Grönlid, Sm</t>
+          <t>A 11444, Grönlif, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>576793</v>
+        <v>576971</v>
       </c>
       <c r="R35" t="n">
-        <v>6379822</v>
+        <v>6379688</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4457,12 +4357,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4483,54 +4383,45 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123312808</v>
+        <v>123259522</v>
       </c>
       <c r="B36" t="n">
-        <v>96957</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -4542,10 +4433,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>576804</v>
+        <v>576971</v>
       </c>
       <c r="R36" t="n">
-        <v>6379891</v>
+        <v>6379715</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4572,12 +4463,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4598,58 +4489,49 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123312540</v>
+        <v>123259716</v>
       </c>
       <c r="B37" t="n">
-        <v>57861</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4657,13 +4539,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>576808</v>
+        <v>576878</v>
       </c>
       <c r="R37" t="n">
-        <v>6379847</v>
+        <v>6379675</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4687,22 +4569,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>15:50</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>15:50</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4711,6 +4583,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4722,58 +4595,49 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123312486</v>
+        <v>123259930</v>
       </c>
       <c r="B38" t="n">
-        <v>57861</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4781,13 +4645,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>576693</v>
+        <v>576949</v>
       </c>
       <c r="R38" t="n">
-        <v>6379898</v>
+        <v>6379790</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4811,22 +4675,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>15:50</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>15:50</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4835,6 +4689,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4846,57 +4701,49 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123313052</v>
+        <v>123259948</v>
       </c>
       <c r="B39" t="n">
-        <v>91400</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4904,10 +4751,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>576677</v>
+        <v>576939</v>
       </c>
       <c r="R39" t="n">
-        <v>6379959</v>
+        <v>6379798</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4934,12 +4781,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4960,22 +4807,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123312904</v>
+        <v>123259974</v>
       </c>
       <c r="B40" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5015,10 +4857,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>576804</v>
+        <v>576950</v>
       </c>
       <c r="R40" t="n">
-        <v>6379845</v>
+        <v>6379824</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5045,12 +4887,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5071,22 +4913,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123313124</v>
+        <v>123260939</v>
       </c>
       <c r="B41" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5126,10 +4963,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>576507</v>
+        <v>576951</v>
       </c>
       <c r="R41" t="n">
-        <v>6379922</v>
+        <v>6379805</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5156,12 +4993,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5182,58 +5019,49 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123313086</v>
+        <v>123312753</v>
       </c>
       <c r="B42" t="n">
-        <v>57861</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5241,10 +5069,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>576640</v>
+        <v>576835</v>
       </c>
       <c r="R42" t="n">
-        <v>6379941</v>
+        <v>6379711</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5285,6 +5113,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5303,15 +5132,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123312753</v>
+        <v>123312904</v>
       </c>
       <c r="B43" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5351,10 +5175,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>576835</v>
+        <v>576804</v>
       </c>
       <c r="R43" t="n">
-        <v>6379711</v>
+        <v>6379845</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5407,7 +5231,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Per Muhr, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5417,12 +5241,7 @@
         <v>123312921</v>
       </c>
       <c r="B44" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5525,50 +5344,42 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123312524</v>
+        <v>123312935</v>
       </c>
       <c r="B45" t="n">
-        <v>92271</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5576,10 +5387,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>576731</v>
+        <v>576793</v>
       </c>
       <c r="R45" t="n">
-        <v>6379842</v>
+        <v>6379822</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5609,19 +5420,9 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>15:50</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5649,50 +5450,38 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123312993</v>
+        <v>123313080</v>
       </c>
       <c r="B46" t="n">
-        <v>91010</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5700,10 +5489,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>576745</v>
+        <v>576640</v>
       </c>
       <c r="R46" t="n">
-        <v>6379872</v>
+        <v>6379941</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5763,37 +5552,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123312569</v>
+        <v>123313124</v>
       </c>
       <c r="B47" t="n">
-        <v>105095</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5811,10 +5595,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>576803</v>
+        <v>576507</v>
       </c>
       <c r="R47" t="n">
-        <v>6379887</v>
+        <v>6379922</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5844,19 +5628,9 @@
           <t>2025-03-19</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>15:50</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>15:50</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5884,15 +5658,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123312502</v>
+        <v>123259554</v>
       </c>
       <c r="B48" t="n">
-        <v>95683</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5900,25 +5669,29 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
@@ -5928,10 +5701,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>576740</v>
+        <v>576891</v>
       </c>
       <c r="R48" t="n">
-        <v>6379855</v>
+        <v>6379769</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5958,22 +5731,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>15:50</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>15:50</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5994,48 +5757,47 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123313080</v>
+        <v>123312474</v>
       </c>
       <c r="B49" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
@@ -6045,13 +5807,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>576640</v>
+        <v>576650</v>
       </c>
       <c r="R49" t="n">
-        <v>6379941</v>
+        <v>6379729</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6078,9 +5840,19 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6108,15 +5880,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123313044</v>
+        <v>123312569</v>
       </c>
       <c r="B50" t="n">
-        <v>91400</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6124,34 +5891,31 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5420</v>
+        <v>221144</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6159,10 +5923,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>576690</v>
+        <v>576803</v>
       </c>
       <c r="R50" t="n">
-        <v>6379955</v>
+        <v>6379887</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6192,9 +5956,19 @@
           <t>2025-03-19</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6219,6 +5993,434 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>123312773</v>
+      </c>
+      <c r="B51" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>A 11444, Grönlid, Sm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>576839</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6379721</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>123312896</v>
+      </c>
+      <c r="B52" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>A 11444, Grönlid, Sm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>576804</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6379845</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>123312958</v>
+      </c>
+      <c r="B53" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>A 11444, Grönlid, Sm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>576745</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6379872</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>123312808</v>
+      </c>
+      <c r="B54" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>A 11444, Grönlid, Sm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>576804</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6379891</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
